--- a/database/event/8039/event_8039_evp_summary.xlsx
+++ b/database/event/8039/event_8039_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>8.2433</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5.3458</v>
       </c>
       <c r="D2" t="n">
         <v>2.9087</v>
@@ -545,7 +545,7 @@
         <v>7.8097</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.0646</v>
       </c>
       <c r="D3" t="n">
         <v>2.7336</v>
@@ -591,7 +591,7 @@
         <v>5.5274</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.5845</v>
       </c>
       <c r="D4" t="n">
         <v>1.8116</v>
@@ -637,7 +637,7 @@
         <v>5.0054</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.246</v>
       </c>
       <c r="D5" t="n">
         <v>1.6007</v>
@@ -683,7 +683,7 @@
         <v>4.4484</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.8848</v>
       </c>
       <c r="D6" t="n">
         <v>1.3757</v>
@@ -729,7 +729,7 @@
         <v>3.7641</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.441</v>
       </c>
       <c r="D7" t="n">
         <v>1.0993</v>
@@ -775,7 +775,7 @@
         <v>3.4506</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.2377</v>
       </c>
       <c r="D8" t="n">
         <v>0.9726</v>
@@ -821,7 +821,7 @@
         <v>3.4029</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.2068</v>
       </c>
       <c r="D9" t="n">
         <v>0.9533</v>
@@ -867,7 +867,7 @@
         <v>3.1944</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.0716</v>
       </c>
       <c r="D10" t="n">
         <v>0.8691</v>
@@ -913,7 +913,7 @@
         <v>2.8855</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.8713</v>
       </c>
       <c r="D11" t="n">
         <v>0.7443</v>
@@ -959,7 +959,7 @@
         <v>2.8455</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.8453</v>
       </c>
       <c r="D12" t="n">
         <v>0.7282</v>
@@ -1005,7 +1005,7 @@
         <v>2.7179</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="D13" t="n">
         <v>0.6766</v>
@@ -1051,7 +1051,7 @@
         <v>2.1462</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.3918</v>
       </c>
       <c r="D14" t="n">
         <v>0.4457</v>
@@ -1097,7 +1097,7 @@
         <v>1.9958</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.2943</v>
       </c>
       <c r="D15" t="n">
         <v>0.3849</v>
@@ -1143,7 +1143,7 @@
         <v>1.7285</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.1209</v>
       </c>
       <c r="D16" t="n">
         <v>0.2769</v>
@@ -1189,7 +1189,7 @@
         <v>1.7041</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.1051</v>
       </c>
       <c r="D17" t="n">
         <v>0.2671</v>
@@ -1235,7 +1235,7 @@
         <v>1.5567</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.0095</v>
       </c>
       <c r="D18" t="n">
         <v>0.2075</v>
@@ -1281,7 +1281,7 @@
         <v>1.4092</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.9139</v>
       </c>
       <c r="D19" t="n">
         <v>0.1479</v>
@@ -1327,7 +1327,7 @@
         <v>1.3696</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.8882</v>
       </c>
       <c r="D20" t="n">
         <v>0.1319</v>
@@ -1373,7 +1373,7 @@
         <v>1.2638</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.8196</v>
       </c>
       <c r="D21" t="n">
         <v>0.0892</v>
@@ -1419,7 +1419,7 @@
         <v>1.259</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.8165</v>
       </c>
       <c r="D22" t="n">
         <v>0.0872</v>
@@ -1465,7 +1465,7 @@
         <v>1.1272</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="D23" t="n">
         <v>0.034</v>
@@ -1511,7 +1511,7 @@
         <v>1.0992</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.7128</v>
       </c>
       <c r="D24" t="n">
         <v>0.0227</v>
@@ -1557,7 +1557,7 @@
         <v>1.0799</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.7003</v>
       </c>
       <c r="D25" t="n">
         <v>0.0149</v>
@@ -1603,7 +1603,7 @@
         <v>1.0494</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.6805</v>
       </c>
       <c r="D26" t="n">
         <v>0.0026</v>
@@ -1649,7 +1649,7 @@
         <v>0.9177</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.5951</v>
       </c>
       <c r="D27" t="n">
         <v>-0.0506</v>
@@ -1695,7 +1695,7 @@
         <v>0.9144</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.593</v>
       </c>
       <c r="D28" t="n">
         <v>-0.052</v>
@@ -1741,7 +1741,7 @@
         <v>0.8262</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="D29" t="n">
         <v>-0.0876</v>
@@ -1787,7 +1787,7 @@
         <v>0.7507</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.4868</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1181</v>
@@ -1833,7 +1833,7 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.4612</v>
       </c>
       <c r="D31" t="n">
         <v>-0.1341</v>
@@ -1879,7 +1879,7 @@
         <v>0.7050999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.4573</v>
       </c>
       <c r="D32" t="n">
         <v>-0.1365</v>
@@ -1925,7 +1925,7 @@
         <v>0.6754</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="D33" t="n">
         <v>-0.1485</v>
@@ -1971,7 +1971,7 @@
         <v>0.6231</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.4041</v>
       </c>
       <c r="D34" t="n">
         <v>-0.1696</v>
@@ -2017,7 +2017,7 @@
         <v>0.5862000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.3802</v>
       </c>
       <c r="D35" t="n">
         <v>-0.1846</v>
@@ -2063,7 +2063,7 @@
         <v>0.5345</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.3466</v>
       </c>
       <c r="D36" t="n">
         <v>-0.2054</v>
@@ -2109,7 +2109,7 @@
         <v>0.4601</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2984</v>
       </c>
       <c r="D37" t="n">
         <v>-0.2355</v>
@@ -2155,7 +2155,7 @@
         <v>0.4601</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2984</v>
       </c>
       <c r="D38" t="n">
         <v>-0.2355</v>
@@ -2201,7 +2201,7 @@
         <v>0.4492</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2913</v>
       </c>
       <c r="D39" t="n">
         <v>-0.2399</v>
@@ -2247,7 +2247,7 @@
         <v>0.3694</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2396</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2721</v>
@@ -2293,7 +2293,7 @@
         <v>0.25</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1621</v>
       </c>
       <c r="D41" t="n">
         <v>-0.3204</v>
@@ -2339,7 +2339,7 @@
         <v>0.1527</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="D42" t="n">
         <v>-0.3597</v>
@@ -2385,7 +2385,7 @@
         <v>0.0872</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.0565</v>
       </c>
       <c r="D43" t="n">
         <v>-0.3861</v>
@@ -2431,7 +2431,7 @@
         <v>0.0338</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.0219</v>
       </c>
       <c r="D44" t="n">
         <v>-0.4077</v>
@@ -2477,7 +2477,7 @@
         <v>-0.0238</v>
       </c>
       <c r="C45" t="n">
-        <v>-0</v>
+        <v>-0.0154</v>
       </c>
       <c r="D45" t="n">
         <v>-0.431</v>
@@ -2523,7 +2523,7 @@
         <v>-0.0328</v>
       </c>
       <c r="C46" t="n">
-        <v>-0</v>
+        <v>-0.0213</v>
       </c>
       <c r="D46" t="n">
         <v>-0.4346</v>
@@ -2569,7 +2569,7 @@
         <v>-0.0738</v>
       </c>
       <c r="C47" t="n">
-        <v>-0</v>
+        <v>-0.0479</v>
       </c>
       <c r="D47" t="n">
         <v>-0.4512</v>
@@ -2615,7 +2615,7 @@
         <v>-0.0798</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0518</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4536</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1038</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0673</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4633</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1591</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.1032</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4856</v>
@@ -2753,7 +2753,7 @@
         <v>-0.1899</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1232</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4981</v>
@@ -2799,7 +2799,7 @@
         <v>-0.2776</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.18</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5335</v>
@@ -2845,7 +2845,7 @@
         <v>-0.2788</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1808</v>
       </c>
       <c r="D53" t="n">
         <v>-0.534</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2862</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1856</v>
       </c>
       <c r="D54" t="n">
         <v>-0.537</v>
@@ -2937,7 +2937,7 @@
         <v>-0.3389</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.2198</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5583</v>
@@ -2983,7 +2983,7 @@
         <v>-0.3403</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.2207</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5588</v>
@@ -3029,7 +3029,7 @@
         <v>-0.3661</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2374</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5693</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3818</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2476</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5756</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5048</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.3274</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6253</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5866</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3804</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6583</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5875</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.381</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6587</v>
@@ -3259,7 +3259,7 @@
         <v>-0.5982</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3879</v>
       </c>
       <c r="D62" t="n">
         <v>-0.663</v>
@@ -3305,7 +3305,7 @@
         <v>-0.5982</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.3879</v>
       </c>
       <c r="D63" t="n">
         <v>-0.663</v>
@@ -3351,7 +3351,7 @@
         <v>-0.6145</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.3985</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6696</v>
@@ -3397,7 +3397,7 @@
         <v>-0.6724</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4361</v>
       </c>
       <c r="D65" t="n">
         <v>-0.6929999999999999</v>
@@ -3443,7 +3443,7 @@
         <v>-0.8011</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.5195</v>
       </c>
       <c r="D66" t="n">
         <v>-0.745</v>
@@ -3489,7 +3489,7 @@
         <v>-0.8756</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.5678</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7751</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9408</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6101</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8014</v>
@@ -3581,7 +3581,7 @@
         <v>-0.959</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6219</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8088</v>
@@ -3627,7 +3627,7 @@
         <v>-1</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.6485</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8253</v>
@@ -3673,7 +3673,7 @@
         <v>-1</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.6485</v>
       </c>
       <c r="D71" t="n">
         <v>-0.8253</v>
@@ -3719,7 +3719,7 @@
         <v>-1</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.6485</v>
       </c>
       <c r="D72" t="n">
         <v>-0.8253</v>
@@ -3765,7 +3765,7 @@
         <v>-1</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.6485</v>
       </c>
       <c r="D73" t="n">
         <v>-0.8253</v>
@@ -3811,7 +3811,7 @@
         <v>-1.0992</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.7128</v>
       </c>
       <c r="D74" t="n">
         <v>-0.8653999999999999</v>
@@ -3857,7 +3857,7 @@
         <v>-1.1387</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.7385</v>
       </c>
       <c r="D75" t="n">
         <v>-0.8814</v>
@@ -3903,7 +3903,7 @@
         <v>-1.1511</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="D76" t="n">
         <v>-0.8864</v>
@@ -3949,7 +3949,7 @@
         <v>-1.1722</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.7602</v>
       </c>
       <c r="D77" t="n">
         <v>-0.8949</v>
@@ -3995,7 +3995,7 @@
         <v>-1.1871</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.7698</v>
       </c>
       <c r="D78" t="n">
         <v>-0.9009</v>
@@ -4041,7 +4041,7 @@
         <v>-1.2489</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-0.8099</v>
       </c>
       <c r="D79" t="n">
         <v>-0.9258999999999999</v>
@@ -4087,7 +4087,7 @@
         <v>-1.7835</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.1566</v>
       </c>
       <c r="D80" t="n">
         <v>-1.1419</v>
@@ -4133,7 +4133,7 @@
         <v>-2.8959</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.878</v>
       </c>
       <c r="D81" t="n">
         <v>-1.5912</v>

--- a/database/event/8039/event_8039_evp_summary.xlsx
+++ b/database/event/8039/event_8039_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>5.3458</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9087</v>
+        <v>2.8402</v>
       </c>
       <c r="E2" t="n">
         <v>8.2433</v>
@@ -548,7 +548,7 @@
         <v>5.0646</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7336</v>
+        <v>2.6675</v>
       </c>
       <c r="E3" t="n">
         <v>7.8097</v>
@@ -594,7 +594,7 @@
         <v>3.5845</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8116</v>
+        <v>1.7582</v>
       </c>
       <c r="E4" t="n">
         <v>5.5274</v>
@@ -640,7 +640,7 @@
         <v>3.246</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6007</v>
+        <v>1.5502</v>
       </c>
       <c r="E5" t="n">
         <v>5.0054</v>
@@ -686,7 +686,7 @@
         <v>2.8848</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3757</v>
+        <v>1.3283</v>
       </c>
       <c r="E6" t="n">
         <v>4.4484</v>
@@ -732,7 +732,7 @@
         <v>2.441</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0993</v>
+        <v>1.0557</v>
       </c>
       <c r="E7" t="n">
         <v>3.7641</v>
@@ -778,7 +778,7 @@
         <v>2.2377</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9726</v>
+        <v>0.9308</v>
       </c>
       <c r="E8" t="n">
         <v>3.4506</v>
@@ -824,7 +824,7 @@
         <v>2.2068</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9533</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="E9" t="n">
         <v>3.4029</v>
@@ -870,7 +870,7 @@
         <v>2.0716</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8691</v>
+        <v>0.8287</v>
       </c>
       <c r="E10" t="n">
         <v>3.1944</v>
@@ -916,7 +916,7 @@
         <v>1.8713</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7443</v>
+        <v>0.7057</v>
       </c>
       <c r="E11" t="n">
         <v>2.8855</v>
@@ -962,7 +962,7 @@
         <v>1.8453</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7282</v>
+        <v>0.6897</v>
       </c>
       <c r="E12" t="n">
         <v>2.8455</v>
@@ -1008,7 +1008,7 @@
         <v>1.7626</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6766</v>
+        <v>0.6389</v>
       </c>
       <c r="E13" t="n">
         <v>2.7179</v>
@@ -1054,7 +1054,7 @@
         <v>1.3918</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4457</v>
+        <v>0.4111</v>
       </c>
       <c r="E14" t="n">
         <v>2.1462</v>
@@ -1100,7 +1100,7 @@
         <v>1.2943</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3849</v>
+        <v>0.3512</v>
       </c>
       <c r="E15" t="n">
         <v>1.9958</v>
@@ -1146,7 +1146,7 @@
         <v>1.1209</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2769</v>
+        <v>0.2447</v>
       </c>
       <c r="E16" t="n">
         <v>1.7285</v>
@@ -1192,7 +1192,7 @@
         <v>1.1051</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2671</v>
+        <v>0.235</v>
       </c>
       <c r="E17" t="n">
         <v>1.7041</v>
@@ -1238,7 +1238,7 @@
         <v>1.0095</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2075</v>
+        <v>0.1763</v>
       </c>
       <c r="E18" t="n">
         <v>1.5567</v>
@@ -1284,7 +1284,7 @@
         <v>0.9139</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1479</v>
+        <v>0.1175</v>
       </c>
       <c r="E19" t="n">
         <v>1.4092</v>
@@ -1330,7 +1330,7 @@
         <v>0.8882</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1319</v>
+        <v>0.1017</v>
       </c>
       <c r="E20" t="n">
         <v>1.3696</v>
@@ -1376,7 +1376,7 @@
         <v>0.8196</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0892</v>
+        <v>0.0596</v>
       </c>
       <c r="E21" t="n">
         <v>1.2638</v>
@@ -1422,7 +1422,7 @@
         <v>0.8165</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0872</v>
+        <v>0.0577</v>
       </c>
       <c r="E22" t="n">
         <v>1.259</v>
@@ -1468,7 +1468,7 @@
         <v>0.731</v>
       </c>
       <c r="D23" t="n">
-        <v>0.034</v>
+        <v>0.0052</v>
       </c>
       <c r="E23" t="n">
         <v>1.1272</v>
@@ -1514,7 +1514,7 @@
         <v>0.7128</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0227</v>
+        <v>-0.006</v>
       </c>
       <c r="E24" t="n">
         <v>1.0992</v>
@@ -1560,7 +1560,7 @@
         <v>0.7003</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0149</v>
+        <v>-0.0137</v>
       </c>
       <c r="E25" t="n">
         <v>1.0799</v>
@@ -1606,7 +1606,7 @@
         <v>0.6805</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0026</v>
+        <v>-0.0258</v>
       </c>
       <c r="E26" t="n">
         <v>1.0494</v>
@@ -1652,7 +1652,7 @@
         <v>0.5951</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0506</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E27" t="n">
         <v>0.9177</v>
@@ -1698,7 +1698,7 @@
         <v>0.593</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.052</v>
+        <v>-0.0796</v>
       </c>
       <c r="E28" t="n">
         <v>0.9144</v>
@@ -1744,7 +1744,7 @@
         <v>0.5358000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0876</v>
+        <v>-0.1148</v>
       </c>
       <c r="E29" t="n">
         <v>0.8262</v>
@@ -1790,7 +1790,7 @@
         <v>0.4868</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1181</v>
+        <v>-0.1448</v>
       </c>
       <c r="E30" t="n">
         <v>0.7507</v>
@@ -1836,7 +1836,7 @@
         <v>0.4612</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1341</v>
+        <v>-0.1606</v>
       </c>
       <c r="E31" t="n">
         <v>0.7112000000000001</v>
@@ -1882,7 +1882,7 @@
         <v>0.4573</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1365</v>
+        <v>-0.163</v>
       </c>
       <c r="E32" t="n">
         <v>0.7050999999999999</v>
@@ -1928,7 +1928,7 @@
         <v>0.438</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1485</v>
+        <v>-0.1748</v>
       </c>
       <c r="E33" t="n">
         <v>0.6754</v>
@@ -1974,7 +1974,7 @@
         <v>0.4041</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1696</v>
+        <v>-0.1957</v>
       </c>
       <c r="E34" t="n">
         <v>0.6231</v>
@@ -2020,7 +2020,7 @@
         <v>0.3802</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1846</v>
+        <v>-0.2104</v>
       </c>
       <c r="E35" t="n">
         <v>0.5862000000000001</v>
@@ -2066,7 +2066,7 @@
         <v>0.3466</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2054</v>
+        <v>-0.231</v>
       </c>
       <c r="E36" t="n">
         <v>0.5345</v>
@@ -2112,7 +2112,7 @@
         <v>0.2984</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2355</v>
+        <v>-0.2606</v>
       </c>
       <c r="E37" t="n">
         <v>0.4601</v>
@@ -2158,7 +2158,7 @@
         <v>0.2984</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2355</v>
+        <v>-0.2606</v>
       </c>
       <c r="E38" t="n">
         <v>0.4601</v>
@@ -2204,7 +2204,7 @@
         <v>0.2913</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2399</v>
+        <v>-0.2649</v>
       </c>
       <c r="E39" t="n">
         <v>0.4492</v>
@@ -2250,7 +2250,7 @@
         <v>0.2396</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2721</v>
+        <v>-0.2967</v>
       </c>
       <c r="E40" t="n">
         <v>0.3694</v>
@@ -2296,7 +2296,7 @@
         <v>0.1621</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3204</v>
+        <v>-0.3443</v>
       </c>
       <c r="E41" t="n">
         <v>0.25</v>
@@ -2342,7 +2342,7 @@
         <v>0.099</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3597</v>
+        <v>-0.3831</v>
       </c>
       <c r="E42" t="n">
         <v>0.1527</v>
@@ -2388,7 +2388,7 @@
         <v>0.0565</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3861</v>
+        <v>-0.4092</v>
       </c>
       <c r="E43" t="n">
         <v>0.0872</v>
@@ -2434,7 +2434,7 @@
         <v>0.0219</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4077</v>
+        <v>-0.4304</v>
       </c>
       <c r="E44" t="n">
         <v>0.0338</v>
@@ -2480,7 +2480,7 @@
         <v>-0.0154</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.431</v>
+        <v>-0.4534</v>
       </c>
       <c r="E45" t="n">
         <v>-0.0238</v>
@@ -2526,7 +2526,7 @@
         <v>-0.0213</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4346</v>
+        <v>-0.457</v>
       </c>
       <c r="E46" t="n">
         <v>-0.0328</v>
@@ -2572,7 +2572,7 @@
         <v>-0.0479</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4512</v>
+        <v>-0.4733</v>
       </c>
       <c r="E47" t="n">
         <v>-0.0738</v>
@@ -2618,7 +2618,7 @@
         <v>-0.0518</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4536</v>
+        <v>-0.4757</v>
       </c>
       <c r="E48" t="n">
         <v>-0.0798</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0673</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4633</v>
+        <v>-0.4853</v>
       </c>
       <c r="E49" t="n">
         <v>-0.1038</v>
@@ -2710,7 +2710,7 @@
         <v>-0.1032</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4856</v>
+        <v>-0.5073</v>
       </c>
       <c r="E50" t="n">
         <v>-0.1591</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1232</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4981</v>
+        <v>-0.5196</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1899</v>
@@ -2802,7 +2802,7 @@
         <v>-0.18</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5335</v>
+        <v>-0.5545</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2776</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1808</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.534</v>
+        <v>-0.555</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2788</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1856</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.537</v>
+        <v>-0.5579</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2862</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2198</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5583</v>
+        <v>-0.5789</v>
       </c>
       <c r="E55" t="n">
         <v>-0.3389</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2207</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5588</v>
+        <v>-0.5795</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3403</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2374</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5693</v>
+        <v>-0.5898</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3661</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2476</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5756</v>
+        <v>-0.596</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3818</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3274</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6253</v>
+        <v>-0.645</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5048</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3804</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6583</v>
+        <v>-0.6776</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5866</v>
@@ -3216,7 +3216,7 @@
         <v>-0.381</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6587</v>
+        <v>-0.678</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5875</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3879</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.663</v>
+        <v>-0.6822</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5982</v>
@@ -3308,7 +3308,7 @@
         <v>-0.3879</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.663</v>
+        <v>-0.6822</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5982</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3985</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6696</v>
+        <v>-0.6887</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6145</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4361</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.7118</v>
       </c>
       <c r="E65" t="n">
         <v>-0.6724</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5195</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.745</v>
+        <v>-0.7631</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8011</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5678</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7751</v>
+        <v>-0.7927</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8756</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6101</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8014</v>
+        <v>-0.8187</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9408</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6219</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8088</v>
+        <v>-0.826</v>
       </c>
       <c r="E69" t="n">
         <v>-0.959</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6485</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E70" t="n">
         <v>-1</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6485</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E71" t="n">
         <v>-1</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6485</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E72" t="n">
         <v>-1</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6485</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E73" t="n">
         <v>-1</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7128</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.8818</v>
       </c>
       <c r="E74" t="n">
         <v>-1.0992</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7385</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8814</v>
+        <v>-0.8976</v>
       </c>
       <c r="E75" t="n">
         <v>-1.1387</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7465000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.8864</v>
+        <v>-0.9025</v>
       </c>
       <c r="E76" t="n">
         <v>-1.1511</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7602</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.8949</v>
+        <v>-0.9109</v>
       </c>
       <c r="E77" t="n">
         <v>-1.1722</v>
@@ -3998,7 +3998,7 @@
         <v>-0.7698</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9009</v>
+        <v>-0.9169</v>
       </c>
       <c r="E78" t="n">
         <v>-1.1871</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8099</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.9415</v>
       </c>
       <c r="E79" t="n">
         <v>-1.2489</v>
@@ -4090,7 +4090,7 @@
         <v>-1.1566</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1419</v>
+        <v>-1.1545</v>
       </c>
       <c r="E80" t="n">
         <v>-1.7835</v>
@@ -4136,7 +4136,7 @@
         <v>-1.878</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5912</v>
+        <v>-1.5976</v>
       </c>
       <c r="E81" t="n">
         <v>-2.8959</v>

--- a/database/event/8039/event_8039_evp_summary.xlsx
+++ b/database/event/8039/event_8039_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.2433</v>
+        <v>7.9923</v>
       </c>
       <c r="C2" t="n">
-        <v>5.3458</v>
+        <v>5.183</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8402</v>
+        <v>2.9701</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2433</v>
+        <v>7.9923</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7325</v>
+        <v>2.1633</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5108</v>
+        <v>5.829</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7325</v>
+        <v>2.1633</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7325</v>
+        <v>2.1633</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7567</v>
+        <v>5.829</v>
       </c>
       <c r="K2" t="n">
         <v>36</v>
@@ -529,7 +529,7 @@
         <v>197</v>
       </c>
       <c r="M2" t="n">
-        <v>8.4892</v>
+        <v>7.9923</v>
       </c>
       <c r="N2" t="n">
         <v>233</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8097</v>
+        <v>7.3197</v>
       </c>
       <c r="C3" t="n">
-        <v>5.0646</v>
+        <v>4.7468</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6675</v>
+        <v>2.6665</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8097</v>
+        <v>7.3197</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7056</v>
+        <v>1.9744</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1041</v>
+        <v>5.3453</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7056</v>
+        <v>1.9744</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7056</v>
+        <v>1.9744</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1041</v>
+        <v>5.3453</v>
       </c>
       <c r="K3" t="n">
         <v>55</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>7.809699999999999</v>
+        <v>7.3197</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5274</v>
+        <v>5.902</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5845</v>
+        <v>3.8275</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7582</v>
+        <v>2.0264</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5274</v>
+        <v>5.902</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7634</v>
+        <v>2.7516</v>
       </c>
       <c r="G4" t="n">
-        <v>3.764</v>
+        <v>3.1504</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7634</v>
+        <v>2.7516</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7634</v>
+        <v>2.7516</v>
       </c>
       <c r="J4" t="n">
-        <v>3.764</v>
+        <v>3.1504</v>
       </c>
       <c r="K4" t="n">
         <v>36</v>
@@ -621,7 +621,7 @@
         <v>197</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5274</v>
+        <v>5.901999999999999</v>
       </c>
       <c r="N4" t="n">
         <v>233</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0054</v>
+        <v>5.3634</v>
       </c>
       <c r="C5" t="n">
-        <v>3.246</v>
+        <v>3.4782</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5502</v>
+        <v>1.7833</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0054</v>
+        <v>5.3634</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4866</v>
+        <v>2.049</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5189</v>
+        <v>3.3144</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4866</v>
+        <v>2.049</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4866</v>
+        <v>2.049</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5189</v>
+        <v>3.3144</v>
       </c>
       <c r="K5" t="n">
         <v>113</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0055</v>
+        <v>5.3634</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4484</v>
+        <v>4.1753</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8848</v>
+        <v>2.7077</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3283</v>
+        <v>1.2469</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4484</v>
+        <v>4.1753</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3789</v>
+        <v>3.2512</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8273</v>
+        <v>0.9241</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3789</v>
+        <v>3.7792</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3789</v>
+        <v>3.7792</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8273</v>
+        <v>0.9241</v>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="L6" t="n">
-        <v>197</v>
+        <v>109</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4484</v>
+        <v>4.7033</v>
       </c>
       <c r="N6" t="n">
-        <v>233</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7641</v>
+        <v>3.9271</v>
       </c>
       <c r="C7" t="n">
-        <v>2.441</v>
+        <v>2.5467</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0557</v>
+        <v>1.1349</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7641</v>
+        <v>3.9271</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6757</v>
+        <v>-0.2113</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0884</v>
+        <v>4.1384</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6757</v>
+        <v>-0.2113</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6757</v>
+        <v>-0.2113</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0884</v>
+        <v>4.1384</v>
       </c>
       <c r="K7" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L7" t="n">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7641</v>
+        <v>3.9271</v>
       </c>
       <c r="N7" t="n">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4506</v>
+        <v>3.7659</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2377</v>
+        <v>2.4422</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9308</v>
+        <v>1.0621</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4506</v>
+        <v>3.7659</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4615</v>
+        <v>3.0723</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9891</v>
+        <v>0.6936</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4615</v>
+        <v>3.3866</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4615</v>
+        <v>3.3866</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9891</v>
+        <v>0.6936</v>
       </c>
       <c r="K8" t="n">
         <v>96</v>
@@ -805,7 +805,7 @@
         <v>109</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4506</v>
+        <v>4.0802</v>
       </c>
       <c r="N8" t="n">
         <v>205</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4029</v>
+        <v>3.4405</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2068</v>
+        <v>2.2312</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9152</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4029</v>
+        <v>3.4405</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6363</v>
+        <v>1.6847</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.7558</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6363</v>
+        <v>1.6847</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6363</v>
+        <v>1.6847</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.7558</v>
       </c>
       <c r="K9" t="n">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="L9" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4029</v>
+        <v>3.4405</v>
       </c>
       <c r="N9" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1944</v>
+        <v>3.4327</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0716</v>
+        <v>2.2261</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8287</v>
+        <v>0.9117</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1944</v>
+        <v>3.4327</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5748</v>
+        <v>1.6244</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6196</v>
+        <v>1.8083</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5748</v>
+        <v>1.6244</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5748</v>
+        <v>1.6244</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6196</v>
+        <v>1.8083</v>
       </c>
       <c r="K10" t="n">
         <v>55</v>
@@ -897,7 +897,7 @@
         <v>156</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1944</v>
+        <v>3.4327</v>
       </c>
       <c r="N10" t="n">
         <v>211</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8855</v>
+        <v>3.0867</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8713</v>
+        <v>2.0017</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7057</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8855</v>
+        <v>3.0867</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3716</v>
+        <v>1.627</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5139</v>
+        <v>1.4597</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3716</v>
+        <v>1.627</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3716</v>
+        <v>1.627</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5139</v>
+        <v>1.4597</v>
       </c>
       <c r="K11" t="n">
         <v>113</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8855</v>
+        <v>3.0867</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8455</v>
+        <v>2.8776</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8453</v>
+        <v>1.8661</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6897</v>
+        <v>0.6611</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8455</v>
+        <v>2.8776</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5088</v>
+        <v>1.8946</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3367</v>
+        <v>0.983</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5088</v>
+        <v>1.8946</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5088</v>
+        <v>1.8946</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3367</v>
+        <v>0.983</v>
       </c>
       <c r="K12" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L12" t="n">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8455</v>
+        <v>2.8776</v>
       </c>
       <c r="N12" t="n">
-        <v>205</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7179</v>
+        <v>2.6481</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7626</v>
+        <v>1.7173</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6389</v>
+        <v>0.5575</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7179</v>
+        <v>2.6481</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7086</v>
+        <v>1.6343</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0093</v>
+        <v>1.0138</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7086</v>
+        <v>1.6343</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7086</v>
+        <v>1.6343</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0093</v>
+        <v>1.0138</v>
       </c>
       <c r="K13" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7179</v>
+        <v>2.6481</v>
       </c>
       <c r="N13" t="n">
-        <v>108</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1462</v>
+        <v>2.3318</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3918</v>
+        <v>1.5122</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4111</v>
+        <v>0.4147</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1462</v>
+        <v>2.3318</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6186</v>
+        <v>1.7137</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5276</v>
+        <v>0.6181</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6186</v>
+        <v>1.7137</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6186</v>
+        <v>1.7137</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5276</v>
+        <v>0.6181</v>
       </c>
       <c r="K14" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         <v>66</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1462</v>
+        <v>2.3318</v>
       </c>
       <c r="N14" t="n">
         <v>125</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9958</v>
+        <v>2.2915</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2943</v>
+        <v>1.486</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3512</v>
+        <v>0.3965</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9958</v>
+        <v>2.2915</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5179</v>
+        <v>1.6069</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4779</v>
+        <v>0.6846</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5179</v>
+        <v>1.6069</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5179</v>
+        <v>1.6069</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4779</v>
+        <v>0.6846</v>
       </c>
       <c r="K15" t="n">
         <v>36</v>
@@ -1127,7 +1127,7 @@
         <v>197</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9958</v>
+        <v>2.2915</v>
       </c>
       <c r="N15" t="n">
         <v>233</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7285</v>
+        <v>2.1789</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1209</v>
+        <v>1.413</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2447</v>
+        <v>0.3457</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7285</v>
+        <v>2.1789</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7285</v>
+        <v>2.1789</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7285</v>
+        <v>2.1789</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7285</v>
+        <v>2.1789</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7285</v>
+        <v>2.1789</v>
       </c>
       <c r="N16" t="n">
         <v>64</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7041</v>
+        <v>2.1077</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1051</v>
+        <v>1.3668</v>
       </c>
       <c r="D17" t="n">
-        <v>0.235</v>
+        <v>0.3135</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7041</v>
+        <v>2.1077</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7041</v>
+        <v>2.1471</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.0394</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7041</v>
+        <v>2.1471</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7041</v>
+        <v>2.1471</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.0394</v>
       </c>
       <c r="K17" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7041</v>
+        <v>2.1077</v>
       </c>
       <c r="N17" t="n">
-        <v>55</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5567</v>
+        <v>1.9152</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0095</v>
+        <v>1.242</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1763</v>
+        <v>0.2266</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5567</v>
+        <v>1.9152</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7413</v>
+        <v>1.9152</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1846</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7413</v>
+        <v>1.9152</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7413</v>
+        <v>1.9152</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1846</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5567</v>
+        <v>1.9152</v>
       </c>
       <c r="N18" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4092</v>
+        <v>1.6586</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9139</v>
+        <v>1.0756</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1175</v>
+        <v>0.1108</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4092</v>
+        <v>1.6586</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0356</v>
+        <v>2.0891</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3736</v>
+        <v>-0.4305</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0356</v>
+        <v>2.0891</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0356</v>
+        <v>2.0891</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3736</v>
+        <v>-0.4305</v>
       </c>
       <c r="K19" t="n">
         <v>64</v>
       </c>
       <c r="L19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4092</v>
+        <v>1.6586</v>
       </c>
       <c r="N19" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3696</v>
+        <v>1.6075</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8882</v>
+        <v>1.0425</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1017</v>
+        <v>0.0877</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3696</v>
+        <v>1.6075</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1778</v>
+        <v>2.0368</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1918</v>
+        <v>-0.4293</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1778</v>
+        <v>2.0368</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1778</v>
+        <v>2.0368</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1918</v>
+        <v>-0.4293</v>
       </c>
       <c r="K20" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L20" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3696</v>
+        <v>1.6075</v>
       </c>
       <c r="N20" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2638</v>
+        <v>1.5776</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8196</v>
+        <v>1.0231</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0596</v>
+        <v>0.0742</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2638</v>
+        <v>1.5776</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2638</v>
+        <v>1.5776</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2638</v>
+        <v>1.5776</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2638</v>
+        <v>1.5776</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2638</v>
+        <v>1.5776</v>
       </c>
       <c r="N21" t="n">
         <v>69</v>
@@ -1412,308 +1412,308 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.259</v>
+        <v>1.4505</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8165</v>
+        <v>0.9407</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0577</v>
+        <v>0.0168</v>
       </c>
       <c r="E22" t="n">
-        <v>1.259</v>
+        <v>1.4505</v>
       </c>
       <c r="F22" t="n">
-        <v>1.259</v>
+        <v>1.1006</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.3499</v>
       </c>
       <c r="H22" t="n">
-        <v>1.259</v>
+        <v>1.1006</v>
       </c>
       <c r="I22" t="n">
-        <v>1.259</v>
+        <v>1.1006</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.3499</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.259</v>
+        <v>1.4505</v>
       </c>
       <c r="N22" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1272</v>
+        <v>1.4366</v>
       </c>
       <c r="C23" t="n">
-        <v>0.731</v>
+        <v>0.9316</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1272</v>
+        <v>1.4366</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7328</v>
+        <v>1.4366</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6056</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7328</v>
+        <v>1.4366</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7328</v>
+        <v>1.4366</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6056</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1272</v>
+        <v>1.4366</v>
       </c>
       <c r="N23" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0992</v>
+        <v>1.2676</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7128</v>
+        <v>0.822</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.006</v>
+        <v>-0.0658</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0992</v>
+        <v>1.2676</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0992</v>
+        <v>1.1366</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0992</v>
+        <v>1.1366</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0992</v>
+        <v>1.1366</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="K24" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0992</v>
+        <v>1.2676</v>
       </c>
       <c r="N24" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0799</v>
+        <v>1.2196</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7003</v>
+        <v>0.7909</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0137</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0799</v>
+        <v>1.2196</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7488</v>
+        <v>1.2196</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6689000000000001</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7488</v>
+        <v>1.2196</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7488</v>
+        <v>1.2196</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6689000000000001</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>64</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0799</v>
+        <v>1.2196</v>
       </c>
       <c r="N25" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.0494</v>
+        <v>1.2086</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6805</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0258</v>
+        <v>-0.0924</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0494</v>
+        <v>1.2086</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0494</v>
+        <v>0.5896</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.6191</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0494</v>
+        <v>0.5896</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0494</v>
+        <v>0.5896</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.6191</v>
       </c>
       <c r="K26" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0494</v>
+        <v>1.2087</v>
       </c>
       <c r="N26" t="n">
-        <v>59</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9177</v>
+        <v>1.1943</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5951</v>
+        <v>0.7745</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0988</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9177</v>
+        <v>1.1943</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1926</v>
+        <v>1.1943</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7251</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1926</v>
+        <v>1.1943</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1926</v>
+        <v>1.1943</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7251</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9177</v>
+        <v>1.1943</v>
       </c>
       <c r="N27" t="n">
-        <v>205</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9144</v>
+        <v>0.9823</v>
       </c>
       <c r="C28" t="n">
-        <v>0.593</v>
+        <v>0.637</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0796</v>
+        <v>-0.1946</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9144</v>
+        <v>0.9823</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9144</v>
+        <v>0.9823</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9144</v>
+        <v>0.9823</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9144</v>
+        <v>0.9823</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9144</v>
+        <v>0.9823</v>
       </c>
       <c r="N28" t="n">
         <v>64</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8262</v>
+        <v>0.9418</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.6108</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1148</v>
+        <v>-0.2128</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8262</v>
+        <v>0.9418</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8262</v>
+        <v>0.9418</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8262</v>
+        <v>0.9418</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8262</v>
+        <v>0.9418</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8262</v>
+        <v>0.9418</v>
       </c>
       <c r="N29" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7507</v>
+        <v>0.9301</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4868</v>
+        <v>0.6032</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1448</v>
+        <v>-0.2181</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7507</v>
+        <v>0.9301</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7507</v>
+        <v>0.9301</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7507</v>
+        <v>0.9301</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7507</v>
+        <v>0.9301</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7507</v>
+        <v>0.9301</v>
       </c>
       <c r="N30" t="n">
         <v>64</v>
@@ -1826,139 +1826,139 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.924</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4612</v>
+        <v>0.5992</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1606</v>
+        <v>-0.2209</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.924</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.2684</v>
+        <v>0.924</v>
       </c>
       <c r="G31" t="n">
-        <v>1.9796</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.2684</v>
+        <v>0.924</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.2684</v>
+        <v>0.924</v>
       </c>
       <c r="J31" t="n">
-        <v>1.9796</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L31" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.924</v>
       </c>
       <c r="N31" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.8592</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4573</v>
+        <v>0.5572</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.163</v>
+        <v>-0.2501</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.8592</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8592</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0565</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8592</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8592</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0565</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="L32" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7051000000000001</v>
+        <v>0.8592</v>
       </c>
       <c r="N32" t="n">
-        <v>233</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6754</v>
+        <v>0.8292</v>
       </c>
       <c r="C33" t="n">
-        <v>0.438</v>
+        <v>0.5377</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1748</v>
+        <v>-0.2637</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6754</v>
+        <v>0.8292</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6754</v>
+        <v>0.477</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.3522</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6754</v>
+        <v>0.477</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6754</v>
+        <v>0.477</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.3522</v>
       </c>
       <c r="K33" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6754</v>
+        <v>0.8291999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>59</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6231</v>
+        <v>0.7879</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4041</v>
+        <v>0.511</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1957</v>
+        <v>-0.2823</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6231</v>
+        <v>0.7879</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6231</v>
+        <v>0.7879</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6231</v>
+        <v>0.7879</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6231</v>
+        <v>0.7879</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6231</v>
+        <v>0.7879</v>
       </c>
       <c r="N34" t="n">
         <v>59</v>
@@ -2010,814 +2010,814 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.7144</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3802</v>
+        <v>0.4633</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2104</v>
+        <v>-0.3155</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.7144</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5756</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.1388</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5756</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5756</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.1388</v>
       </c>
       <c r="K35" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.7144</v>
       </c>
       <c r="N35" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5345</v>
+        <v>0.7069</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3466</v>
+        <v>0.4584</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.231</v>
+        <v>-0.3189</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5345</v>
+        <v>0.7069</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5345</v>
+        <v>0.7069</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5345</v>
+        <v>0.7069</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5345</v>
+        <v>0.7069</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5345</v>
+        <v>0.7069</v>
       </c>
       <c r="N36" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4601</v>
+        <v>0.6604</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2984</v>
+        <v>0.4283</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2606</v>
+        <v>-0.3399</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4601</v>
+        <v>0.6604</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4601</v>
+        <v>0.6604</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4601</v>
+        <v>0.6604</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4601</v>
+        <v>0.6604</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4601</v>
+        <v>0.6604</v>
       </c>
       <c r="N37" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4601</v>
+        <v>0.5772</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2984</v>
+        <v>0.3743</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2606</v>
+        <v>-0.3774</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4601</v>
+        <v>0.5772</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4601</v>
+        <v>0.5772</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4601</v>
+        <v>0.5772</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4601</v>
+        <v>0.5772</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4601</v>
+        <v>0.5772</v>
       </c>
       <c r="N38" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4492</v>
+        <v>0.5235</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2913</v>
+        <v>0.3395</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2649</v>
+        <v>-0.4017</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4492</v>
+        <v>0.5235</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5251</v>
+        <v>0.5235</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0759</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5251</v>
+        <v>0.5235</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5251</v>
+        <v>0.5235</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.0759</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L39" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4492</v>
+        <v>0.5235</v>
       </c>
       <c r="N39" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3694</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2396</v>
+        <v>0.3357</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2967</v>
+        <v>-0.4043</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3694</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3694</v>
+        <v>-1.1062</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1.6238</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3694</v>
+        <v>-1.1062</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3694</v>
+        <v>-1.1062</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1.6238</v>
       </c>
       <c r="K40" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3694</v>
+        <v>0.5175999999999998</v>
       </c>
       <c r="N40" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.25</v>
+        <v>0.4732</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1621</v>
+        <v>0.3069</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3443</v>
+        <v>-0.4244</v>
       </c>
       <c r="E41" t="n">
-        <v>0.25</v>
+        <v>0.4732</v>
       </c>
       <c r="F41" t="n">
-        <v>0.25</v>
+        <v>0.4732</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.25</v>
+        <v>0.4732</v>
       </c>
       <c r="I41" t="n">
-        <v>0.25</v>
+        <v>0.4732</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.25</v>
+        <v>0.4732</v>
       </c>
       <c r="N41" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1527</v>
+        <v>0.4703</v>
       </c>
       <c r="C42" t="n">
-        <v>0.099</v>
+        <v>0.305</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3831</v>
+        <v>-0.4257</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1527</v>
+        <v>0.4703</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1527</v>
+        <v>0.4703</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1527</v>
+        <v>0.4703</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1527</v>
+        <v>0.4703</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1527</v>
+        <v>0.4703</v>
       </c>
       <c r="N42" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0872</v>
+        <v>0.3319</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0565</v>
+        <v>0.2152</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4092</v>
+        <v>-0.4882</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0872</v>
+        <v>0.3319</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.6954</v>
+        <v>0.3319</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7826</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.6954</v>
+        <v>0.3319</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6954</v>
+        <v>0.3319</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7826</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="L43" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.08719999999999994</v>
+        <v>0.3319</v>
       </c>
       <c r="N43" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0338</v>
+        <v>0.3192</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0219</v>
+        <v>0.207</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4304</v>
+        <v>-0.4939</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0338</v>
+        <v>0.3192</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0338</v>
+        <v>-0.6121</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.9313</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0338</v>
+        <v>-0.6121</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0338</v>
+        <v>-0.6121</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.9313</v>
       </c>
       <c r="K44" t="n">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0338</v>
+        <v>0.3192</v>
       </c>
       <c r="N44" t="n">
-        <v>55</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.0238</v>
+        <v>0.2003</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0154</v>
+        <v>0.1299</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4534</v>
+        <v>-0.5476</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0238</v>
+        <v>0.2003</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.0238</v>
+        <v>0.2003</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.0238</v>
+        <v>0.2003</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0238</v>
+        <v>0.2003</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0238</v>
+        <v>0.2003</v>
       </c>
       <c r="N45" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0328</v>
+        <v>0.1681</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0213</v>
+        <v>0.109</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.457</v>
+        <v>-0.5621</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0328</v>
+        <v>0.1681</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0328</v>
+        <v>0.1681</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0328</v>
+        <v>0.1681</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0328</v>
+        <v>0.1681</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0328</v>
+        <v>0.1681</v>
       </c>
       <c r="N46" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0738</v>
+        <v>0.0788</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0479</v>
+        <v>0.0511</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4733</v>
+        <v>-0.6024</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0738</v>
+        <v>0.0788</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0738</v>
+        <v>0.0788</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0738</v>
+        <v>0.0788</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0738</v>
+        <v>0.0788</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0738</v>
+        <v>0.0788</v>
       </c>
       <c r="N47" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0798</v>
+        <v>0.0549</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0518</v>
+        <v>0.0356</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4757</v>
+        <v>-0.6132</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0798</v>
+        <v>0.0549</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.5836</v>
+        <v>0.0549</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5038</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.5836</v>
+        <v>0.0549</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5836</v>
+        <v>0.0549</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5038</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="L48" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.07979999999999998</v>
+        <v>0.0549</v>
       </c>
       <c r="N48" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1038</v>
+        <v>0.0184</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0673</v>
+        <v>0.0119</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4853</v>
+        <v>-0.6297</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1038</v>
+        <v>0.0184</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.7716</v>
+        <v>0.0184</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6677999999999999</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.7716</v>
+        <v>0.0184</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7716</v>
+        <v>0.0184</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6677999999999999</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="L49" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1038</v>
+        <v>0.0184</v>
       </c>
       <c r="N49" t="n">
-        <v>214</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1591</v>
+        <v>0.0177</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1032</v>
+        <v>0.0115</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5073</v>
+        <v>-0.63</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1591</v>
+        <v>0.0177</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1591</v>
+        <v>-0.5684</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.5861</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1591</v>
+        <v>-0.5684</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1591</v>
+        <v>-0.5684</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.5861</v>
       </c>
       <c r="K50" t="n">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1591</v>
+        <v>0.01769999999999994</v>
       </c>
       <c r="N50" t="n">
-        <v>42</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1899</v>
+        <v>-0.0581</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1232</v>
+        <v>-0.0377</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5196</v>
+        <v>-0.6642</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1899</v>
+        <v>-0.0581</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1899</v>
+        <v>-0.0581</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1899</v>
+        <v>-0.0581</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1899</v>
+        <v>-0.0581</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1899</v>
+        <v>-0.0581</v>
       </c>
       <c r="N51" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2776</v>
+        <v>-0.0781</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.18</v>
+        <v>-0.0506</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5545</v>
+        <v>-0.6733</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2776</v>
+        <v>-0.0781</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2776</v>
+        <v>-0.0781</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2776</v>
+        <v>-0.0781</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2776</v>
+        <v>-0.0781</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2776</v>
+        <v>-0.0781</v>
       </c>
       <c r="N52" t="n">
         <v>59</v>
@@ -2838,219 +2838,219 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2788</v>
+        <v>-0.1164</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1808</v>
+        <v>-0.0755</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.555</v>
+        <v>-0.6906</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2788</v>
+        <v>-0.1164</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3763</v>
+        <v>-0.1164</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.6551</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3763</v>
+        <v>-0.1164</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3763</v>
+        <v>-0.1164</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.6551</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2788</v>
+        <v>-0.1164</v>
       </c>
       <c r="N53" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2862</v>
+        <v>-0.1269</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1856</v>
+        <v>-0.0823</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5579</v>
+        <v>-0.6953</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2862</v>
+        <v>-0.1269</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2862</v>
+        <v>0.2691</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.396</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2862</v>
+        <v>0.2691</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2862</v>
+        <v>0.2691</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.396</v>
       </c>
       <c r="K54" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2862</v>
+        <v>-0.1269</v>
       </c>
       <c r="N54" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3389</v>
+        <v>-0.1297</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2198</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5789</v>
+        <v>-0.6966</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3389</v>
+        <v>-0.1297</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3389</v>
+        <v>-0.1297</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3389</v>
+        <v>-0.1297</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3389</v>
+        <v>-0.1297</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3389</v>
+        <v>-0.1297</v>
       </c>
       <c r="N55" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3403</v>
+        <v>-0.1457</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2207</v>
+        <v>-0.0945</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5795</v>
+        <v>-0.7038</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3403</v>
+        <v>-0.1457</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3403</v>
+        <v>-0.1457</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3403</v>
+        <v>-0.1457</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3403</v>
+        <v>-0.1457</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3403</v>
+        <v>-0.1457</v>
       </c>
       <c r="N56" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3661</v>
+        <v>-0.163</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2374</v>
+        <v>-0.1057</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5898</v>
+        <v>-0.7116</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3661</v>
+        <v>-0.163</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6339</v>
+        <v>0.4778</v>
       </c>
       <c r="G57" t="n">
-        <v>-1</v>
+        <v>-0.6408</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6339</v>
+        <v>0.4778</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6339</v>
+        <v>0.4778</v>
       </c>
       <c r="J57" t="n">
-        <v>-1</v>
+        <v>-0.6408</v>
       </c>
       <c r="K57" t="n">
         <v>69</v>
@@ -3059,7 +3059,7 @@
         <v>65</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3661</v>
+        <v>-0.163</v>
       </c>
       <c r="N57" t="n">
         <v>134</v>
@@ -3068,277 +3068,277 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3818</v>
+        <v>-0.2077</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2476</v>
+        <v>-0.1347</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.596</v>
+        <v>-0.7318</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3818</v>
+        <v>-0.2077</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3818</v>
+        <v>-0.2077</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3818</v>
+        <v>-0.2077</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3818</v>
+        <v>-0.2077</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3818</v>
+        <v>-0.2077</v>
       </c>
       <c r="N58" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5048</v>
+        <v>-0.2184</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3274</v>
+        <v>-0.1416</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.645</v>
+        <v>-0.7366</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5048</v>
+        <v>-0.2184</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5048</v>
+        <v>-0.2184</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5048</v>
+        <v>-0.2184</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5048</v>
+        <v>-0.2184</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5048</v>
+        <v>-0.2184</v>
       </c>
       <c r="N59" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5866</v>
+        <v>-0.2525</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3804</v>
+        <v>-0.1637</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6776</v>
+        <v>-0.752</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5866</v>
+        <v>-0.2525</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5866</v>
+        <v>-0.4583</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.2058</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5866</v>
+        <v>-0.4583</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5866</v>
+        <v>-0.4583</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>0.2058</v>
       </c>
       <c r="K60" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5866</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5875</v>
+        <v>-0.2827</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.381</v>
+        <v>-0.1833</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.678</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5875</v>
+        <v>-0.2827</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5875</v>
+        <v>-0.2827</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5875</v>
+        <v>-0.2827</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5875</v>
+        <v>-0.2827</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5875</v>
+        <v>-0.2827</v>
       </c>
       <c r="N61" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5982</v>
+        <v>-0.3007</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3879</v>
+        <v>-0.195</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6822</v>
+        <v>-0.7738</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5982</v>
+        <v>-0.3007</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5982</v>
+        <v>-0.6232</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.3225</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5982</v>
+        <v>-0.6232</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5982</v>
+        <v>-0.6232</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>0.3225</v>
       </c>
       <c r="K62" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5982</v>
+        <v>-0.3007</v>
       </c>
       <c r="N62" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5982</v>
+        <v>-0.3254</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3879</v>
+        <v>-0.211</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6822</v>
+        <v>-0.7849</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5982</v>
+        <v>-0.3254</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6329</v>
+        <v>-0.3254</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0347</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6329</v>
+        <v>-0.3254</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6329</v>
+        <v>-0.3254</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0347</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L63" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.5982000000000001</v>
+        <v>-0.3254</v>
       </c>
       <c r="N63" t="n">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6145</v>
+        <v>-0.3364</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3985</v>
+        <v>-0.2182</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6887</v>
+        <v>-0.7899</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6145</v>
+        <v>-0.3364</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6145</v>
+        <v>-0.3364</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6145</v>
+        <v>-0.3364</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6145</v>
+        <v>-0.3364</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6145</v>
+        <v>-0.3364</v>
       </c>
       <c r="N64" t="n">
         <v>64</v>
@@ -3390,35 +3390,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6724</v>
+        <v>-0.363</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4361</v>
+        <v>-0.2354</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7118</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6724</v>
+        <v>-0.363</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2565</v>
+        <v>0.637</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2565</v>
+        <v>0.637</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2565</v>
+        <v>0.637</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-1</v>
       </c>
       <c r="K65" t="n">
         <v>69</v>
@@ -3427,7 +3427,7 @@
         <v>65</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6723999999999999</v>
+        <v>-0.363</v>
       </c>
       <c r="N65" t="n">
         <v>134</v>
@@ -3436,231 +3436,231 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8011</v>
+        <v>-0.4148</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5195</v>
+        <v>-0.269</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7631</v>
+        <v>-0.8253</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8011</v>
+        <v>-0.4148</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8011</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-1.0776</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8011</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8011</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-1.0776</v>
       </c>
       <c r="K66" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8011</v>
+        <v>-0.4147999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>59</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8756</v>
+        <v>-0.4282</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5678</v>
+        <v>-0.2777</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7927</v>
+        <v>-0.8313</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8756</v>
+        <v>-0.4282</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8756</v>
+        <v>-0.4282</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8756</v>
+        <v>-0.4282</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8756</v>
+        <v>-0.4282</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8756</v>
+        <v>-0.4282</v>
       </c>
       <c r="N67" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9408</v>
+        <v>-0.4583</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6101</v>
+        <v>-0.2972</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8187</v>
+        <v>-0.8449</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9408</v>
+        <v>-0.4583</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3109</v>
+        <v>0.35</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.2517</v>
+        <v>-0.8083</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3109</v>
+        <v>0.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3109</v>
+        <v>0.35</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.2517</v>
+        <v>-0.8083</v>
       </c>
       <c r="K68" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="L68" t="n">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.9408000000000001</v>
+        <v>-0.4583</v>
       </c>
       <c r="N68" t="n">
-        <v>211</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.959</v>
+        <v>-0.5667</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6219</v>
+        <v>-0.3675</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.826</v>
+        <v>-0.8939</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.959</v>
+        <v>-0.5667</v>
       </c>
       <c r="F69" t="n">
-        <v>0.041</v>
+        <v>-0.5667</v>
       </c>
       <c r="G69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.041</v>
+        <v>-0.5667</v>
       </c>
       <c r="I69" t="n">
-        <v>0.041</v>
+        <v>-0.5667</v>
       </c>
       <c r="J69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L69" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.959</v>
+        <v>-0.5667</v>
       </c>
       <c r="N69" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Alkaren</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1</v>
+        <v>-0.6414</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6485</v>
+        <v>-0.4159</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8423</v>
+        <v>-0.9276</v>
       </c>
       <c r="E70" t="n">
-        <v>-1</v>
+        <v>-0.6414</v>
       </c>
       <c r="F70" t="n">
-        <v>-1</v>
+        <v>-0.5938</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-0.0476</v>
       </c>
       <c r="H70" t="n">
-        <v>-1</v>
+        <v>-0.5938</v>
       </c>
       <c r="I70" t="n">
-        <v>-1</v>
+        <v>-0.5938</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-0.0476</v>
       </c>
       <c r="K70" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M70" t="n">
-        <v>-1</v>
+        <v>-0.6414</v>
       </c>
       <c r="N70" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71">
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1</v>
+        <v>-0.6548</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6485</v>
+        <v>-0.4246</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8423</v>
+        <v>-0.9336</v>
       </c>
       <c r="E71" t="n">
-        <v>-1</v>
+        <v>-0.6548</v>
       </c>
       <c r="F71" t="n">
-        <v>-1</v>
+        <v>-0.6548</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1</v>
+        <v>-0.6548</v>
       </c>
       <c r="I71" t="n">
-        <v>-1</v>
+        <v>-0.6548</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1</v>
+        <v>-0.6548</v>
       </c>
       <c r="N71" t="n">
         <v>55</v>
@@ -3712,185 +3712,185 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1</v>
+        <v>-0.6684</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6485</v>
+        <v>-0.4335</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8423</v>
+        <v>-0.9398</v>
       </c>
       <c r="E72" t="n">
-        <v>-1</v>
+        <v>-0.6684</v>
       </c>
       <c r="F72" t="n">
-        <v>-1</v>
+        <v>-0.217</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>-0.4514</v>
       </c>
       <c r="H72" t="n">
-        <v>-1</v>
+        <v>-0.217</v>
       </c>
       <c r="I72" t="n">
-        <v>-1</v>
+        <v>-0.217</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>-0.4514</v>
       </c>
       <c r="K72" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M72" t="n">
-        <v>-1</v>
+        <v>-0.6684</v>
       </c>
       <c r="N72" t="n">
-        <v>36</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1</v>
+        <v>-0.7074</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6485</v>
+        <v>-0.4588</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8423</v>
+        <v>-0.9574</v>
       </c>
       <c r="E73" t="n">
-        <v>-1</v>
+        <v>-0.7074</v>
       </c>
       <c r="F73" t="n">
-        <v>-1</v>
+        <v>0.6539</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-1.3614</v>
       </c>
       <c r="H73" t="n">
-        <v>-1</v>
+        <v>0.6539</v>
       </c>
       <c r="I73" t="n">
-        <v>-1</v>
+        <v>0.6539</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-1.3614</v>
       </c>
       <c r="K73" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M73" t="n">
-        <v>-1</v>
+        <v>-0.7074999999999999</v>
       </c>
       <c r="N73" t="n">
-        <v>64</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alkaren</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0992</v>
+        <v>-0.7343</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7128</v>
+        <v>-0.4762</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8818</v>
+        <v>-0.9695</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0992</v>
+        <v>-0.7343</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.945</v>
+        <v>-0.7343</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.945</v>
+        <v>-0.7343</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.945</v>
+        <v>-0.7343</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L74" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0992</v>
+        <v>-0.7343</v>
       </c>
       <c r="N74" t="n">
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1387</v>
+        <v>-0.7477</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7385</v>
+        <v>-0.4849</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8976</v>
+        <v>-0.9756</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1387</v>
+        <v>-0.7477</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9437</v>
+        <v>-0.7477</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.195</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9437</v>
+        <v>-0.7477</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9437</v>
+        <v>-0.7477</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.195</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L75" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1387</v>
+        <v>-0.7477</v>
       </c>
       <c r="N75" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76">
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1511</v>
+        <v>-0.8305</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.5386</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9025</v>
+        <v>-1.0129</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1511</v>
+        <v>-0.8305</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1511</v>
+        <v>-0.1193</v>
       </c>
       <c r="G76" t="n">
-        <v>-1</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.1511</v>
+        <v>-0.1193</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1511</v>
+        <v>-0.1193</v>
       </c>
       <c r="J76" t="n">
-        <v>-1</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="K76" t="n">
         <v>64</v>
@@ -3933,7 +3933,7 @@
         <v>44</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.1511</v>
+        <v>-0.8305</v>
       </c>
       <c r="N76" t="n">
         <v>108</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.1722</v>
+        <v>-0.8383</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7602</v>
+        <v>-0.5436</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9109</v>
+        <v>-1.0165</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.1722</v>
+        <v>-0.8383</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4047</v>
+        <v>-0.8383</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.577</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4047</v>
+        <v>-0.8383</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4047</v>
+        <v>-0.8383</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.577</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L77" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.1723</v>
+        <v>-0.8383</v>
       </c>
       <c r="N77" t="n">
-        <v>205</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.1871</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7698</v>
+        <v>-0.607</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9169</v>
+        <v>-1.0606</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.1871</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.3248</v>
+        <v>-0.8652</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.8623</v>
+        <v>-0.0708</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.3248</v>
+        <v>-0.8652</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3248</v>
+        <v>-0.8652</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.8623</v>
+        <v>-0.0708</v>
       </c>
       <c r="K78" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L78" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.1871</v>
+        <v>-0.9359999999999999</v>
       </c>
       <c r="N78" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79">
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.2489</v>
+        <v>-1.0119</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8099</v>
+        <v>-0.6562</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.9415</v>
+        <v>-1.0948</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.2489</v>
+        <v>-1.0119</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.0636</v>
+        <v>-0.9851</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.1853</v>
+        <v>-0.0268</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.0636</v>
+        <v>-0.9851</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.0636</v>
+        <v>-0.9851</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.1853</v>
+        <v>-0.0268</v>
       </c>
       <c r="K79" t="n">
         <v>59</v>
@@ -4071,7 +4071,7 @@
         <v>66</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.2489</v>
+        <v>-1.0119</v>
       </c>
       <c r="N79" t="n">
         <v>125</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.7835</v>
+        <v>-1.3674</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.1566</v>
+        <v>-0.8868</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1545</v>
+        <v>-1.2553</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.7835</v>
+        <v>-1.3674</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.2153</v>
+        <v>-0.8117</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5682</v>
+        <v>-0.5557</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.2153</v>
+        <v>-0.8117</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2153</v>
+        <v>-0.8117</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.5682</v>
+        <v>-0.5557</v>
       </c>
       <c r="K80" t="n">
         <v>55</v>
@@ -4117,7 +4117,7 @@
         <v>156</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.7835</v>
+        <v>-1.3674</v>
       </c>
       <c r="N80" t="n">
         <v>211</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8959</v>
+        <v>-2.1208</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.878</v>
+        <v>-1.3753</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5976</v>
+        <v>-1.5954</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8959</v>
+        <v>-2.1208</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.0796</v>
+        <v>-1.799</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.8163</v>
+        <v>-0.3218</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.0796</v>
+        <v>-1.799</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.0796</v>
+        <v>-1.799</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.8163</v>
+        <v>-0.3218</v>
       </c>
       <c r="K81" t="n">
         <v>113</v>
@@ -4163,7 +4163,7 @@
         <v>101</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.8959</v>
+        <v>-2.1208</v>
       </c>
       <c r="N81" t="n">
         <v>214</v>
@@ -4269,10 +4269,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8171</v>
+        <v>1.5405</v>
       </c>
       <c r="J2" t="n">
-        <v>54.513</v>
+        <v>46.215</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0815</v>
+        <v>0.1361</v>
       </c>
       <c r="J3" t="n">
-        <v>2.445</v>
+        <v>4.083</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0068</v>
+        <v>0.0646</v>
       </c>
       <c r="J4" t="n">
-        <v>0.204</v>
+        <v>1.938</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1971</v>
+        <v>-0.1272</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.913</v>
+        <v>-3.816</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6634</v>
+        <v>-0.606</v>
       </c>
       <c r="J6" t="n">
-        <v>-19.902</v>
+        <v>-18.18</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6885</v>
+        <v>0.8472</v>
       </c>
       <c r="J7" t="n">
-        <v>20.655</v>
+        <v>25.416</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6038</v>
+        <v>0.7306</v>
       </c>
       <c r="J8" t="n">
-        <v>18.114</v>
+        <v>21.918</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1861</v>
+        <v>0.2014</v>
       </c>
       <c r="J9" t="n">
-        <v>5.583</v>
+        <v>6.042</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5867</v>
+        <v>-0.3849</v>
       </c>
       <c r="J10" t="n">
-        <v>-17.601</v>
+        <v>-11.547</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.4851</v>
       </c>
       <c r="J11" t="n">
-        <v>-21.579</v>
+        <v>-14.553</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3541</v>
+        <v>1.2239</v>
       </c>
       <c r="J12" t="n">
-        <v>29.7902</v>
+        <v>26.9258</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6364</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>14.0008</v>
+        <v>13.695</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2752</v>
+        <v>0.3173</v>
       </c>
       <c r="J14" t="n">
-        <v>6.0544</v>
+        <v>6.9806</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4549</v>
+        <v>-0.3864</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.0078</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4549</v>
+        <v>-0.3864</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.0078</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.39</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6501</v>
+        <v>0.7935</v>
       </c>
       <c r="J17" t="n">
-        <v>14.3022</v>
+        <v>17.457</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0057</v>
+        <v>-0.0168</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1254</v>
+        <v>-0.3696</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1733</v>
+        <v>-0.1067</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.8126</v>
+        <v>-2.3474</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2455</v>
+        <v>-0.1507</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.401</v>
+        <v>-3.3154</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.58</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.663</v>
+        <v>-0.4424</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.586</v>
+        <v>-9.732799999999999</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>2.71</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3259</v>
+        <v>1.8681</v>
       </c>
       <c r="J22" t="n">
-        <v>39.5403</v>
+        <v>31.7577</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4011</v>
+        <v>0.5099</v>
       </c>
       <c r="J23" t="n">
-        <v>6.8187</v>
+        <v>8.6683</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.18</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3533</v>
+        <v>0.4599</v>
       </c>
       <c r="J24" t="n">
-        <v>6.0061</v>
+        <v>7.8183</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1234</v>
+        <v>0.2178</v>
       </c>
       <c r="J25" t="n">
-        <v>2.0978</v>
+        <v>3.7026</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0375</v>
+        <v>0.1277</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6375</v>
+        <v>2.1709</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.45</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7685</v>
+        <v>0.9673</v>
       </c>
       <c r="J27" t="n">
-        <v>13.0645</v>
+        <v>16.4441</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3275</v>
+        <v>-0.2186</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.5675</v>
+        <v>-3.7162</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.79</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3443</v>
+        <v>-0.2283</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.8531</v>
+        <v>-3.8811</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.4092</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.4618</v>
+        <v>-6.9564</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.716</v>
+        <v>-0.4832</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.172</v>
+        <v>-8.214399999999999</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.83</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0492</v>
+        <v>0.963</v>
       </c>
       <c r="J32" t="n">
-        <v>23.0824</v>
+        <v>21.186</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4062</v>
+        <v>0.3618</v>
       </c>
       <c r="J33" t="n">
-        <v>8.936400000000001</v>
+        <v>7.9596</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3767</v>
+        <v>0.3386</v>
       </c>
       <c r="J34" t="n">
-        <v>8.2874</v>
+        <v>7.4492</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0041</v>
+        <v>0.04</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0902</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5264</v>
+        <v>-0.3387</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.5808</v>
+        <v>-7.4514</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.75</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0445</v>
+        <v>1.0246</v>
       </c>
       <c r="J37" t="n">
-        <v>22.979</v>
+        <v>22.5412</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>0.98</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0477</v>
+        <v>-0.0344</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.0494</v>
+        <v>-0.7568</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1838</v>
+        <v>-0.1091</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.0436</v>
+        <v>-2.4002</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5547</v>
+        <v>-0.3618</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.2034</v>
+        <v>-7.9596</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6906</v>
+        <v>-0.4632</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.1932</v>
+        <v>-10.1904</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>0.87</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0301</v>
+        <v>-0.0522</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4816</v>
+        <v>-0.8352000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>0.71</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2821</v>
+        <v>-0.2434</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.5136</v>
+        <v>-3.8944</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.43</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7477</v>
+        <v>-0.5165</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.9632</v>
+        <v>-8.263999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.34</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8726</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.9616</v>
+        <v>-9.668799999999999</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.29</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9381</v>
+        <v>-0.6538</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.0096</v>
+        <v>-10.4608</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>2.59</v>
       </c>
       <c r="I47" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J47" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.75</v>
       </c>
       <c r="I48" t="n">
-        <v>1.4841</v>
+        <v>1.3586</v>
       </c>
       <c r="J48" t="n">
-        <v>23.7456</v>
+        <v>21.7376</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.56</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0852</v>
+        <v>1.1484</v>
       </c>
       <c r="J49" t="n">
-        <v>17.3632</v>
+        <v>18.3744</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.43</v>
       </c>
       <c r="I50" t="n">
-        <v>0.829</v>
+        <v>0.9789</v>
       </c>
       <c r="J50" t="n">
-        <v>13.264</v>
+        <v>15.6624</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>1.07</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0213</v>
+        <v>0.1156</v>
       </c>
       <c r="J51" t="n">
-        <v>0.3408</v>
+        <v>1.8496</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>0.97</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0171</v>
+        <v>-0.0202</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2736</v>
+        <v>-0.3232</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.024</v>
+        <v>-0.0479</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.384</v>
+        <v>-0.7664</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2203</v>
+        <v>-0.1749</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.5248</v>
+        <v>-2.7984</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4049</v>
+        <v>-0.2711</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.4784</v>
+        <v>-4.3376</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.45</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7934</v>
+        <v>-0.542</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.6944</v>
+        <v>-8.672000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>2.08</v>
       </c>
       <c r="I57" t="n">
-        <v>2.0575</v>
+        <v>1.7774</v>
       </c>
       <c r="J57" t="n">
-        <v>32.92</v>
+        <v>28.4384</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.46</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0375</v>
+        <v>1.0551</v>
       </c>
       <c r="J58" t="n">
-        <v>16.6</v>
+        <v>16.8816</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.28</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6031</v>
+        <v>0.7101</v>
       </c>
       <c r="J59" t="n">
-        <v>9.6496</v>
+        <v>11.3616</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1897</v>
+        <v>0.2844</v>
       </c>
       <c r="J60" t="n">
-        <v>3.0352</v>
+        <v>4.5504</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1073</v>
+        <v>0.1982</v>
       </c>
       <c r="J61" t="n">
-        <v>1.7168</v>
+        <v>3.1712</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.58</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3206</v>
+        <v>0.9402</v>
       </c>
       <c r="J62" t="n">
-        <v>25.0914</v>
+        <v>17.8638</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.57</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3012</v>
+        <v>0.928</v>
       </c>
       <c r="J63" t="n">
-        <v>24.7228</v>
+        <v>17.632</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4701</v>
+        <v>0.4677</v>
       </c>
       <c r="J64" t="n">
-        <v>8.931900000000001</v>
+        <v>8.8863</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1.14</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2936</v>
+        <v>0.363</v>
       </c>
       <c r="J65" t="n">
-        <v>5.5784</v>
+        <v>6.897</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2408</v>
+        <v>0.3268</v>
       </c>
       <c r="J66" t="n">
-        <v>4.5752</v>
+        <v>6.2092</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0697</v>
+        <v>0.0333</v>
       </c>
       <c r="J67" t="n">
-        <v>1.3243</v>
+        <v>0.6327</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1692</v>
+        <v>-0.1314</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.2148</v>
+        <v>-2.4966</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1882</v>
+        <v>-0.1421</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.5758</v>
+        <v>-2.6999</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3078</v>
+        <v>-0.2021</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.8482</v>
+        <v>-3.8399</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.71</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4748</v>
+        <v>-0.3093</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.0212</v>
+        <v>-5.8767</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3619</v>
+        <v>0.9544</v>
       </c>
       <c r="J72" t="n">
-        <v>32.6856</v>
+        <v>22.9056</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7889</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>18.9336</v>
+        <v>14.0688</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0344</v>
+        <v>0.0771</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8256</v>
+        <v>1.8504</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.697</v>
+        <v>-0.6449</v>
       </c>
       <c r="J75" t="n">
-        <v>-16.728</v>
+        <v>-15.4776</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7451</v>
+        <v>-0.6964</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.8824</v>
+        <v>-16.7136</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.743</v>
+        <v>0.6813</v>
       </c>
       <c r="J77" t="n">
-        <v>17.832</v>
+        <v>16.3512</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I78" t="n">
-        <v>0.234</v>
+        <v>0.2599</v>
       </c>
       <c r="J78" t="n">
-        <v>5.616</v>
+        <v>6.2376</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2363</v>
+        <v>-0.1373</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.6712</v>
+        <v>-3.2952</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2692</v>
+        <v>-0.1593</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.4608</v>
+        <v>-3.8232</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4456</v>
+        <v>-0.2817</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.6944</v>
+        <v>-6.7608</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3097</v>
+        <v>0.9283</v>
       </c>
       <c r="J82" t="n">
-        <v>27.5037</v>
+        <v>19.4943</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.44</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0676</v>
+        <v>0.7773</v>
       </c>
       <c r="J83" t="n">
-        <v>22.4196</v>
+        <v>16.3233</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6067</v>
+        <v>0.5303</v>
       </c>
       <c r="J84" t="n">
-        <v>12.7407</v>
+        <v>11.1363</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0262</v>
+        <v>0.1036</v>
       </c>
       <c r="J85" t="n">
-        <v>0.5502</v>
+        <v>2.1756</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>1.03</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0688</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.1764</v>
+        <v>1.4448</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.36</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6027</v>
+        <v>0.5661</v>
       </c>
       <c r="J87" t="n">
-        <v>12.6567</v>
+        <v>11.8881</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5357</v>
       </c>
       <c r="J88" t="n">
-        <v>11.865</v>
+        <v>11.2497</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1674</v>
+        <v>-0.0982</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.5154</v>
+        <v>-2.0622</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3041</v>
+        <v>-0.1859</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.3861</v>
+        <v>-3.9039</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.44</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8299</v>
+        <v>-0.5709</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.4279</v>
+        <v>-11.9889</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.45</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6996</v>
+        <v>0.5262</v>
       </c>
       <c r="J92" t="n">
-        <v>15.3912</v>
+        <v>11.5764</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5272</v>
+        <v>0.4202</v>
       </c>
       <c r="J93" t="n">
-        <v>11.5984</v>
+        <v>9.244400000000001</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0376</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.6896</v>
+        <v>-0.8272</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2501</v>
+        <v>-0.1473</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.5022</v>
+        <v>-3.2406</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.46</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.5563</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.842</v>
+        <v>-12.2386</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6403</v>
+        <v>0.469</v>
       </c>
       <c r="J97" t="n">
-        <v>14.0866</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4509</v>
+        <v>0.3679</v>
       </c>
       <c r="J98" t="n">
-        <v>9.9198</v>
+        <v>8.0938</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>1.28</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4373</v>
+        <v>0.361</v>
       </c>
       <c r="J99" t="n">
-        <v>9.6206</v>
+        <v>7.942</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0357</v>
+        <v>0.0635</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7854</v>
+        <v>1.397</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4017</v>
+        <v>-0.2472</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.837400000000001</v>
+        <v>-5.4384</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>2.29</v>
       </c>
       <c r="I102" t="n">
-        <v>2.1936</v>
+        <v>1.812</v>
       </c>
       <c r="J102" t="n">
-        <v>43.872</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.2</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5036</v>
+        <v>0.4657</v>
       </c>
       <c r="J103" t="n">
-        <v>10.072</v>
+        <v>9.314</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3662</v>
+        <v>-0.2877</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.324</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5359</v>
+        <v>-0.4654</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.718</v>
+        <v>-9.308</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7581</v>
+        <v>-0.7055</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.162</v>
+        <v>-14.11</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.52</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7962</v>
+        <v>0.7268</v>
       </c>
       <c r="J107" t="n">
-        <v>15.924</v>
+        <v>14.536</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3934</v>
+        <v>0.4013</v>
       </c>
       <c r="J108" t="n">
-        <v>7.868</v>
+        <v>8.026</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.85</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3011</v>
+        <v>-0.1847</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.022</v>
+        <v>-3.694</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5281</v>
+        <v>-0.3425</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.562</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6417</v>
+        <v>-0.4263</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.834</v>
+        <v>-8.526</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2262</v>
+        <v>0.8672</v>
       </c>
       <c r="J112" t="n">
-        <v>26.9764</v>
+        <v>19.0784</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.24</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6755</v>
+        <v>0.5295</v>
       </c>
       <c r="J113" t="n">
-        <v>14.861</v>
+        <v>11.649</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.22</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6249</v>
+        <v>0.5011</v>
       </c>
       <c r="J114" t="n">
-        <v>13.7478</v>
+        <v>11.0242</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1055</v>
+        <v>0.1642</v>
       </c>
       <c r="J115" t="n">
-        <v>2.321</v>
+        <v>3.6124</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.76</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8112</v>
+        <v>-0.7654</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.8464</v>
+        <v>-16.8388</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5916</v>
+        <v>0.5571</v>
       </c>
       <c r="J117" t="n">
-        <v>13.0152</v>
+        <v>12.2562</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2015</v>
+        <v>0.2103</v>
       </c>
       <c r="J118" t="n">
-        <v>4.433</v>
+        <v>4.6266</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.95</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1255</v>
+        <v>-0.0738</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.761</v>
+        <v>-1.6236</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.271</v>
+        <v>-0.1643</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.962</v>
+        <v>-3.6146</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.64</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5931</v>
+        <v>-0.39</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.0482</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3769</v>
+        <v>0.3188</v>
       </c>
       <c r="J122" t="n">
-        <v>7.9149</v>
+        <v>6.6948</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0931</v>
+        <v>-0.0857</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.9551</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2276</v>
+        <v>-0.1623</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.7796</v>
+        <v>-3.4083</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.79</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3558</v>
+        <v>-0.2315</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.4718</v>
+        <v>-4.8615</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6839</v>
+        <v>-0.4589</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.3619</v>
+        <v>-9.636900000000001</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.69</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9006</v>
+        <v>0.619</v>
       </c>
       <c r="J127" t="n">
-        <v>18.9126</v>
+        <v>12.999</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5723</v>
+        <v>0.4357</v>
       </c>
       <c r="J128" t="n">
-        <v>12.0183</v>
+        <v>9.149699999999999</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.25</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3679</v>
+        <v>0.333</v>
       </c>
       <c r="J129" t="n">
-        <v>7.7259</v>
+        <v>6.993</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.11</v>
       </c>
       <c r="I130" t="n">
-        <v>0.142</v>
+        <v>0.1617</v>
       </c>
       <c r="J130" t="n">
-        <v>2.982</v>
+        <v>3.3957</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5032</v>
+        <v>-0.3213</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.5672</v>
+        <v>-6.7473</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3449</v>
+        <v>0.9437</v>
       </c>
       <c r="J132" t="n">
-        <v>30.9327</v>
+        <v>21.7051</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.39</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0392</v>
+        <v>0.7449</v>
       </c>
       <c r="J133" t="n">
-        <v>23.9016</v>
+        <v>17.1327</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I134" t="n">
-        <v>0.016</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>0.368</v>
+        <v>1.5893</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4477</v>
+        <v>-0.3811</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.2971</v>
+        <v>-8.7653</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8923</v>
+        <v>-0.8554</v>
       </c>
       <c r="J136" t="n">
-        <v>-20.5229</v>
+        <v>-19.6742</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.61</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="J137" t="n">
-        <v>20.1825</v>
+        <v>18.2735</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.234</v>
+        <v>0.2599</v>
       </c>
       <c r="J138" t="n">
-        <v>5.382</v>
+        <v>5.9777</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2018</v>
+        <v>-0.1147</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.6414</v>
+        <v>-2.6381</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4319</v>
+        <v>-0.272</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.9337</v>
+        <v>-6.256</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4859</v>
+        <v>-0.3108</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.1757</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5211</v>
+        <v>0.5013</v>
       </c>
       <c r="J142" t="n">
-        <v>10.422</v>
+        <v>10.026</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2526</v>
+        <v>-0.1948</v>
       </c>
       <c r="J143" t="n">
-        <v>-5.052</v>
+        <v>-3.896</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>0.77</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3524</v>
+        <v>-0.2422</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.048</v>
+        <v>-4.844</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.604</v>
+        <v>-0.4027</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.08</v>
+        <v>-8.054</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7318</v>
+        <v>-0.4955</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.636</v>
+        <v>-9.91</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.89</v>
       </c>
       <c r="I147" t="n">
-        <v>1.801</v>
+        <v>1.2991</v>
       </c>
       <c r="J147" t="n">
-        <v>36.02</v>
+        <v>25.982</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.38</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8796</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>17.592</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>1.3</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6696</v>
+        <v>0.5871</v>
       </c>
       <c r="J149" t="n">
-        <v>13.392</v>
+        <v>11.742</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>1.2</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4309</v>
+        <v>0.4487</v>
       </c>
       <c r="J150" t="n">
-        <v>8.618</v>
+        <v>8.974</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.037</v>
+        <v>0.0467</v>
       </c>
       <c r="J151" t="n">
-        <v>-0.74</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.53</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7665</v>
+        <v>0.7013</v>
       </c>
       <c r="J152" t="n">
-        <v>18.396</v>
+        <v>16.8312</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.3</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4882</v>
+        <v>0.4817</v>
       </c>
       <c r="J153" t="n">
-        <v>11.7168</v>
+        <v>11.5608</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0984</v>
+        <v>0.1472</v>
       </c>
       <c r="J154" t="n">
-        <v>2.3616</v>
+        <v>3.5328</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3165</v>
+        <v>-0.1883</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.596</v>
+        <v>-4.5192</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4845</v>
+        <v>-0.3085</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.628</v>
+        <v>-7.404</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8901</v>
+        <v>0.644</v>
       </c>
       <c r="J157" t="n">
-        <v>21.3624</v>
+        <v>15.456</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4084</v>
+        <v>0.3544</v>
       </c>
       <c r="J158" t="n">
-        <v>9.801600000000001</v>
+        <v>8.505599999999999</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.05</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2137</v>
+        <v>0.1906</v>
       </c>
       <c r="J159" t="n">
-        <v>5.1288</v>
+        <v>4.5744</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.99</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0589</v>
       </c>
       <c r="J160" t="n">
-        <v>-2.2632</v>
+        <v>-1.4136</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.68</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9578</v>
+        <v>-0.9302</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.9872</v>
+        <v>-22.3248</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2</v>
+        <v>0.1834</v>
       </c>
       <c r="J162" t="n">
-        <v>3.4</v>
+        <v>3.1178</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0237</v>
+        <v>-0.0504</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.4029</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2977</v>
+        <v>-0.2288</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.0609</v>
+        <v>-3.8896</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.6059</v>
+        <v>-0.406</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.3003</v>
+        <v>-6.902</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.39</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8577</v>
+        <v>-0.5916</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.5809</v>
+        <v>-10.0572</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>2.73</v>
       </c>
       <c r="I167" t="n">
-        <v>2.4965</v>
+        <v>2.2001</v>
       </c>
       <c r="J167" t="n">
-        <v>42.4405</v>
+        <v>37.4017</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.25</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5214</v>
+        <v>0.5103</v>
       </c>
       <c r="J168" t="n">
-        <v>8.863799999999999</v>
+        <v>8.6751</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3809</v>
+        <v>0.4245</v>
       </c>
       <c r="J169" t="n">
-        <v>6.4753</v>
+        <v>7.2165</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0699</v>
+        <v>0.161</v>
       </c>
       <c r="J170" t="n">
-        <v>1.1883</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4193</v>
+        <v>-0.3355</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.1281</v>
+        <v>-5.7035</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3973</v>
+        <v>0.4003</v>
       </c>
       <c r="J172" t="n">
-        <v>8.343299999999999</v>
+        <v>8.4063</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2026</v>
+        <v>0.1956</v>
       </c>
       <c r="J173" t="n">
-        <v>4.2546</v>
+        <v>4.1076</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.98</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0003</v>
+        <v>-0.0233</v>
       </c>
       <c r="J174" t="n">
-        <v>0.0063</v>
+        <v>-0.4893</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.77</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.395</v>
+        <v>-0.2542</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.295</v>
+        <v>-5.3382</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.42</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8416</v>
+        <v>-0.5795</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.6736</v>
+        <v>-12.1695</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.73</v>
       </c>
       <c r="I177" t="n">
-        <v>1.6347</v>
+        <v>1.141</v>
       </c>
       <c r="J177" t="n">
-        <v>34.3287</v>
+        <v>23.961</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0965</v>
+        <v>0.7931</v>
       </c>
       <c r="J178" t="n">
-        <v>23.0265</v>
+        <v>16.6551</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.186</v>
+        <v>0.2626</v>
       </c>
       <c r="J179" t="n">
-        <v>3.906</v>
+        <v>5.5146</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1399</v>
+        <v>-0.0605</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.9379</v>
+        <v>-1.2705</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.97</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2765</v>
+        <v>-0.1939</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.8065</v>
+        <v>-4.0719</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.78</v>
       </c>
       <c r="I182" t="n">
-        <v>1.6874</v>
+        <v>1.1816</v>
       </c>
       <c r="J182" t="n">
-        <v>37.1228</v>
+        <v>25.9952</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.66</v>
       </c>
       <c r="I183" t="n">
-        <v>1.475</v>
+        <v>1.0384</v>
       </c>
       <c r="J183" t="n">
-        <v>32.45</v>
+        <v>22.8448</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3474</v>
+        <v>0.3947</v>
       </c>
       <c r="J184" t="n">
-        <v>7.6428</v>
+        <v>8.683400000000001</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2429</v>
+        <v>0.3279</v>
       </c>
       <c r="J185" t="n">
-        <v>5.3438</v>
+        <v>7.2138</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5857</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.8854</v>
+        <v>-11.3432</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>0.93</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0605</v>
+        <v>-0.0726</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.331</v>
+        <v>-1.5972</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>0.93</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0605</v>
+        <v>-0.0726</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.331</v>
+        <v>-1.5972</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.84</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2181</v>
+        <v>-0.1743</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.7982</v>
+        <v>-3.8346</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4792</v>
+        <v>-0.318</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.5424</v>
+        <v>-6.996</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6818</v>
+        <v>-0.4585</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.9996</v>
+        <v>-10.087</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.77</v>
       </c>
       <c r="I192" t="n">
-        <v>1.037</v>
+        <v>0.7449</v>
       </c>
       <c r="J192" t="n">
-        <v>22.814</v>
+        <v>16.3878</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.19</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3488</v>
+        <v>0.3087</v>
       </c>
       <c r="J193" t="n">
-        <v>7.6736</v>
+        <v>6.7914</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0318</v>
+        <v>-0.0047</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.6996</v>
+        <v>-0.1034</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2443</v>
+        <v>-0.1406</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.3746</v>
+        <v>-3.0932</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.43</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8479</v>
+        <v>-0.5857</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.6538</v>
+        <v>-12.8854</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9761</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>21.4742</v>
+        <v>14.6036</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.4958</v>
       </c>
       <c r="J198" t="n">
-        <v>15.202</v>
+        <v>10.9076</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1089</v>
+        <v>0.1176</v>
       </c>
       <c r="J199" t="n">
-        <v>2.3958</v>
+        <v>2.5872</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5517</v>
+        <v>-0.358</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.1374</v>
+        <v>-7.876</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.64</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6131</v>
+        <v>-0.4042</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.4882</v>
+        <v>-8.8924</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0049</v>
+        <v>0.7393</v>
       </c>
       <c r="J202" t="n">
-        <v>21.1029</v>
+        <v>15.5253</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.37</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9172</v>
+        <v>0.6876</v>
       </c>
       <c r="J203" t="n">
-        <v>19.2612</v>
+        <v>14.4396</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.26</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6388</v>
+        <v>0.5436</v>
       </c>
       <c r="J204" t="n">
-        <v>13.4148</v>
+        <v>11.4156</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.6085</v>
+        <v>0.5304</v>
       </c>
       <c r="J205" t="n">
-        <v>12.7785</v>
+        <v>11.1384</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>1.02</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0448</v>
+        <v>0.0322</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.9408</v>
+        <v>0.6762</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.497</v>
+        <v>0.4797</v>
       </c>
       <c r="J207" t="n">
-        <v>10.437</v>
+        <v>10.0737</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.83</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2811</v>
+        <v>-0.1905</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.9031</v>
+        <v>-4.0005</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3167</v>
+        <v>-0.2102</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.6507</v>
+        <v>-4.4142</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4118</v>
+        <v>-0.2687</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.6478</v>
+        <v>-5.6427</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6309</v>
+        <v>-0.4201</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.2489</v>
+        <v>-8.822100000000001</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.039</v>
+        <v>-0.0587</v>
       </c>
       <c r="J212" t="n">
-        <v>-0.741</v>
+        <v>-1.1153</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.039</v>
+        <v>-0.0587</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.741</v>
+        <v>-1.1153</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1979</v>
+        <v>-0.1629</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.7601</v>
+        <v>-3.0951</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6024</v>
+        <v>-0.4018</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.4456</v>
+        <v>-7.6342</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.57</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6418</v>
+        <v>-0.4298</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.1942</v>
+        <v>-8.1662</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.66</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8667</v>
+        <v>0.7846</v>
       </c>
       <c r="J217" t="n">
-        <v>16.4673</v>
+        <v>14.9074</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.65</v>
       </c>
       <c r="I218" t="n">
-        <v>0.856</v>
+        <v>0.7741</v>
       </c>
       <c r="J218" t="n">
-        <v>16.264</v>
+        <v>14.7079</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2636</v>
+        <v>0.2657</v>
       </c>
       <c r="J219" t="n">
-        <v>5.0084</v>
+        <v>5.0483</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.98</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1373</v>
+        <v>-0.0601</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.6087</v>
+        <v>-1.1419</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4913</v>
+        <v>-0.3125</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.3347</v>
+        <v>-5.9375</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.69</v>
       </c>
       <c r="I222" t="n">
-        <v>1.5737</v>
+        <v>1.373</v>
       </c>
       <c r="J222" t="n">
-        <v>26.7529</v>
+        <v>23.341</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.32</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8248</v>
+        <v>0.8327</v>
       </c>
       <c r="J223" t="n">
-        <v>14.0216</v>
+        <v>14.1559</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.13</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3091</v>
+        <v>0.3793</v>
       </c>
       <c r="J224" t="n">
-        <v>5.2547</v>
+        <v>6.4481</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>1.02</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0318</v>
+        <v>0.0414</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.5406</v>
+        <v>0.7038</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3035</v>
+        <v>-0.223</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.1595</v>
+        <v>-3.791</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.26</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5266</v>
+        <v>0.6227</v>
       </c>
       <c r="J227" t="n">
-        <v>8.952199999999999</v>
+        <v>10.5859</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0839</v>
+        <v>-0.0825</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.4263</v>
+        <v>-1.4025</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3632</v>
+        <v>-0.2388</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.1744</v>
+        <v>-4.0596</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5511</v>
+        <v>-0.3632</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.3687</v>
+        <v>-6.1744</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.57</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.655</v>
+        <v>-0.4379</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.135</v>
+        <v>-7.4443</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4427</v>
+        <v>1.2828</v>
       </c>
       <c r="J232" t="n">
-        <v>33.1821</v>
+        <v>29.5044</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.52</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3258</v>
+        <v>1.2039</v>
       </c>
       <c r="J233" t="n">
-        <v>30.4934</v>
+        <v>27.6897</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5949</v>
+        <v>-0.5376</v>
       </c>
       <c r="J234" t="n">
-        <v>-13.6827</v>
+        <v>-12.3648</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.77</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.767</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="J235" t="n">
-        <v>-17.641</v>
+        <v>-16.5669</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.67</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.9928</v>
+        <v>-0.9678</v>
       </c>
       <c r="J236" t="n">
-        <v>-22.8344</v>
+        <v>-22.2594</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.63</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8966</v>
+        <v>1.0844</v>
       </c>
       <c r="J237" t="n">
-        <v>20.6218</v>
+        <v>24.9412</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.34</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5597</v>
+        <v>0.6723</v>
       </c>
       <c r="J238" t="n">
-        <v>12.8731</v>
+        <v>15.4629</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3332</v>
+        <v>-0.2025</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.6636</v>
+        <v>-4.6575</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.71</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.3307</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.8128</v>
+        <v>-7.6061</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5773</v>
+        <v>-0.3777</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.2779</v>
+        <v>-8.687099999999999</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.4</v>
       </c>
       <c r="I242" t="n">
-        <v>0.632</v>
+        <v>0.7703</v>
       </c>
       <c r="J242" t="n">
-        <v>13.904</v>
+        <v>16.9466</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.19</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3544</v>
+        <v>0.408</v>
       </c>
       <c r="J243" t="n">
-        <v>7.7968</v>
+        <v>8.976000000000001</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3245</v>
+        <v>0.3713</v>
       </c>
       <c r="J244" t="n">
-        <v>7.139</v>
+        <v>8.1686</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0612</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J245" t="n">
-        <v>1.3464</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.42</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.8575</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.865</v>
+        <v>-13.0504</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4372</v>
+        <v>1.2813</v>
       </c>
       <c r="J247" t="n">
-        <v>31.6184</v>
+        <v>28.1886</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.56</v>
       </c>
       <c r="I248" t="n">
-        <v>1.3414</v>
+        <v>1.2183</v>
       </c>
       <c r="J248" t="n">
-        <v>29.5108</v>
+        <v>26.8026</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.064</v>
+        <v>0.0068</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.408</v>
+        <v>0.1496</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.99</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1811</v>
+        <v>-0.1031</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.9842</v>
+        <v>-2.2682</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.82</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6815</v>
+        <v>-0.6226</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.993</v>
+        <v>-13.6972</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.26</v>
       </c>
       <c r="I252" t="n">
-        <v>0.525</v>
+        <v>0.6204</v>
       </c>
       <c r="J252" t="n">
-        <v>10.5</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.14</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3527</v>
+        <v>0.3855</v>
       </c>
       <c r="J253" t="n">
-        <v>7.054</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.7</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4836</v>
+        <v>-0.3164</v>
       </c>
       <c r="J254" t="n">
-        <v>-9.672000000000001</v>
+        <v>-6.328</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.57</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.6558</v>
+        <v>-0.4384</v>
       </c>
       <c r="J255" t="n">
-        <v>-13.116</v>
+        <v>-8.768000000000001</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.54</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6933</v>
+        <v>-0.4661</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.866</v>
+        <v>-9.321999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0934</v>
+        <v>1.0707</v>
       </c>
       <c r="J257" t="n">
-        <v>21.868</v>
+        <v>21.414</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0514</v>
+        <v>1.0446</v>
       </c>
       <c r="J258" t="n">
-        <v>21.028</v>
+        <v>20.892</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.34</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8278</v>
+        <v>0.8605</v>
       </c>
       <c r="J259" t="n">
-        <v>16.556</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.12</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2509</v>
+        <v>0.3357</v>
       </c>
       <c r="J260" t="n">
-        <v>5.018</v>
+        <v>6.714</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>1.12</v>
       </c>
       <c r="I261" t="n">
-        <v>0.2509</v>
+        <v>0.3357</v>
       </c>
       <c r="J261" t="n">
-        <v>5.018</v>
+        <v>6.714</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>2.1</v>
       </c>
       <c r="I262" t="n">
-        <v>1.26</v>
+        <v>1.1083</v>
       </c>
       <c r="J262" t="n">
-        <v>23.94</v>
+        <v>21.0577</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.68</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8458</v>
+        <v>0.7735</v>
       </c>
       <c r="J263" t="n">
-        <v>16.0702</v>
+        <v>14.6965</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1379</v>
+        <v>0.1697</v>
       </c>
       <c r="J264" t="n">
-        <v>2.6201</v>
+        <v>3.2243</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1379</v>
+        <v>0.1697</v>
       </c>
       <c r="J265" t="n">
-        <v>2.6201</v>
+        <v>3.2243</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.01</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.0728</v>
+        <v>-0.0162</v>
       </c>
       <c r="J266" t="n">
-        <v>-1.3832</v>
+        <v>-0.3078</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.11</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3512</v>
+        <v>0.2942</v>
       </c>
       <c r="J267" t="n">
-        <v>6.6728</v>
+        <v>5.5898</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1249</v>
+        <v>-0.1204</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.3731</v>
+        <v>-2.2876</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.62</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5605</v>
+        <v>-0.376</v>
       </c>
       <c r="J269" t="n">
-        <v>-10.6495</v>
+        <v>-7.144</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.61</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5746</v>
+        <v>-0.3854</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.9174</v>
+        <v>-7.3226</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.45</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7831</v>
+        <v>-0.5345</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.8789</v>
+        <v>-10.1555</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.52</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8033</v>
+        <v>0.9993</v>
       </c>
       <c r="J272" t="n">
-        <v>12.8528</v>
+        <v>15.9888</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.02</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0912</v>
+        <v>0.0756</v>
       </c>
       <c r="J273" t="n">
-        <v>1.4592</v>
+        <v>1.2096</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>0.98</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0323</v>
+        <v>-0.0325</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.5168</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.64</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5886</v>
+        <v>-0.3871</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.4176</v>
+        <v>-6.1936</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.6</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6385</v>
+        <v>-0.4241</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.216</v>
+        <v>-6.7856</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.76</v>
       </c>
       <c r="I277" t="n">
-        <v>1.6344</v>
+        <v>1.4191</v>
       </c>
       <c r="J277" t="n">
-        <v>26.1504</v>
+        <v>22.7056</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.55</v>
       </c>
       <c r="I278" t="n">
-        <v>1.2405</v>
+        <v>1.1691</v>
       </c>
       <c r="J278" t="n">
-        <v>19.848</v>
+        <v>18.7056</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>1.28</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6173</v>
+        <v>0.7164</v>
       </c>
       <c r="J279" t="n">
-        <v>9.876799999999999</v>
+        <v>11.4624</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>1.15</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3033</v>
+        <v>0.3994</v>
       </c>
       <c r="J280" t="n">
-        <v>4.8528</v>
+        <v>6.3904</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>1.11</v>
       </c>
       <c r="I281" t="n">
-        <v>0.1991</v>
+        <v>0.2914</v>
       </c>
       <c r="J281" t="n">
-        <v>3.1856</v>
+        <v>4.6624</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.35</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6056</v>
+        <v>0.7313</v>
       </c>
       <c r="J282" t="n">
-        <v>12.112</v>
+        <v>14.626</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0718</v>
+        <v>-0.0584</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.436</v>
+        <v>-1.168</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.88</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2401</v>
+        <v>-0.1491</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.802</v>
+        <v>-2.982</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.78</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.397</v>
+        <v>-0.2515</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.94</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.72</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4811</v>
+        <v>-0.3098</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.622</v>
+        <v>-6.196</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2847</v>
+        <v>1.1813</v>
       </c>
       <c r="J287" t="n">
-        <v>25.694</v>
+        <v>23.626</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.9318</v>
+        <v>0.9308</v>
       </c>
       <c r="J288" t="n">
-        <v>18.636</v>
+        <v>18.616</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3252</v>
+        <v>0.386</v>
       </c>
       <c r="J289" t="n">
-        <v>6.504</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.11</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2682</v>
+        <v>0.3318</v>
       </c>
       <c r="J290" t="n">
-        <v>5.364</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.84</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6313</v>
+        <v>-0.5686</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.626</v>
+        <v>-11.372</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.99</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1554</v>
+        <v>1.0444</v>
       </c>
       <c r="J292" t="n">
-        <v>20.7972</v>
+        <v>18.7992</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.46</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5914</v>
+        <v>0.5488</v>
       </c>
       <c r="J293" t="n">
-        <v>10.6452</v>
+        <v>9.878399999999999</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.45</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5784</v>
+        <v>0.5386</v>
       </c>
       <c r="J294" t="n">
-        <v>10.4112</v>
+        <v>9.694800000000001</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.1946</v>
+        <v>0.2219</v>
       </c>
       <c r="J295" t="n">
-        <v>3.5028</v>
+        <v>3.9942</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>1.01</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.0736</v>
+        <v>-0.0167</v>
       </c>
       <c r="J296" t="n">
-        <v>-1.3248</v>
+        <v>-0.3006</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>0.88</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0897</v>
+        <v>-0.1001</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.6146</v>
+        <v>-1.8018</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>0.77</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2669</v>
+        <v>-0.2226</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.8042</v>
+        <v>-4.0068</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4136</v>
+        <v>-0.3111</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.4448</v>
+        <v>-5.5998</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.62</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5286</v>
+        <v>-0.3645</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.514799999999999</v>
+        <v>-6.561</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.36</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8792</v>
+        <v>-0.6081</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.8256</v>
+        <v>-10.9458</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.25</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5204</v>
+        <v>0.6148</v>
       </c>
       <c r="J302" t="n">
-        <v>8.3264</v>
+        <v>9.8368</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.302</v>
+        <v>-0.2077</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.832</v>
+        <v>-3.3232</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.77</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3711</v>
+        <v>-0.2462</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.9376</v>
+        <v>-3.9392</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.7</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4766</v>
+        <v>-0.3134</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.6256</v>
+        <v>-5.0144</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.57</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6512</v>
+        <v>-0.4355</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.4192</v>
+        <v>-6.968</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.96</v>
       </c>
       <c r="I307" t="n">
-        <v>1.941</v>
+        <v>1.6394</v>
       </c>
       <c r="J307" t="n">
-        <v>31.056</v>
+        <v>26.2304</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.67</v>
       </c>
       <c r="I308" t="n">
-        <v>1.4522</v>
+        <v>1.3049</v>
       </c>
       <c r="J308" t="n">
-        <v>23.2352</v>
+        <v>20.8784</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.54</v>
       </c>
       <c r="I309" t="n">
-        <v>1.2004</v>
+        <v>1.1506</v>
       </c>
       <c r="J309" t="n">
-        <v>19.2064</v>
+        <v>18.4096</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3187</v>
+        <v>-0.2305</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.0992</v>
+        <v>-3.688</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.92</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4722</v>
+        <v>-0.392</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.5552</v>
+        <v>-6.272</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.32</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.6412</v>
       </c>
       <c r="J312" t="n">
-        <v>16.104</v>
+        <v>19.236</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4442</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="J313" t="n">
-        <v>13.326</v>
+        <v>15.591</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1621</v>
+        <v>0.1779</v>
       </c>
       <c r="J314" t="n">
-        <v>4.863</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.85</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3162</v>
+        <v>-0.1912</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.486000000000001</v>
+        <v>-5.736</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.65</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5885</v>
+        <v>-0.3861</v>
       </c>
       <c r="J316" t="n">
-        <v>-17.655</v>
+        <v>-11.583</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.3</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8707</v>
+        <v>0.8441</v>
       </c>
       <c r="J317" t="n">
-        <v>26.121</v>
+        <v>25.323</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.23</v>
       </c>
       <c r="I318" t="n">
-        <v>0.7059</v>
+        <v>0.6723</v>
       </c>
       <c r="J318" t="n">
-        <v>21.177</v>
+        <v>20.169</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.07</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2529</v>
+        <v>0.2448</v>
       </c>
       <c r="J319" t="n">
-        <v>7.587</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>1.07</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2529</v>
+        <v>0.2448</v>
       </c>
       <c r="J320" t="n">
-        <v>7.587</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.63</v>
       </c>
       <c r="I321" t="n">
-        <v>-1.0747</v>
+        <v>-1.0597</v>
       </c>
       <c r="J321" t="n">
-        <v>-32.241</v>
+        <v>-31.791</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.95</v>
       </c>
       <c r="I322" t="n">
-        <v>1.9996</v>
+        <v>1.7099</v>
       </c>
       <c r="J322" t="n">
-        <v>47.9904</v>
+        <v>41.0376</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.59</v>
       </c>
       <c r="I323" t="n">
-        <v>1.415</v>
+        <v>1.2654</v>
       </c>
       <c r="J323" t="n">
-        <v>33.96</v>
+        <v>30.3696</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.82</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.6731</v>
+        <v>-0.6147</v>
       </c>
       <c r="J324" t="n">
-        <v>-16.1544</v>
+        <v>-14.7528</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.7917</v>
+        <v>-0.7436</v>
       </c>
       <c r="J325" t="n">
-        <v>-19.0008</v>
+        <v>-17.8464</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.9484</v>
+        <v>-0.9169</v>
       </c>
       <c r="J326" t="n">
-        <v>-22.7616</v>
+        <v>-22.0056</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.36</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6089</v>
+        <v>0.7362</v>
       </c>
       <c r="J327" t="n">
-        <v>14.6136</v>
+        <v>17.6688</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2246</v>
+        <v>0.2353</v>
       </c>
       <c r="J328" t="n">
-        <v>5.3904</v>
+        <v>5.6472</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.92</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1788</v>
+        <v>-0.1079</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.2912</v>
+        <v>-2.5896</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.84</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3144</v>
+        <v>-0.1941</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.5456</v>
+        <v>-4.6584</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.61</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6281</v>
+        <v>-0.4162</v>
       </c>
       <c r="J331" t="n">
-        <v>-15.0744</v>
+        <v>-9.988799999999999</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.25</v>
       </c>
       <c r="I332" t="n">
-        <v>0.753</v>
+        <v>0.7212</v>
       </c>
       <c r="J332" t="n">
-        <v>26.355</v>
+        <v>25.242</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.19</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6044</v>
+        <v>0.5703</v>
       </c>
       <c r="J333" t="n">
-        <v>21.154</v>
+        <v>19.9605</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.18</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5784</v>
+        <v>0.5446</v>
       </c>
       <c r="J334" t="n">
-        <v>20.244</v>
+        <v>19.061</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.99</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1186</v>
+        <v>-0.0678</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.151</v>
+        <v>-2.373</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.7</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.9233</v>
+        <v>-0.8911</v>
       </c>
       <c r="J336" t="n">
-        <v>-32.3155</v>
+        <v>-31.1885</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.78</v>
       </c>
       <c r="I337" t="n">
-        <v>1.0344</v>
+        <v>1.2013</v>
       </c>
       <c r="J337" t="n">
-        <v>36.204</v>
+        <v>42.0455</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.03</v>
       </c>
       <c r="I338" t="n">
-        <v>0.0368</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="J338" t="n">
-        <v>1.288</v>
+        <v>2.7195</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.02</v>
       </c>
       <c r="I339" t="n">
-        <v>0.0142</v>
+        <v>0.0517</v>
       </c>
       <c r="J339" t="n">
-        <v>0.497</v>
+        <v>1.8095</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.203</v>
+        <v>-0.1105</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.105</v>
+        <v>-3.8675</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4975</v>
+        <v>-0.3181</v>
       </c>
       <c r="J341" t="n">
-        <v>-17.4125</v>
+        <v>-11.1335</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.39</v>
       </c>
       <c r="I342" t="n">
-        <v>0.676</v>
+        <v>0.6369</v>
       </c>
       <c r="J342" t="n">
-        <v>14.196</v>
+        <v>13.3749</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.04</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1638</v>
+        <v>0.1131</v>
       </c>
       <c r="J343" t="n">
-        <v>3.4398</v>
+        <v>2.3751</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2299</v>
+        <v>-0.1539</v>
       </c>
       <c r="J344" t="n">
-        <v>-4.8279</v>
+        <v>-3.2319</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.5084</v>
+        <v>-0.3313</v>
       </c>
       <c r="J345" t="n">
-        <v>-10.6764</v>
+        <v>-6.9573</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.42</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.8416</v>
+        <v>-0.5795</v>
       </c>
       <c r="J346" t="n">
-        <v>-17.6736</v>
+        <v>-12.1695</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.4</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5735</v>
+        <v>0.5072</v>
       </c>
       <c r="J347" t="n">
-        <v>12.0435</v>
+        <v>10.6512</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.3</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4434</v>
+        <v>0.3947</v>
       </c>
       <c r="J348" t="n">
-        <v>9.311400000000001</v>
+        <v>8.2887</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.29</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4294</v>
+        <v>0.3833</v>
       </c>
       <c r="J349" t="n">
-        <v>9.0174</v>
+        <v>8.049300000000001</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>1.22</v>
       </c>
       <c r="I350" t="n">
-        <v>0.3153</v>
+        <v>0.303</v>
       </c>
       <c r="J350" t="n">
-        <v>6.6213</v>
+        <v>6.363</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.96</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.1762</v>
+        <v>-0.0868</v>
       </c>
       <c r="J351" t="n">
-        <v>-3.7002</v>
+        <v>-1.8228</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.43</v>
       </c>
       <c r="I352" t="n">
-        <v>1.0912</v>
+        <v>1.0562</v>
       </c>
       <c r="J352" t="n">
-        <v>21.824</v>
+        <v>21.124</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.26</v>
       </c>
       <c r="I353" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7069</v>
       </c>
       <c r="J353" t="n">
-        <v>14.204</v>
+        <v>14.138</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.26</v>
       </c>
       <c r="I354" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7069</v>
       </c>
       <c r="J354" t="n">
-        <v>14.204</v>
+        <v>14.138</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.1</v>
       </c>
       <c r="I355" t="n">
-        <v>0.2487</v>
+        <v>0.3081</v>
       </c>
       <c r="J355" t="n">
-        <v>4.974</v>
+        <v>6.162</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.83</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.6512</v>
+        <v>-0.5908</v>
       </c>
       <c r="J356" t="n">
-        <v>-13.024</v>
+        <v>-11.816</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.35</v>
       </c>
       <c r="I357" t="n">
-        <v>0.5723</v>
+        <v>0.6891</v>
       </c>
       <c r="J357" t="n">
-        <v>11.446</v>
+        <v>13.782</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.25</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4415</v>
+        <v>0.5172</v>
       </c>
       <c r="J358" t="n">
-        <v>8.83</v>
+        <v>10.344</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>1.15</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2959</v>
+        <v>0.3354</v>
       </c>
       <c r="J359" t="n">
-        <v>5.918</v>
+        <v>6.708</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.85</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3181</v>
+        <v>-0.1921</v>
       </c>
       <c r="J360" t="n">
-        <v>-6.362</v>
+        <v>-3.842</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.58</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6747</v>
+        <v>-0.451</v>
       </c>
       <c r="J361" t="n">
-        <v>-13.494</v>
+        <v>-9.02</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.9</v>
       </c>
       <c r="I362" t="n">
-        <v>1.9582</v>
+        <v>1.6612</v>
       </c>
       <c r="J362" t="n">
-        <v>45.0386</v>
+        <v>38.2076</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.22</v>
       </c>
       <c r="I363" t="n">
-        <v>0.6339</v>
+        <v>0.6214</v>
       </c>
       <c r="J363" t="n">
-        <v>14.5797</v>
+        <v>14.2922</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.19</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5553</v>
+        <v>0.5476</v>
       </c>
       <c r="J364" t="n">
-        <v>12.7719</v>
+        <v>12.5948</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.9</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4563</v>
+        <v>-0.3875</v>
       </c>
       <c r="J365" t="n">
-        <v>-10.4949</v>
+        <v>-8.9125</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.48</v>
       </c>
       <c r="I366" t="n">
-        <v>-1.3909</v>
+        <v>-1.424</v>
       </c>
       <c r="J366" t="n">
-        <v>-31.9907</v>
+        <v>-32.752</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.3</v>
       </c>
       <c r="I367" t="n">
-        <v>0.4953</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="J367" t="n">
-        <v>11.3919</v>
+        <v>13.5976</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.19</v>
       </c>
       <c r="I368" t="n">
-        <v>0.3424</v>
+        <v>0.3994</v>
       </c>
       <c r="J368" t="n">
-        <v>7.8752</v>
+        <v>9.186199999999999</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.03</v>
       </c>
       <c r="I369" t="n">
-        <v>0.045</v>
+        <v>0.0814</v>
       </c>
       <c r="J369" t="n">
-        <v>1.035</v>
+        <v>1.8722</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.97</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1202</v>
+        <v>-0.0575</v>
       </c>
       <c r="J370" t="n">
-        <v>-2.7646</v>
+        <v>-1.3225</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.265</v>
+        <v>-0.1537</v>
       </c>
       <c r="J371" t="n">
-        <v>-6.095</v>
+        <v>-3.5351</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.84</v>
       </c>
       <c r="I372" t="n">
-        <v>1.0598</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="J372" t="n">
-        <v>24.3754</v>
+        <v>22.3629</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.14</v>
       </c>
       <c r="I373" t="n">
-        <v>0.1953</v>
+        <v>0.2048</v>
       </c>
       <c r="J373" t="n">
-        <v>4.4919</v>
+        <v>4.7104</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.12</v>
       </c>
       <c r="I374" t="n">
-        <v>0.1634</v>
+        <v>0.1779</v>
       </c>
       <c r="J374" t="n">
-        <v>3.7582</v>
+        <v>4.0917</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>1.07</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0799</v>
+        <v>0.1059</v>
       </c>
       <c r="J375" t="n">
-        <v>1.8377</v>
+        <v>2.4357</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.92</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2443</v>
+        <v>-0.1343</v>
       </c>
       <c r="J376" t="n">
-        <v>-5.6189</v>
+        <v>-3.0889</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.51</v>
       </c>
       <c r="I377" t="n">
-        <v>0.797</v>
+        <v>0.7681</v>
       </c>
       <c r="J377" t="n">
-        <v>18.331</v>
+        <v>17.6663</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.03</v>
       </c>
       <c r="I378" t="n">
-        <v>0.12</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J378" t="n">
-        <v>2.76</v>
+        <v>1.8561</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.96</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.0718</v>
+        <v>-0.0584</v>
       </c>
       <c r="J379" t="n">
-        <v>-1.6514</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.68</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.5344</v>
+        <v>-0.3479</v>
       </c>
       <c r="J380" t="n">
-        <v>-12.2912</v>
+        <v>-8.0017</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.51</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.7446</v>
+        <v>-0.5044</v>
       </c>
       <c r="J381" t="n">
-        <v>-17.1258</v>
+        <v>-11.6012</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.28</v>
       </c>
       <c r="I382" t="n">
-        <v>0.522</v>
+        <v>0.6159</v>
       </c>
       <c r="J382" t="n">
-        <v>11.484</v>
+        <v>13.5498</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.17</v>
       </c>
       <c r="I383" t="n">
-        <v>0.3684</v>
+        <v>0.4107</v>
       </c>
       <c r="J383" t="n">
-        <v>8.104799999999999</v>
+        <v>9.035399999999999</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.91</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.175</v>
+        <v>-0.115</v>
       </c>
       <c r="J384" t="n">
-        <v>-3.85</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.62</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.608</v>
+        <v>-0.4019</v>
       </c>
       <c r="J385" t="n">
-        <v>-13.376</v>
+        <v>-8.841799999999999</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.62</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.608</v>
+        <v>-0.4019</v>
       </c>
       <c r="J386" t="n">
-        <v>-13.376</v>
+        <v>-8.841799999999999</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.82</v>
       </c>
       <c r="I387" t="n">
-        <v>1.8401</v>
+        <v>1.5565</v>
       </c>
       <c r="J387" t="n">
-        <v>40.4822</v>
+        <v>34.243</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.24</v>
       </c>
       <c r="I388" t="n">
-        <v>0.6743</v>
+        <v>0.6653</v>
       </c>
       <c r="J388" t="n">
-        <v>14.8346</v>
+        <v>14.6366</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.17</v>
       </c>
       <c r="I389" t="n">
-        <v>0.4863</v>
+        <v>0.4946</v>
       </c>
       <c r="J389" t="n">
-        <v>10.6986</v>
+        <v>10.8812</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.9</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4617</v>
+        <v>-0.3917</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.1574</v>
+        <v>-8.6174</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.64</v>
       </c>
       <c r="I391" t="n">
-        <v>-1.0737</v>
+        <v>-1.0581</v>
       </c>
       <c r="J391" t="n">
-        <v>-23.6214</v>
+        <v>-23.2782</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.54</v>
       </c>
       <c r="I392" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.0072</v>
       </c>
       <c r="J392" t="n">
-        <v>19.488</v>
+        <v>24.1728</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.02</v>
       </c>
       <c r="I393" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="J393" t="n">
-        <v>1.7376</v>
+        <v>1.6176</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.9</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.2253</v>
+        <v>-0.1334</v>
       </c>
       <c r="J394" t="n">
-        <v>-5.4072</v>
+        <v>-3.2016</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.78</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.4103</v>
+        <v>-0.258</v>
       </c>
       <c r="J395" t="n">
-        <v>-9.847200000000001</v>
+        <v>-6.192</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.72</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4924</v>
+        <v>-0.3163</v>
       </c>
       <c r="J396" t="n">
-        <v>-11.8176</v>
+        <v>-7.5912</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.39</v>
       </c>
       <c r="I397" t="n">
-        <v>1.0586</v>
+        <v>1.0257</v>
       </c>
       <c r="J397" t="n">
-        <v>25.4064</v>
+        <v>24.6168</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.16</v>
       </c>
       <c r="I398" t="n">
-        <v>0.5148</v>
+        <v>0.4876</v>
       </c>
       <c r="J398" t="n">
-        <v>12.3552</v>
+        <v>11.7024</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.11</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3701</v>
+        <v>0.3542</v>
       </c>
       <c r="J399" t="n">
-        <v>8.882400000000001</v>
+        <v>8.5008</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.99</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1279</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J400" t="n">
-        <v>-3.0696</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.74</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.8374</v>
+        <v>-0.7964</v>
       </c>
       <c r="J401" t="n">
-        <v>-20.0976</v>
+        <v>-19.1136</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.41</v>
       </c>
       <c r="I402" t="n">
-        <v>0.6627</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J402" t="n">
-        <v>13.254</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.06</v>
       </c>
       <c r="I403" t="n">
-        <v>0.1612</v>
+        <v>0.1648</v>
       </c>
       <c r="J403" t="n">
-        <v>3.224</v>
+        <v>3.296</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.01</v>
       </c>
       <c r="I404" t="n">
-        <v>0.0488</v>
+        <v>0.0398</v>
       </c>
       <c r="J404" t="n">
-        <v>0.976</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.4089</v>
+        <v>-0.2573</v>
       </c>
       <c r="J405" t="n">
-        <v>-8.178000000000001</v>
+        <v>-5.146</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.67</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5565</v>
+        <v>-0.3629</v>
       </c>
       <c r="J406" t="n">
-        <v>-11.13</v>
+        <v>-7.258</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.56</v>
       </c>
       <c r="I407" t="n">
-        <v>1.3249</v>
+        <v>1.2096</v>
       </c>
       <c r="J407" t="n">
-        <v>26.498</v>
+        <v>24.192</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.56</v>
       </c>
       <c r="I408" t="n">
-        <v>1.3249</v>
+        <v>1.2096</v>
       </c>
       <c r="J408" t="n">
-        <v>26.498</v>
+        <v>24.192</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.44</v>
       </c>
       <c r="I409" t="n">
-        <v>1.0837</v>
+        <v>1.057</v>
       </c>
       <c r="J409" t="n">
-        <v>21.674</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.98</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2345</v>
+        <v>-0.1527</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.69</v>
+        <v>-3.054</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.62</v>
       </c>
       <c r="I411" t="n">
-        <v>-1.1286</v>
+        <v>-1.1211</v>
       </c>
       <c r="J411" t="n">
-        <v>-22.572</v>
+        <v>-22.422</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.14</v>
       </c>
       <c r="I412" t="n">
-        <v>0.3733</v>
+        <v>0.4124</v>
       </c>
       <c r="J412" t="n">
-        <v>5.9728</v>
+        <v>6.5984</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>0.83</v>
       </c>
       <c r="I413" t="n">
-        <v>-0.2387</v>
+        <v>-0.1855</v>
       </c>
       <c r="J413" t="n">
-        <v>-3.8192</v>
+        <v>-2.968</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>0.7</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.4667</v>
+        <v>-0.3094</v>
       </c>
       <c r="J414" t="n">
-        <v>-7.4672</v>
+        <v>-4.9504</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.67</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.51</v>
+        <v>-0.3378</v>
       </c>
       <c r="J415" t="n">
-        <v>-8.16</v>
+        <v>-5.4048</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.62</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.5789</v>
+        <v>-0.3848</v>
       </c>
       <c r="J416" t="n">
-        <v>-9.2624</v>
+        <v>-6.1568</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.94</v>
       </c>
       <c r="I417" t="n">
-        <v>1.8902</v>
+        <v>1.5981</v>
       </c>
       <c r="J417" t="n">
-        <v>30.2432</v>
+        <v>25.5696</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.89</v>
       </c>
       <c r="I418" t="n">
-        <v>1.8113</v>
+        <v>1.542</v>
       </c>
       <c r="J418" t="n">
-        <v>28.9808</v>
+        <v>24.672</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>1.4</v>
       </c>
       <c r="I419" t="n">
-        <v>0.8319</v>
+        <v>0.9537</v>
       </c>
       <c r="J419" t="n">
-        <v>13.3104</v>
+        <v>15.2592</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>1.22</v>
       </c>
       <c r="I420" t="n">
-        <v>0.4349</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J420" t="n">
-        <v>6.9584</v>
+        <v>8.798400000000001</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>1.01</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.1444</v>
+        <v>-0.0586</v>
       </c>
       <c r="J421" t="n">
-        <v>-2.3104</v>
+        <v>-0.9376</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8039/event_8039_evp_summary.xlsx
+++ b/database/event/8039/event_8039_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.9923</v>
+        <v>8.2765</v>
       </c>
       <c r="C2" t="n">
-        <v>5.183</v>
+        <v>5.3673</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9701</v>
+        <v>3.1434</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9923</v>
+        <v>8.2765</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1633</v>
+        <v>2.0857</v>
       </c>
       <c r="G2" t="n">
-        <v>5.829</v>
+        <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1633</v>
+        <v>2.0857</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1633</v>
+        <v>2.0857</v>
       </c>
       <c r="J2" t="n">
-        <v>5.829</v>
+        <v>6.4095</v>
       </c>
       <c r="K2" t="n">
         <v>36</v>
@@ -529,7 +529,7 @@
         <v>197</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9923</v>
+        <v>8.495200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>233</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3197</v>
+        <v>7.4423</v>
       </c>
       <c r="C3" t="n">
-        <v>4.7468</v>
+        <v>4.8264</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6665</v>
+        <v>2.7637</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3197</v>
+        <v>7.4423</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9744</v>
+        <v>1.895</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3453</v>
+        <v>5.5473</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9744</v>
+        <v>1.895</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9744</v>
+        <v>1.895</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3453</v>
+        <v>5.5473</v>
       </c>
       <c r="K3" t="n">
         <v>55</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>7.3197</v>
+        <v>7.442299999999999</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.902</v>
+        <v>6.0217</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8275</v>
+        <v>3.9051</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0264</v>
+        <v>2.117</v>
       </c>
       <c r="E4" t="n">
-        <v>5.902</v>
+        <v>6.0217</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7516</v>
+        <v>2.4877</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1504</v>
+        <v>3.534</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7516</v>
+        <v>2.7198</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7516</v>
+        <v>2.7198</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1504</v>
+        <v>3.534</v>
       </c>
       <c r="K4" t="n">
         <v>36</v>
@@ -621,7 +621,7 @@
         <v>197</v>
       </c>
       <c r="M4" t="n">
-        <v>5.901999999999999</v>
+        <v>6.2538</v>
       </c>
       <c r="N4" t="n">
         <v>233</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3634</v>
+        <v>5.7289</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4782</v>
+        <v>3.7152</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7833</v>
+        <v>1.9837</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3634</v>
+        <v>5.7289</v>
       </c>
       <c r="F5" t="n">
-        <v>2.049</v>
+        <v>1.9894</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3144</v>
+        <v>3.7396</v>
       </c>
       <c r="H5" t="n">
-        <v>2.049</v>
+        <v>1.9894</v>
       </c>
       <c r="I5" t="n">
-        <v>2.049</v>
+        <v>1.9894</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3144</v>
+        <v>3.7396</v>
       </c>
       <c r="K5" t="n">
         <v>113</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3634</v>
+        <v>5.729</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -676,185 +676,185 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1753</v>
+        <v>4.1972</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7077</v>
+        <v>2.7219</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2469</v>
+        <v>1.2864</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1753</v>
+        <v>4.1972</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2512</v>
+        <v>-0.1597</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9241</v>
+        <v>4.3569</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7792</v>
+        <v>-0.1597</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7792</v>
+        <v>-0.1597</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9241</v>
+        <v>4.3569</v>
       </c>
       <c r="K6" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7033</v>
+        <v>4.1972</v>
       </c>
       <c r="N6" t="n">
-        <v>205</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9271</v>
+        <v>3.9656</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5467</v>
+        <v>2.5717</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1349</v>
+        <v>1.181</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9271</v>
+        <v>3.9656</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2113</v>
+        <v>2.9528</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1384</v>
+        <v>1.0128</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2113</v>
+        <v>3.7379</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2113</v>
+        <v>3.7379</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1384</v>
+        <v>1.0128</v>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="L7" t="n">
-        <v>197</v>
+        <v>109</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9271</v>
+        <v>4.7507</v>
       </c>
       <c r="N7" t="n">
-        <v>233</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7659</v>
+        <v>3.6378</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4422</v>
+        <v>2.3591</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0621</v>
+        <v>1.0318</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7659</v>
+        <v>3.6378</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0723</v>
+        <v>1.6521</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6936</v>
+        <v>1.9857</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3866</v>
+        <v>1.6521</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3866</v>
+        <v>1.6521</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6936</v>
+        <v>1.9857</v>
       </c>
       <c r="K8" t="n">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="L8" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0802</v>
+        <v>3.6378</v>
       </c>
       <c r="N8" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4405</v>
+        <v>3.6095</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2312</v>
+        <v>2.3408</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9152</v>
+        <v>1.0189</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4405</v>
+        <v>3.6095</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6847</v>
+        <v>2.8293</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7558</v>
+        <v>0.7802</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6847</v>
+        <v>3.4674</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6847</v>
+        <v>3.4674</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7558</v>
+        <v>0.7802</v>
       </c>
       <c r="K9" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="L9" t="n">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4405</v>
+        <v>4.2476</v>
       </c>
       <c r="N9" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4327</v>
+        <v>3.4607</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2261</v>
+        <v>2.2443</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9117</v>
+        <v>0.9512</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4327</v>
+        <v>3.4607</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6244</v>
+        <v>1.5621</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8083</v>
+        <v>1.8986</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6244</v>
+        <v>1.5621</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6244</v>
+        <v>1.5621</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8083</v>
+        <v>1.8986</v>
       </c>
       <c r="K10" t="n">
         <v>55</v>
@@ -897,7 +897,7 @@
         <v>156</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4327</v>
+        <v>3.4607</v>
       </c>
       <c r="N10" t="n">
         <v>211</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0867</v>
+        <v>3.2416</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0017</v>
+        <v>2.1022</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.8514</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0867</v>
+        <v>3.2416</v>
       </c>
       <c r="F11" t="n">
-        <v>1.627</v>
+        <v>1.5685</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4597</v>
+        <v>1.6731</v>
       </c>
       <c r="H11" t="n">
-        <v>1.627</v>
+        <v>1.5685</v>
       </c>
       <c r="I11" t="n">
-        <v>1.627</v>
+        <v>1.5685</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4597</v>
+        <v>1.6731</v>
       </c>
       <c r="K11" t="n">
         <v>113</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0867</v>
+        <v>3.2416</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8776</v>
+        <v>2.8657</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8661</v>
+        <v>1.8584</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6611</v>
+        <v>0.6803</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8776</v>
+        <v>2.8657</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8946</v>
+        <v>1.7845</v>
       </c>
       <c r="G12" t="n">
-        <v>0.983</v>
+        <v>1.0812</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8946</v>
+        <v>1.7845</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8946</v>
+        <v>1.7845</v>
       </c>
       <c r="J12" t="n">
-        <v>0.983</v>
+        <v>1.0812</v>
       </c>
       <c r="K12" t="n">
         <v>64</v>
@@ -989,7 +989,7 @@
         <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8776</v>
+        <v>2.8657</v>
       </c>
       <c r="N12" t="n">
         <v>108</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6481</v>
+        <v>2.7212</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7173</v>
+        <v>1.7647</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5575</v>
+        <v>0.6145</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6481</v>
+        <v>2.7212</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6343</v>
+        <v>1.6098</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0138</v>
+        <v>1.1114</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6343</v>
+        <v>1.6098</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6343</v>
+        <v>1.6098</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0138</v>
+        <v>1.1114</v>
       </c>
       <c r="K13" t="n">
         <v>96</v>
@@ -1035,7 +1035,7 @@
         <v>109</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6481</v>
+        <v>2.7212</v>
       </c>
       <c r="N13" t="n">
         <v>205</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3318</v>
+        <v>2.5104</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5122</v>
+        <v>1.628</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4147</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3318</v>
+        <v>2.5104</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7137</v>
+        <v>1.5584</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6181</v>
+        <v>0.952</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7137</v>
+        <v>1.5584</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7137</v>
+        <v>1.5584</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6181</v>
+        <v>0.952</v>
       </c>
       <c r="K14" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L14" t="n">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3318</v>
+        <v>2.5104</v>
       </c>
       <c r="N14" t="n">
-        <v>125</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2915</v>
+        <v>2.3096</v>
       </c>
       <c r="C15" t="n">
-        <v>1.486</v>
+        <v>1.4978</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3965</v>
+        <v>0.4272</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2915</v>
+        <v>2.3096</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6069</v>
+        <v>1.6211</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6846</v>
+        <v>0.6885</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6069</v>
+        <v>1.6211</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6069</v>
+        <v>1.6211</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6846</v>
+        <v>0.6885</v>
       </c>
       <c r="K15" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2915</v>
+        <v>2.3096</v>
       </c>
       <c r="N15" t="n">
-        <v>233</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1789</v>
+        <v>2.1253</v>
       </c>
       <c r="C16" t="n">
-        <v>1.413</v>
+        <v>1.3783</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3457</v>
+        <v>0.3433</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1789</v>
+        <v>2.1253</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1789</v>
+        <v>2.1253</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1789</v>
+        <v>2.1253</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1789</v>
+        <v>2.1253</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1789</v>
+        <v>2.1253</v>
       </c>
       <c r="N16" t="n">
         <v>64</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1077</v>
+        <v>2.0696</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3668</v>
+        <v>1.3421</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3135</v>
+        <v>0.3179</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1077</v>
+        <v>2.0696</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1471</v>
+        <v>2.0739</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0394</v>
+        <v>-0.0043</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1471</v>
+        <v>2.0739</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1471</v>
+        <v>2.0739</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0394</v>
+        <v>-0.0043</v>
       </c>
       <c r="K17" t="n">
         <v>59</v>
@@ -1219,7 +1219,7 @@
         <v>66</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1077</v>
+        <v>2.0696</v>
       </c>
       <c r="N17" t="n">
         <v>125</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9152</v>
+        <v>1.8844</v>
       </c>
       <c r="C18" t="n">
-        <v>1.242</v>
+        <v>1.222</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2266</v>
+        <v>0.2336</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9152</v>
+        <v>1.8844</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9152</v>
+        <v>1.8844</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9152</v>
+        <v>1.8844</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9152</v>
+        <v>1.8844</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9152</v>
+        <v>1.8844</v>
       </c>
       <c r="N18" t="n">
         <v>55</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6586</v>
+        <v>1.5708</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0756</v>
+        <v>1.0187</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1108</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6586</v>
+        <v>1.5708</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0891</v>
+        <v>2.0314</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4305</v>
+        <v>-0.4606</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0891</v>
+        <v>2.0314</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0891</v>
+        <v>2.0314</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4305</v>
+        <v>-0.4606</v>
       </c>
       <c r="K19" t="n">
         <v>64</v>
@@ -1311,7 +1311,7 @@
         <v>44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6586</v>
+        <v>1.5708</v>
       </c>
       <c r="N19" t="n">
         <v>108</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6075</v>
+        <v>1.5251</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0425</v>
+        <v>0.989</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0877</v>
+        <v>0.0701</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6075</v>
+        <v>1.5251</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0368</v>
+        <v>1.9786</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4293</v>
+        <v>-0.4535</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0368</v>
+        <v>1.9786</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0368</v>
+        <v>1.9786</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4293</v>
+        <v>-0.4535</v>
       </c>
       <c r="K20" t="n">
         <v>64</v>
@@ -1357,7 +1357,7 @@
         <v>38</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6075</v>
+        <v>1.5251</v>
       </c>
       <c r="N20" t="n">
         <v>102</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5776</v>
+        <v>1.4952</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0231</v>
+        <v>0.9696</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0742</v>
+        <v>0.0564</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5776</v>
+        <v>1.4952</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5776</v>
+        <v>1.4952</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5776</v>
+        <v>1.4952</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5776</v>
+        <v>1.4952</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5776</v>
+        <v>1.4952</v>
       </c>
       <c r="N21" t="n">
         <v>69</v>
@@ -1412,400 +1412,400 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4505</v>
+        <v>1.4224</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9407</v>
+        <v>0.9224</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0168</v>
+        <v>0.0233</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4505</v>
+        <v>1.4224</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1006</v>
+        <v>1.4224</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3499</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1006</v>
+        <v>1.4224</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1006</v>
+        <v>1.4224</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3499</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4505</v>
+        <v>1.4224</v>
       </c>
       <c r="N22" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4366</v>
+        <v>1.3966</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9316</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0105</v>
+        <v>0.0116</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4366</v>
+        <v>1.3966</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4366</v>
+        <v>1.0363</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.3603</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4366</v>
+        <v>1.0363</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4366</v>
+        <v>1.0363</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.3603</v>
       </c>
       <c r="K23" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4366</v>
+        <v>1.3966</v>
       </c>
       <c r="N23" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2676</v>
+        <v>1.3038</v>
       </c>
       <c r="C24" t="n">
-        <v>0.822</v>
+        <v>0.8455</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0658</v>
+        <v>-0.0307</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2676</v>
+        <v>1.3038</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1366</v>
+        <v>0.5988</v>
       </c>
       <c r="G24" t="n">
-        <v>0.131</v>
+        <v>0.705</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1366</v>
+        <v>0.5988</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1366</v>
+        <v>0.5988</v>
       </c>
       <c r="J24" t="n">
-        <v>0.131</v>
+        <v>0.705</v>
       </c>
       <c r="K24" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="L24" t="n">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2676</v>
+        <v>1.3038</v>
       </c>
       <c r="N24" t="n">
-        <v>134</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2196</v>
+        <v>1.2713</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7909</v>
+        <v>0.8244</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0455</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2196</v>
+        <v>1.2713</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2196</v>
+        <v>1.1091</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1622</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2196</v>
+        <v>1.1091</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2196</v>
+        <v>1.1091</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.1622</v>
       </c>
       <c r="K25" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2196</v>
+        <v>1.2713</v>
       </c>
       <c r="N25" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2086</v>
+        <v>1.2303</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0924</v>
+        <v>-0.0641</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2086</v>
+        <v>1.2303</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5896</v>
+        <v>1.2303</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6191</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5896</v>
+        <v>1.2303</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5896</v>
+        <v>1.2303</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6191</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L26" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2087</v>
+        <v>1.2303</v>
       </c>
       <c r="N26" t="n">
-        <v>205</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1943</v>
+        <v>1.1603</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7745</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0988</v>
+        <v>-0.096</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1943</v>
+        <v>1.1603</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1943</v>
+        <v>0.5855</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.5748</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1943</v>
+        <v>0.5855</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1943</v>
+        <v>0.5855</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.5748</v>
       </c>
       <c r="K27" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1943</v>
+        <v>1.1603</v>
       </c>
       <c r="N27" t="n">
-        <v>59</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9823</v>
+        <v>1.1405</v>
       </c>
       <c r="C28" t="n">
-        <v>0.637</v>
+        <v>0.7396</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1946</v>
+        <v>-0.105</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9823</v>
+        <v>1.1405</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9823</v>
+        <v>1.1405</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9823</v>
+        <v>1.1405</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9823</v>
+        <v>1.1405</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9823</v>
+        <v>1.1405</v>
       </c>
       <c r="N28" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9418</v>
+        <v>0.9557</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6108</v>
+        <v>0.6198</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2128</v>
+        <v>-0.1891</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9418</v>
+        <v>0.9557</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9418</v>
+        <v>0.9557</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9418</v>
+        <v>0.9557</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9418</v>
+        <v>0.9557</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9418</v>
+        <v>0.9557</v>
       </c>
       <c r="N29" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9301</v>
+        <v>0.9488</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6032</v>
+        <v>0.6153</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2181</v>
+        <v>-0.1923</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9301</v>
+        <v>0.9488</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9301</v>
+        <v>0.9488</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9301</v>
+        <v>0.9488</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9301</v>
+        <v>0.9488</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9301</v>
+        <v>0.9488</v>
       </c>
       <c r="N30" t="n">
         <v>64</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.924</v>
+        <v>0.9099</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5992</v>
+        <v>0.5901</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2209</v>
+        <v>-0.21</v>
       </c>
       <c r="E31" t="n">
-        <v>0.924</v>
+        <v>0.9099</v>
       </c>
       <c r="F31" t="n">
-        <v>0.924</v>
+        <v>0.9099</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.924</v>
+        <v>0.9099</v>
       </c>
       <c r="I31" t="n">
-        <v>0.924</v>
+        <v>0.9099</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.924</v>
+        <v>0.9099</v>
       </c>
       <c r="N31" t="n">
         <v>64</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8592</v>
+        <v>0.8911</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5572</v>
+        <v>0.5779</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2501</v>
+        <v>-0.2186</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8592</v>
+        <v>0.8911</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8592</v>
+        <v>0.8911</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8592</v>
+        <v>0.8911</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8592</v>
+        <v>0.8911</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8592</v>
+        <v>0.8911</v>
       </c>
       <c r="N32" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8292</v>
+        <v>0.8158</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5377</v>
+        <v>0.529</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2637</v>
+        <v>-0.2528</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8292</v>
+        <v>0.8158</v>
       </c>
       <c r="F33" t="n">
-        <v>0.477</v>
+        <v>0.8158</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3522</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.477</v>
+        <v>0.8158</v>
       </c>
       <c r="I33" t="n">
-        <v>0.477</v>
+        <v>0.8158</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3522</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="L33" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8291999999999999</v>
+        <v>0.8158</v>
       </c>
       <c r="N33" t="n">
-        <v>233</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7879</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>0.511</v>
+        <v>0.4965</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2823</v>
+        <v>-0.2757</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7879</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7879</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7879</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7879</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7879</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>59</v>
@@ -2010,323 +2010,323 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7144</v>
+        <v>0.7499</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4633</v>
+        <v>0.4863</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3155</v>
+        <v>-0.2828</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7144</v>
+        <v>0.7499</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5756</v>
+        <v>-1.0629</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1388</v>
+        <v>1.8128</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5756</v>
+        <v>-1.0629</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5756</v>
+        <v>-1.0629</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1388</v>
+        <v>1.8128</v>
       </c>
       <c r="K35" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L35" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7144</v>
+        <v>0.7499</v>
       </c>
       <c r="N35" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7069</v>
+        <v>0.7094</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4584</v>
+        <v>0.46</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3189</v>
+        <v>-0.3013</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7069</v>
+        <v>0.7094</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7069</v>
+        <v>0.5233</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.1861</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7069</v>
+        <v>0.5233</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7069</v>
+        <v>0.5233</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.1861</v>
       </c>
       <c r="K36" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7069</v>
+        <v>0.7094</v>
       </c>
       <c r="N36" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6604</v>
+        <v>0.6838</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4283</v>
+        <v>0.4434</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3399</v>
+        <v>-0.3129</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6604</v>
+        <v>0.6838</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6604</v>
+        <v>0.6838</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6604</v>
+        <v>0.6838</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6604</v>
+        <v>0.6838</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6604</v>
+        <v>0.6838</v>
       </c>
       <c r="N37" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5772</v>
+        <v>0.6407</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3743</v>
+        <v>0.4155</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3774</v>
+        <v>-0.3325</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5772</v>
+        <v>0.6407</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5772</v>
+        <v>0.6407</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5772</v>
+        <v>0.6407</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5772</v>
+        <v>0.6407</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5772</v>
+        <v>0.6407</v>
       </c>
       <c r="N38" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5235</v>
+        <v>0.5642</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3395</v>
+        <v>0.3659</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4017</v>
+        <v>-0.3674</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5235</v>
+        <v>0.5642</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5235</v>
+        <v>0.5642</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5235</v>
+        <v>0.5642</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5235</v>
+        <v>0.5642</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5235</v>
+        <v>0.5642</v>
       </c>
       <c r="N39" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3357</v>
+        <v>0.337</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4043</v>
+        <v>-0.3876</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1062</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>1.6238</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1062</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1062</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>1.6238</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L40" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5175999999999998</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4732</v>
+        <v>0.4831</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3069</v>
+        <v>0.3133</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4244</v>
+        <v>-0.4043</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4732</v>
+        <v>0.4831</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4732</v>
+        <v>-0.5828</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.0659</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4732</v>
+        <v>-0.5828</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4732</v>
+        <v>-0.5828</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1.0659</v>
       </c>
       <c r="K41" t="n">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4732</v>
+        <v>0.4831000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>36</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4703</v>
+        <v>0.4742</v>
       </c>
       <c r="C42" t="n">
-        <v>0.305</v>
+        <v>0.3075</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4257</v>
+        <v>-0.4083</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4703</v>
+        <v>0.4742</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4703</v>
+        <v>0.4742</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4703</v>
+        <v>0.4742</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4703</v>
+        <v>0.4742</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4703</v>
+        <v>0.4742</v>
       </c>
       <c r="N42" t="n">
         <v>64</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3319</v>
+        <v>0.4169</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2152</v>
+        <v>0.2704</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4882</v>
+        <v>-0.4344</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3319</v>
+        <v>0.4169</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3319</v>
+        <v>0.4169</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3319</v>
+        <v>0.4169</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3319</v>
+        <v>0.4169</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3319</v>
+        <v>0.4169</v>
       </c>
       <c r="N43" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3192</v>
+        <v>0.2893</v>
       </c>
       <c r="C44" t="n">
-        <v>0.207</v>
+        <v>0.1876</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4939</v>
+        <v>-0.4925</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3192</v>
+        <v>0.2893</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.6121</v>
+        <v>0.2893</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9313</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.6121</v>
+        <v>0.2893</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6121</v>
+        <v>0.2893</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9313</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="L44" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3192</v>
+        <v>0.2893</v>
       </c>
       <c r="N44" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2003</v>
+        <v>0.1735</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1299</v>
+        <v>0.1125</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5476</v>
+        <v>-0.5452</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2003</v>
+        <v>0.1735</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2003</v>
+        <v>0.1735</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2003</v>
+        <v>0.1735</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2003</v>
+        <v>0.1735</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2003</v>
+        <v>0.1735</v>
       </c>
       <c r="N45" t="n">
         <v>55</v>
@@ -2516,967 +2516,967 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1681</v>
+        <v>0.1724</v>
       </c>
       <c r="C46" t="n">
-        <v>0.109</v>
+        <v>0.1118</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5621</v>
+        <v>-0.5457</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1681</v>
+        <v>0.1724</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1681</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1681</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1681</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1681</v>
+        <v>0.1724</v>
       </c>
       <c r="N46" t="n">
-        <v>59</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0788</v>
+        <v>0.1323</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0511</v>
+        <v>0.0858</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6024</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0788</v>
+        <v>0.1323</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0788</v>
+        <v>0.1323</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0788</v>
+        <v>0.1323</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0788</v>
+        <v>0.1323</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0788</v>
+        <v>0.1323</v>
       </c>
       <c r="N47" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>0.08459999999999999</v>
+      </c>
+      <c r="C48" t="n">
         <v>0.0549</v>
       </c>
-      <c r="C48" t="n">
-        <v>0.0356</v>
-      </c>
       <c r="D48" t="n">
-        <v>-0.6132</v>
+        <v>-0.5857</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0549</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0549</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0549</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0549</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0549</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0184</v>
+        <v>0.0412</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0119</v>
+        <v>0.0267</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6297</v>
+        <v>-0.6054</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0184</v>
+        <v>0.0412</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0184</v>
+        <v>0.0412</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0184</v>
+        <v>0.0412</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0184</v>
+        <v>0.0412</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0184</v>
+        <v>0.0412</v>
       </c>
       <c r="N49" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0177</v>
+        <v>-0.0103</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0115</v>
+        <v>-0.0067</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.63</v>
+        <v>-0.6289</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0177</v>
+        <v>-0.0103</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.5684</v>
+        <v>-0.0103</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5861</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.5684</v>
+        <v>-0.0103</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5684</v>
+        <v>-0.0103</v>
       </c>
       <c r="J50" t="n">
-        <v>0.5861</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="L50" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01769999999999994</v>
+        <v>-0.0103</v>
       </c>
       <c r="N50" t="n">
-        <v>214</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0581</v>
+        <v>-0.0569</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0377</v>
+        <v>-0.0369</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6642</v>
+        <v>-0.6501</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0581</v>
+        <v>-0.0569</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0581</v>
+        <v>0.3428</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.3997</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0581</v>
+        <v>0.3428</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0581</v>
+        <v>0.3428</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.3997</v>
       </c>
       <c r="K51" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0581</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0781</v>
+        <v>-0.0675</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0506</v>
+        <v>-0.0438</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6733</v>
+        <v>-0.6549</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0781</v>
+        <v>-0.0675</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0781</v>
+        <v>-0.0675</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0781</v>
+        <v>-0.0675</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0781</v>
+        <v>-0.0675</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0781</v>
+        <v>-0.0675</v>
       </c>
       <c r="N52" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1164</v>
+        <v>-0.1149</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0755</v>
+        <v>-0.0745</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6906</v>
+        <v>-0.6765</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1164</v>
+        <v>-0.1149</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1164</v>
+        <v>-0.1149</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1164</v>
+        <v>-0.1149</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1164</v>
+        <v>-0.1149</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1164</v>
+        <v>-0.1149</v>
       </c>
       <c r="N53" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1269</v>
+        <v>-0.1186</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0823</v>
+        <v>-0.0769</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6953</v>
+        <v>-0.6782</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1269</v>
+        <v>-0.1186</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2691</v>
+        <v>-0.1186</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.396</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2691</v>
+        <v>-0.1186</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2691</v>
+        <v>-0.1186</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.396</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1269</v>
+        <v>-0.1186</v>
       </c>
       <c r="N54" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1297</v>
+        <v>-0.119</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0772</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6966</v>
+        <v>-0.6784</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1297</v>
+        <v>-0.119</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1297</v>
+        <v>-0.119</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1297</v>
+        <v>-0.119</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1297</v>
+        <v>-0.119</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1297</v>
+        <v>-0.119</v>
       </c>
       <c r="N55" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1457</v>
+        <v>-0.142</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0945</v>
+        <v>-0.0921</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7038</v>
+        <v>-0.6888</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1457</v>
+        <v>-0.142</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1457</v>
+        <v>-0.5243</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.3823</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1457</v>
+        <v>-0.5243</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1457</v>
+        <v>-0.5243</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.3823</v>
       </c>
       <c r="K56" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.1457</v>
+        <v>-0.142</v>
       </c>
       <c r="N56" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.163</v>
+        <v>-0.1596</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1057</v>
+        <v>-0.1035</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7116</v>
+        <v>-0.6969</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.163</v>
+        <v>-0.1596</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4778</v>
+        <v>-0.1596</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.6408</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4778</v>
+        <v>-0.1596</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4778</v>
+        <v>-0.1596</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.6408</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="L57" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.163</v>
+        <v>-0.1596</v>
       </c>
       <c r="N57" t="n">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2077</v>
+        <v>-0.1596</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1347</v>
+        <v>-0.1035</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7318</v>
+        <v>-0.6969</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2077</v>
+        <v>-0.1596</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2077</v>
+        <v>-0.4417</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2077</v>
+        <v>-0.4417</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2077</v>
+        <v>-0.4417</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="K58" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2077</v>
+        <v>-0.1596</v>
       </c>
       <c r="N58" t="n">
-        <v>42</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2184</v>
+        <v>-0.2201</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1416</v>
+        <v>-0.1427</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7366</v>
+        <v>-0.7244</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2184</v>
+        <v>-0.2201</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2184</v>
+        <v>-0.2201</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2184</v>
+        <v>-0.2201</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2184</v>
+        <v>-0.2201</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2184</v>
+        <v>-0.2201</v>
       </c>
       <c r="N59" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2525</v>
+        <v>-0.2365</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1637</v>
+        <v>-0.1534</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.752</v>
+        <v>-0.7319</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2525</v>
+        <v>-0.2365</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4583</v>
+        <v>0.4483</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2058</v>
+        <v>-0.6848</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4583</v>
+        <v>0.4483</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4583</v>
+        <v>0.4483</v>
       </c>
       <c r="J60" t="n">
-        <v>0.2058</v>
+        <v>-0.6848</v>
       </c>
       <c r="K60" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L60" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2524999999999999</v>
+        <v>-0.2365</v>
       </c>
       <c r="N60" t="n">
-        <v>108</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2827</v>
+        <v>-0.2403</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1833</v>
+        <v>-0.1558</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7336</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2827</v>
+        <v>-0.2403</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2827</v>
+        <v>-0.2403</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2827</v>
+        <v>-0.2403</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2827</v>
+        <v>-0.2403</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2827</v>
+        <v>-0.2403</v>
       </c>
       <c r="N61" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3007</v>
+        <v>-0.2884</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.195</v>
+        <v>-0.187</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7738</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3007</v>
+        <v>-0.2884</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6232</v>
+        <v>-0.2884</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3225</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6232</v>
+        <v>-0.2884</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6232</v>
+        <v>-0.2884</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3225</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L62" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3007</v>
+        <v>-0.2884</v>
       </c>
       <c r="N62" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3254</v>
+        <v>-0.2988</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.211</v>
+        <v>-0.1938</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7849</v>
+        <v>-0.7602</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3254</v>
+        <v>-0.2988</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3254</v>
+        <v>0.6269</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-0.9257</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3254</v>
+        <v>0.6269</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3254</v>
+        <v>0.6269</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>-0.9257</v>
       </c>
       <c r="K63" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3254</v>
+        <v>-0.2988</v>
       </c>
       <c r="N63" t="n">
-        <v>69</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3364</v>
+        <v>-0.3339</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2182</v>
+        <v>-0.2165</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7899</v>
+        <v>-0.7762</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3364</v>
+        <v>-0.3339</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3364</v>
+        <v>-0.3339</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3364</v>
+        <v>-0.3339</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3364</v>
+        <v>-0.3339</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3364</v>
+        <v>-0.3339</v>
       </c>
       <c r="N64" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.363</v>
+        <v>-0.3595</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2354</v>
+        <v>-0.2331</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.7879</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.363</v>
+        <v>-0.3595</v>
       </c>
       <c r="F65" t="n">
-        <v>0.637</v>
+        <v>-0.3595</v>
       </c>
       <c r="G65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.637</v>
+        <v>-0.3595</v>
       </c>
       <c r="I65" t="n">
-        <v>0.637</v>
+        <v>-0.3595</v>
       </c>
       <c r="J65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L65" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.363</v>
+        <v>-0.3595</v>
       </c>
       <c r="N65" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4148</v>
+        <v>-0.3656</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.269</v>
+        <v>-0.2371</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8253</v>
+        <v>-0.7906</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4148</v>
+        <v>-0.3656</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6344</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.0776</v>
+        <v>-1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6344</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6344</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.0776</v>
+        <v>-1</v>
       </c>
       <c r="K66" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L66" t="n">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4147999999999999</v>
+        <v>-0.3656</v>
       </c>
       <c r="N66" t="n">
-        <v>211</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4282</v>
+        <v>-0.4346</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2777</v>
+        <v>-0.2818</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8313</v>
+        <v>-0.822</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4282</v>
+        <v>-0.4346</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4282</v>
+        <v>-0.4346</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4282</v>
+        <v>-0.4346</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4282</v>
+        <v>-0.4346</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.4282</v>
+        <v>-0.4346</v>
       </c>
       <c r="N67" t="n">
         <v>59</v>
@@ -3532,31 +3532,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4583</v>
+        <v>-0.4998</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2972</v>
+        <v>-0.3241</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8449</v>
+        <v>-0.8517</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4583</v>
+        <v>-0.4998</v>
       </c>
       <c r="F68" t="n">
-        <v>0.35</v>
+        <v>0.3302</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.8083</v>
+        <v>-0.83</v>
       </c>
       <c r="H68" t="n">
-        <v>0.35</v>
+        <v>0.3302</v>
       </c>
       <c r="I68" t="n">
-        <v>0.35</v>
+        <v>0.3302</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.8083</v>
+        <v>-0.83</v>
       </c>
       <c r="K68" t="n">
         <v>64</v>
@@ -3565,7 +3565,7 @@
         <v>38</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4583</v>
+        <v>-0.4998</v>
       </c>
       <c r="N68" t="n">
         <v>102</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5667</v>
+        <v>-0.5975</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3675</v>
+        <v>-0.3875</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8939</v>
+        <v>-0.8962</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5667</v>
+        <v>-0.5975</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5667</v>
+        <v>-0.5975</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5667</v>
+        <v>-0.5975</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5667</v>
+        <v>-0.5975</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5667</v>
+        <v>-0.5975</v>
       </c>
       <c r="N69" t="n">
         <v>36</v>
@@ -3624,31 +3624,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6414</v>
+        <v>-0.6219</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4159</v>
+        <v>-0.4033</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9276</v>
+        <v>-0.9073</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6414</v>
+        <v>-0.6219</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5938</v>
+        <v>-0.5679</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.0476</v>
+        <v>-0.054</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5938</v>
+        <v>-0.5679</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5938</v>
+        <v>-0.5679</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.0476</v>
+        <v>-0.054</v>
       </c>
       <c r="K70" t="n">
         <v>64</v>
@@ -3657,7 +3657,7 @@
         <v>44</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6414</v>
+        <v>-0.6219</v>
       </c>
       <c r="N70" t="n">
         <v>108</v>
@@ -3666,93 +3666,93 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6548</v>
+        <v>-0.6646</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4246</v>
+        <v>-0.431</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9336</v>
+        <v>-0.9267</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6548</v>
+        <v>-0.6646</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6548</v>
+        <v>-0.2028</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-0.4618</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6548</v>
+        <v>-0.2028</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6548</v>
+        <v>-0.2028</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>-0.4618</v>
       </c>
       <c r="K71" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6548</v>
+        <v>-0.6646</v>
       </c>
       <c r="N71" t="n">
-        <v>55</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6684</v>
+        <v>-0.6673</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4335</v>
+        <v>-0.4327</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9398</v>
+        <v>-0.928</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6684</v>
+        <v>-0.6673</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.217</v>
+        <v>-0.6673</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.4514</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.217</v>
+        <v>-0.6673</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.217</v>
+        <v>-0.6673</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.4514</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L72" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6684</v>
+        <v>-0.6673</v>
       </c>
       <c r="N72" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73">
@@ -3762,31 +3762,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7074</v>
+        <v>-0.735</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4588</v>
+        <v>-0.4766</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9574</v>
+        <v>-0.9588</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7074</v>
+        <v>-0.735</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6539</v>
+        <v>0.6562</v>
       </c>
       <c r="G73" t="n">
-        <v>-1.3614</v>
+        <v>-1.3912</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6539</v>
+        <v>0.6562</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6539</v>
+        <v>0.6562</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.3614</v>
+        <v>-1.3912</v>
       </c>
       <c r="K73" t="n">
         <v>96</v>
@@ -3795,7 +3795,7 @@
         <v>109</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7074999999999999</v>
+        <v>-0.735</v>
       </c>
       <c r="N73" t="n">
         <v>205</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7343</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4762</v>
+        <v>-0.4886</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9695</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7343</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7343</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7343</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7343</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7343</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="N74" t="n">
         <v>59</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7477</v>
+        <v>-0.773</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4849</v>
+        <v>-0.5013</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9756</v>
+        <v>-0.9761</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7477</v>
+        <v>-0.773</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7477</v>
+        <v>-0.773</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7477</v>
+        <v>-0.773</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7477</v>
+        <v>-0.773</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.7477</v>
+        <v>-0.773</v>
       </c>
       <c r="N75" t="n">
         <v>36</v>
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8305</v>
+        <v>-0.7982</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5386</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0129</v>
+        <v>-0.9876</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.8305</v>
+        <v>-0.7982</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1193</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.735</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.1193</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1193</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.735</v>
       </c>
       <c r="K76" t="n">
         <v>64</v>
@@ -3933,7 +3933,7 @@
         <v>44</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.8305</v>
+        <v>-0.7982</v>
       </c>
       <c r="N76" t="n">
         <v>108</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.8383</v>
+        <v>-0.8457</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5436</v>
+        <v>-0.5484</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0165</v>
+        <v>-1.0092</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.8383</v>
+        <v>-0.8457</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8383</v>
+        <v>-0.8457</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8383</v>
+        <v>-0.8457</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.8383</v>
+        <v>-0.8457</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.8383</v>
+        <v>-0.8457</v>
       </c>
       <c r="N77" t="n">
         <v>64</v>
@@ -3992,31 +3992,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9079</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.607</v>
+        <v>-0.5888</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0606</v>
+        <v>-1.0375</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9079</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.8652</v>
+        <v>-0.8045</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.0708</v>
+        <v>-0.1034</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.8652</v>
+        <v>-0.8045</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.8652</v>
+        <v>-0.8045</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.0708</v>
+        <v>-0.1034</v>
       </c>
       <c r="K78" t="n">
         <v>64</v>
@@ -4025,7 +4025,7 @@
         <v>38</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.9359999999999999</v>
+        <v>-0.9079</v>
       </c>
       <c r="N78" t="n">
         <v>102</v>
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.0119</v>
+        <v>-0.9295</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6562</v>
+        <v>-0.6028</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0948</v>
+        <v>-1.0473</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.0119</v>
+        <v>-0.9295</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.9851</v>
+        <v>-0.9</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.0268</v>
+        <v>-0.0295</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.9851</v>
+        <v>-0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.9851</v>
+        <v>-0.9</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.0268</v>
+        <v>-0.0295</v>
       </c>
       <c r="K79" t="n">
         <v>59</v>
@@ -4071,7 +4071,7 @@
         <v>66</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.0119</v>
+        <v>-0.9295</v>
       </c>
       <c r="N79" t="n">
         <v>125</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.3674</v>
+        <v>-1.1707</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.8868</v>
+        <v>-0.7592</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2553</v>
+        <v>-1.1571</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.3674</v>
+        <v>-1.1707</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.8117</v>
+        <v>-0.7633</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5557</v>
+        <v>-0.4074</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.8117</v>
+        <v>-0.7633</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.8117</v>
+        <v>-0.7633</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.5557</v>
+        <v>-0.4074</v>
       </c>
       <c r="K80" t="n">
         <v>55</v>
@@ -4117,7 +4117,7 @@
         <v>156</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.3674</v>
+        <v>-1.1707</v>
       </c>
       <c r="N80" t="n">
         <v>211</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1208</v>
+        <v>-1.9252</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.3753</v>
+        <v>-1.2485</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5954</v>
+        <v>-1.5006</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1208</v>
+        <v>-1.9252</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.799</v>
+        <v>-1.6894</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.3218</v>
+        <v>-0.2357</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.799</v>
+        <v>-1.6894</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.799</v>
+        <v>-1.6894</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.3218</v>
+        <v>-0.2357</v>
       </c>
       <c r="K81" t="n">
         <v>113</v>
@@ -4163,7 +4163,7 @@
         <v>101</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.1208</v>
+        <v>-1.9251</v>
       </c>
       <c r="N81" t="n">
         <v>214</v>
@@ -4269,10 +4269,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5405</v>
+        <v>1.6627</v>
       </c>
       <c r="J2" t="n">
-        <v>46.215</v>
+        <v>49.881</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1361</v>
+        <v>0.1495</v>
       </c>
       <c r="J3" t="n">
-        <v>4.083</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0646</v>
+        <v>0.0796</v>
       </c>
       <c r="J4" t="n">
-        <v>1.938</v>
+        <v>2.388</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1272</v>
+        <v>-0.1226</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.816</v>
+        <v>-3.678</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.606</v>
+        <v>-0.5669</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.18</v>
+        <v>-17.007</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8472</v>
+        <v>0.8054</v>
       </c>
       <c r="J7" t="n">
-        <v>25.416</v>
+        <v>24.162</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7306</v>
+        <v>0.701</v>
       </c>
       <c r="J8" t="n">
-        <v>21.918</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2014</v>
+        <v>0.2099</v>
       </c>
       <c r="J9" t="n">
-        <v>6.042</v>
+        <v>6.297</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3849</v>
+        <v>-0.3944</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.547</v>
+        <v>-11.832</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4851</v>
+        <v>-0.4902</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.553</v>
+        <v>-14.706</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2239</v>
+        <v>1.2543</v>
       </c>
       <c r="J12" t="n">
-        <v>26.9258</v>
+        <v>27.5946</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="J13" t="n">
-        <v>13.695</v>
+        <v>13.1582</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3173</v>
+        <v>0.3204</v>
       </c>
       <c r="J14" t="n">
-        <v>6.9806</v>
+        <v>7.0488</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3864</v>
+        <v>-0.3682</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.5008</v>
+        <v>-8.1004</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3864</v>
+        <v>-0.3682</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.5008</v>
+        <v>-8.1004</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.39</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7935</v>
+        <v>0.7528</v>
       </c>
       <c r="J17" t="n">
-        <v>17.457</v>
+        <v>16.5616</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0168</v>
+        <v>-0.0224</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3696</v>
+        <v>-0.4928</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1067</v>
+        <v>-0.1198</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3474</v>
+        <v>-2.6356</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1507</v>
+        <v>-0.1651</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.3154</v>
+        <v>-3.6322</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.58</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4424</v>
+        <v>-0.4506</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.732799999999999</v>
+        <v>-9.9132</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>2.71</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J22" t="n">
-        <v>31.7577</v>
+        <v>31.3701</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5099</v>
+        <v>0.5105</v>
       </c>
       <c r="J23" t="n">
-        <v>8.6683</v>
+        <v>8.6785</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.18</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4599</v>
+        <v>0.4655</v>
       </c>
       <c r="J24" t="n">
-        <v>7.8183</v>
+        <v>7.9135</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2178</v>
+        <v>0.2446</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7026</v>
+        <v>4.1582</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1277</v>
+        <v>0.1602</v>
       </c>
       <c r="J26" t="n">
-        <v>2.1709</v>
+        <v>2.7234</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.45</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9673</v>
+        <v>0.9011</v>
       </c>
       <c r="J27" t="n">
-        <v>16.4441</v>
+        <v>15.3187</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2186</v>
+        <v>-0.2366</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.7162</v>
+        <v>-4.0222</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.79</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2283</v>
+        <v>-0.2462</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.8811</v>
+        <v>-4.1854</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4092</v>
+        <v>-0.4214</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.9564</v>
+        <v>-7.1638</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4832</v>
+        <v>-0.4915</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.214399999999999</v>
+        <v>-8.355499999999999</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.83</v>
       </c>
       <c r="I32" t="n">
-        <v>0.963</v>
+        <v>0.9413</v>
       </c>
       <c r="J32" t="n">
-        <v>21.186</v>
+        <v>20.7086</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3618</v>
+        <v>0.3778</v>
       </c>
       <c r="J33" t="n">
-        <v>7.9596</v>
+        <v>8.3116</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3386</v>
+        <v>0.3553</v>
       </c>
       <c r="J34" t="n">
-        <v>7.4492</v>
+        <v>7.8166</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04</v>
+        <v>0.0552</v>
       </c>
       <c r="J35" t="n">
-        <v>0.88</v>
+        <v>1.2144</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3387</v>
+        <v>-0.3461</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.4514</v>
+        <v>-7.6142</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.75</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0246</v>
+        <v>0.9825</v>
       </c>
       <c r="J37" t="n">
-        <v>22.5412</v>
+        <v>21.615</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>0.98</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0344</v>
+        <v>-0.0416</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7568</v>
+        <v>-0.9152</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1091</v>
+        <v>-0.1217</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.4002</v>
+        <v>-2.6774</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3618</v>
+        <v>-0.3729</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.9596</v>
+        <v>-8.203799999999999</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4632</v>
+        <v>-0.47</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.1904</v>
+        <v>-10.34</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>0.87</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0522</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-1.4464</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>0.71</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2434</v>
+        <v>-0.2736</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.8944</v>
+        <v>-4.3776</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.43</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5165</v>
+        <v>-0.5302</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.263999999999999</v>
+        <v>-8.4832</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.34</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.6108</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.668799999999999</v>
+        <v>-9.7728</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.29</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6538</v>
+        <v>-0.6559</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.4608</v>
+        <v>-10.4944</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>2.59</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J47" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.75</v>
       </c>
       <c r="I48" t="n">
-        <v>1.3586</v>
+        <v>1.352</v>
       </c>
       <c r="J48" t="n">
-        <v>21.7376</v>
+        <v>21.632</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.56</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1484</v>
+        <v>1.1254</v>
       </c>
       <c r="J49" t="n">
-        <v>18.3744</v>
+        <v>18.0064</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.43</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9789</v>
+        <v>0.9378</v>
       </c>
       <c r="J50" t="n">
-        <v>15.6624</v>
+        <v>15.0048</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>1.07</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1156</v>
+        <v>0.159</v>
       </c>
       <c r="J51" t="n">
-        <v>1.8496</v>
+        <v>2.544</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>0.97</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0202</v>
+        <v>-0.0352</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.3232</v>
+        <v>-0.5632</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0479</v>
+        <v>-0.0645</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.7664</v>
+        <v>-1.032</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1749</v>
+        <v>-0.1939</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.7984</v>
+        <v>-3.1024</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2711</v>
+        <v>-0.2895</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.3376</v>
+        <v>-4.632</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.45</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.542</v>
+        <v>-0.5476</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.672000000000001</v>
+        <v>-8.7616</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>2.08</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7774</v>
+        <v>1.7836</v>
       </c>
       <c r="J57" t="n">
-        <v>28.4384</v>
+        <v>28.5376</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.46</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0551</v>
+        <v>1.0146</v>
       </c>
       <c r="J58" t="n">
-        <v>16.8816</v>
+        <v>16.2336</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.28</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7101</v>
+        <v>0.6868</v>
       </c>
       <c r="J59" t="n">
-        <v>11.3616</v>
+        <v>10.9888</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2844</v>
+        <v>0.3039</v>
       </c>
       <c r="J60" t="n">
-        <v>4.5504</v>
+        <v>4.8624</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1982</v>
+        <v>0.2241</v>
       </c>
       <c r="J61" t="n">
-        <v>3.1712</v>
+        <v>3.5856</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.58</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9402</v>
+        <v>1.0399</v>
       </c>
       <c r="J62" t="n">
-        <v>17.8638</v>
+        <v>19.7581</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.57</v>
       </c>
       <c r="I63" t="n">
-        <v>0.928</v>
+        <v>1.0268</v>
       </c>
       <c r="J63" t="n">
-        <v>17.632</v>
+        <v>19.5092</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4677</v>
+        <v>0.5216</v>
       </c>
       <c r="J64" t="n">
-        <v>8.8863</v>
+        <v>9.910399999999999</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1.14</v>
       </c>
       <c r="I65" t="n">
-        <v>0.363</v>
+        <v>0.3906</v>
       </c>
       <c r="J65" t="n">
-        <v>6.897</v>
+        <v>7.4214</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3268</v>
+        <v>0.3414</v>
       </c>
       <c r="J66" t="n">
-        <v>6.2092</v>
+        <v>6.4866</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0333</v>
+        <v>0.0241</v>
       </c>
       <c r="J67" t="n">
-        <v>0.6327</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1314</v>
+        <v>-0.1476</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.4966</v>
+        <v>-2.8044</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1421</v>
+        <v>-0.1585</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.6999</v>
+        <v>-3.0115</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2021</v>
+        <v>-0.2194</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.8399</v>
+        <v>-4.1686</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.71</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3093</v>
+        <v>-0.3248</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.8767</v>
+        <v>-6.1712</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9544</v>
+        <v>1.0432</v>
       </c>
       <c r="J72" t="n">
-        <v>22.9056</v>
+        <v>25.0368</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6453</v>
       </c>
       <c r="J73" t="n">
-        <v>14.0688</v>
+        <v>15.4872</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0771</v>
+        <v>0.0883</v>
       </c>
       <c r="J74" t="n">
-        <v>1.8504</v>
+        <v>2.1192</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6449</v>
+        <v>-0.6041</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.4776</v>
+        <v>-14.4984</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6964</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.7136</v>
+        <v>-15.5928</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6813</v>
+        <v>0.7607</v>
       </c>
       <c r="J77" t="n">
-        <v>16.3512</v>
+        <v>18.2568</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2599</v>
+        <v>0.267</v>
       </c>
       <c r="J78" t="n">
-        <v>6.2376</v>
+        <v>6.408</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1373</v>
+        <v>-0.1493</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.2952</v>
+        <v>-3.5832</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1593</v>
+        <v>-0.1718</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.8232</v>
+        <v>-4.1232</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2817</v>
+        <v>-0.2939</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.7608</v>
+        <v>-7.0536</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9283</v>
+        <v>1.0247</v>
       </c>
       <c r="J82" t="n">
-        <v>19.4943</v>
+        <v>21.5187</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.44</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7773</v>
+        <v>0.8622</v>
       </c>
       <c r="J83" t="n">
-        <v>16.3233</v>
+        <v>18.1062</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5303</v>
+        <v>0.59</v>
       </c>
       <c r="J84" t="n">
-        <v>11.1363</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1036</v>
+        <v>0.1269</v>
       </c>
       <c r="J85" t="n">
-        <v>2.1756</v>
+        <v>2.6649</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>1.03</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0688</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>1.4448</v>
+        <v>1.9572</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.36</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5661</v>
+        <v>0.6292</v>
       </c>
       <c r="J87" t="n">
-        <v>11.8881</v>
+        <v>13.2132</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5357</v>
+        <v>0.5948</v>
       </c>
       <c r="J88" t="n">
-        <v>11.2497</v>
+        <v>12.4908</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0982</v>
+        <v>-0.1101</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.0622</v>
+        <v>-2.3121</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1859</v>
+        <v>-0.1999</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.9039</v>
+        <v>-4.1979</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.44</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5709</v>
+        <v>-0.5718</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.9889</v>
+        <v>-12.0078</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.45</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5262</v>
+        <v>0.5889</v>
       </c>
       <c r="J92" t="n">
-        <v>11.5764</v>
+        <v>12.9558</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4202</v>
+        <v>0.4663</v>
       </c>
       <c r="J93" t="n">
-        <v>9.244400000000001</v>
+        <v>10.2586</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0376</v>
+        <v>-0.0439</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.8272</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1473</v>
+        <v>-0.1598</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.2406</v>
+        <v>-3.5156</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.46</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5563</v>
+        <v>-0.5576</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.2386</v>
+        <v>-12.2672</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>0.469</v>
+        <v>0.5339</v>
       </c>
       <c r="J97" t="n">
-        <v>10.318</v>
+        <v>11.7458</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3679</v>
+        <v>0.4047</v>
       </c>
       <c r="J98" t="n">
-        <v>8.0938</v>
+        <v>8.9034</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>1.28</v>
       </c>
       <c r="I99" t="n">
-        <v>0.361</v>
+        <v>0.3937</v>
       </c>
       <c r="J99" t="n">
-        <v>7.942</v>
+        <v>8.6614</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0635</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>1.397</v>
+        <v>1.7226</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2472</v>
+        <v>-0.2567</v>
       </c>
       <c r="J101" t="n">
-        <v>-5.4384</v>
+        <v>-5.6474</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>2.29</v>
       </c>
       <c r="I102" t="n">
-        <v>1.812</v>
+        <v>1.9448</v>
       </c>
       <c r="J102" t="n">
-        <v>36.24</v>
+        <v>38.896</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.2</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4657</v>
+        <v>0.5161</v>
       </c>
       <c r="J103" t="n">
-        <v>9.314</v>
+        <v>10.322</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2877</v>
+        <v>-0.2713</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.754</v>
+        <v>-5.426</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4654</v>
+        <v>-0.4358</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.308</v>
+        <v>-8.715999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7055</v>
+        <v>-0.6515</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.11</v>
+        <v>-13.03</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.52</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7268</v>
+        <v>0.8082</v>
       </c>
       <c r="J107" t="n">
-        <v>14.536</v>
+        <v>16.164</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4013</v>
+        <v>0.4376</v>
       </c>
       <c r="J108" t="n">
-        <v>8.026</v>
+        <v>8.752000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.85</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1847</v>
+        <v>-0.1989</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.694</v>
+        <v>-3.978</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3425</v>
+        <v>-0.3543</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.85</v>
+        <v>-7.086</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4263</v>
+        <v>-0.4349</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.526</v>
+        <v>-8.698</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8672</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>19.0784</v>
+        <v>20.9902</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.24</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5295</v>
+        <v>0.5858</v>
       </c>
       <c r="J113" t="n">
-        <v>11.649</v>
+        <v>12.8876</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.22</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5011</v>
+        <v>0.554</v>
       </c>
       <c r="J114" t="n">
-        <v>11.0242</v>
+        <v>12.188</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1642</v>
+        <v>0.1777</v>
       </c>
       <c r="J115" t="n">
-        <v>3.6124</v>
+        <v>3.9094</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.76</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7654</v>
+        <v>-0.7073</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.8388</v>
+        <v>-15.5606</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5571</v>
+        <v>0.6187</v>
       </c>
       <c r="J117" t="n">
-        <v>12.2562</v>
+        <v>13.6114</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2103</v>
+        <v>0.2163</v>
       </c>
       <c r="J118" t="n">
-        <v>4.6266</v>
+        <v>4.7586</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.95</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0738</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.6236</v>
+        <v>-1.859</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1643</v>
+        <v>-0.1782</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.6146</v>
+        <v>-3.9204</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.64</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.58</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3188</v>
+        <v>0.3164</v>
       </c>
       <c r="J122" t="n">
-        <v>6.6948</v>
+        <v>6.6444</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0857</v>
+        <v>-0.1006</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.7997</v>
+        <v>-2.1126</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1623</v>
+        <v>-0.1793</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.4083</v>
+        <v>-3.7653</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.79</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2315</v>
+        <v>-0.2487</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.8615</v>
+        <v>-5.2227</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4589</v>
+        <v>-0.4681</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.636900000000001</v>
+        <v>-9.8301</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.69</v>
       </c>
       <c r="I127" t="n">
-        <v>0.619</v>
+        <v>0.7104</v>
       </c>
       <c r="J127" t="n">
-        <v>12.999</v>
+        <v>14.9184</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4357</v>
+        <v>0.4962</v>
       </c>
       <c r="J128" t="n">
-        <v>9.149699999999999</v>
+        <v>10.4202</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.25</v>
       </c>
       <c r="I129" t="n">
-        <v>0.333</v>
+        <v>0.3541</v>
       </c>
       <c r="J129" t="n">
-        <v>6.993</v>
+        <v>7.4361</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.11</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1617</v>
+        <v>0.181</v>
       </c>
       <c r="J130" t="n">
-        <v>3.3957</v>
+        <v>3.801</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3213</v>
+        <v>-0.3288</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.7473</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9437</v>
+        <v>1.0336</v>
       </c>
       <c r="J132" t="n">
-        <v>21.7051</v>
+        <v>23.7728</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.39</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7449</v>
+        <v>0.8203</v>
       </c>
       <c r="J133" t="n">
-        <v>17.1327</v>
+        <v>18.8669</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I134" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="J134" t="n">
-        <v>1.5893</v>
+        <v>1.9044</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3811</v>
+        <v>-0.3644</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.7653</v>
+        <v>-8.3812</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8554</v>
+        <v>-0.788</v>
       </c>
       <c r="J136" t="n">
-        <v>-19.6742</v>
+        <v>-18.124</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.61</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7945</v>
+        <v>0.8861</v>
       </c>
       <c r="J137" t="n">
-        <v>18.2735</v>
+        <v>20.3803</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2599</v>
+        <v>0.267</v>
       </c>
       <c r="J138" t="n">
-        <v>5.9777</v>
+        <v>6.141</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1147</v>
+        <v>-0.126</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.6381</v>
+        <v>-2.898</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.77</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.272</v>
+        <v>-0.2843</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.256</v>
+        <v>-6.5389</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3108</v>
+        <v>-0.3223</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.1484</v>
+        <v>-7.4129</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5013</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>10.026</v>
+        <v>10.856</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1948</v>
+        <v>-0.2138</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.896</v>
+        <v>-4.276</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>0.77</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2422</v>
+        <v>-0.2612</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.844</v>
+        <v>-5.224</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4027</v>
+        <v>-0.4163</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.054</v>
+        <v>-8.326000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4955</v>
+        <v>-0.5041</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.91</v>
+        <v>-10.082</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.89</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2991</v>
+        <v>1.4211</v>
       </c>
       <c r="J147" t="n">
-        <v>25.982</v>
+        <v>28.422</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.38</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7678</v>
       </c>
       <c r="J148" t="n">
-        <v>13.76</v>
+        <v>15.356</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>1.3</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5871</v>
+        <v>0.656</v>
       </c>
       <c r="J149" t="n">
-        <v>11.742</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>1.2</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4487</v>
+        <v>0.5014</v>
       </c>
       <c r="J150" t="n">
-        <v>8.974</v>
+        <v>10.028</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0467</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.554</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.53</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7013</v>
+        <v>0.7862</v>
       </c>
       <c r="J152" t="n">
-        <v>16.8312</v>
+        <v>18.8688</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.3</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4817</v>
+        <v>0.5384</v>
       </c>
       <c r="J153" t="n">
-        <v>11.5608</v>
+        <v>12.9216</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1472</v>
+        <v>0.1598</v>
       </c>
       <c r="J154" t="n">
-        <v>3.5328</v>
+        <v>3.8352</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1883</v>
+        <v>-0.1994</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.5192</v>
+        <v>-4.7856</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3085</v>
+        <v>-0.3187</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.404</v>
+        <v>-7.6488</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I157" t="n">
-        <v>0.644</v>
+        <v>0.7055</v>
       </c>
       <c r="J157" t="n">
-        <v>15.456</v>
+        <v>16.932</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3544</v>
+        <v>0.3621</v>
       </c>
       <c r="J158" t="n">
-        <v>8.505599999999999</v>
+        <v>8.6904</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.05</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1906</v>
+        <v>0.1957</v>
       </c>
       <c r="J159" t="n">
-        <v>4.5744</v>
+        <v>4.6968</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.99</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0589</v>
+        <v>-0.0625</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.4136</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.68</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9302</v>
+        <v>-0.8568</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.3248</v>
+        <v>-20.5632</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1834</v>
+        <v>0.167</v>
       </c>
       <c r="J162" t="n">
-        <v>3.1178</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0504</v>
+        <v>-0.0698</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.8568</v>
+        <v>-1.1866</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2288</v>
+        <v>-0.2488</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.8896</v>
+        <v>-4.2296</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.406</v>
+        <v>-0.4205</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.902</v>
+        <v>-7.1485</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.39</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5916</v>
+        <v>-0.5945</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.0572</v>
+        <v>-10.1065</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>2.73</v>
       </c>
       <c r="I167" t="n">
-        <v>2.2001</v>
+        <v>2.353</v>
       </c>
       <c r="J167" t="n">
-        <v>37.4017</v>
+        <v>40.001</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.25</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5103</v>
+        <v>0.5728</v>
       </c>
       <c r="J168" t="n">
-        <v>8.6751</v>
+        <v>9.7376</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4245</v>
+        <v>0.4765</v>
       </c>
       <c r="J169" t="n">
-        <v>7.2165</v>
+        <v>8.1005</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.161</v>
+        <v>0.191</v>
       </c>
       <c r="J170" t="n">
-        <v>2.737</v>
+        <v>3.247</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3355</v>
+        <v>-0.3049</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.7035</v>
+        <v>-5.1833</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4003</v>
+        <v>0.4301</v>
       </c>
       <c r="J172" t="n">
-        <v>8.4063</v>
+        <v>9.0321</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1956</v>
+        <v>0.1948</v>
       </c>
       <c r="J173" t="n">
-        <v>4.1076</v>
+        <v>4.0908</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.98</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0233</v>
+        <v>-0.033</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.4893</v>
+        <v>-0.6929999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.77</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2542</v>
+        <v>-0.2704</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.3382</v>
+        <v>-5.6784</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.42</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5795</v>
+        <v>-0.5812</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.1695</v>
+        <v>-12.2052</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.73</v>
       </c>
       <c r="I177" t="n">
-        <v>1.141</v>
+        <v>1.2498</v>
       </c>
       <c r="J177" t="n">
-        <v>23.961</v>
+        <v>26.2458</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7931</v>
+        <v>0.8787</v>
       </c>
       <c r="J178" t="n">
-        <v>16.6551</v>
+        <v>18.4527</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2626</v>
+        <v>0.2759</v>
       </c>
       <c r="J179" t="n">
-        <v>5.5146</v>
+        <v>5.7939</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0605</v>
+        <v>-0.0419</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.2705</v>
+        <v>-0.8799</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.97</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1939</v>
+        <v>-0.1798</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.0719</v>
+        <v>-3.7758</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.78</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1816</v>
+        <v>1.2958</v>
       </c>
       <c r="J182" t="n">
-        <v>25.9952</v>
+        <v>28.5076</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.66</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0384</v>
+        <v>1.1443</v>
       </c>
       <c r="J183" t="n">
-        <v>22.8448</v>
+        <v>25.1746</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3947</v>
+        <v>0.4362</v>
       </c>
       <c r="J184" t="n">
-        <v>8.683400000000001</v>
+        <v>9.596399999999999</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3279</v>
+        <v>0.3423</v>
       </c>
       <c r="J185" t="n">
-        <v>7.2138</v>
+        <v>7.5306</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4769</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.3432</v>
+        <v>-10.4918</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>0.93</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.0726</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.5972</v>
+        <v>-1.9888</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>0.93</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0726</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.5972</v>
+        <v>-1.9888</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.84</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1743</v>
+        <v>-0.1935</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.8346</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.318</v>
+        <v>-0.3352</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.996</v>
+        <v>-7.3744</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4585</v>
+        <v>-0.4692</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.087</v>
+        <v>-10.3224</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.77</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7449</v>
+        <v>0.8376</v>
       </c>
       <c r="J192" t="n">
-        <v>16.3878</v>
+        <v>18.4272</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.19</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3087</v>
+        <v>0.3169</v>
       </c>
       <c r="J193" t="n">
-        <v>6.7914</v>
+        <v>6.9718</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0047</v>
+        <v>-0.0036</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.1034</v>
+        <v>-0.07920000000000001</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1406</v>
+        <v>-0.1519</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.0932</v>
+        <v>-3.3418</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.43</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5857</v>
+        <v>-0.5848</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.8854</v>
+        <v>-12.8656</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.7583</v>
       </c>
       <c r="J197" t="n">
-        <v>14.6036</v>
+        <v>16.6826</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4958</v>
+        <v>0.5639</v>
       </c>
       <c r="J198" t="n">
-        <v>10.9076</v>
+        <v>12.4058</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1176</v>
+        <v>0.1326</v>
       </c>
       <c r="J199" t="n">
-        <v>2.5872</v>
+        <v>2.9172</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.358</v>
+        <v>-0.3665</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.876</v>
+        <v>-8.063000000000001</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.64</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4042</v>
+        <v>-0.4112</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.8924</v>
+        <v>-9.0464</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.41</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7393</v>
+        <v>0.8208</v>
       </c>
       <c r="J202" t="n">
-        <v>15.5253</v>
+        <v>17.2368</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.37</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6876</v>
+        <v>0.7644</v>
       </c>
       <c r="J203" t="n">
-        <v>14.4396</v>
+        <v>16.0524</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.26</v>
       </c>
       <c r="I204" t="n">
-        <v>0.5436</v>
+        <v>0.605</v>
       </c>
       <c r="J204" t="n">
-        <v>11.4156</v>
+        <v>12.705</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5304</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J205" t="n">
-        <v>11.1384</v>
+        <v>12.3942</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>1.02</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0322</v>
+        <v>0.057</v>
       </c>
       <c r="J206" t="n">
-        <v>0.6762</v>
+        <v>1.197</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4797</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J207" t="n">
-        <v>10.0737</v>
+        <v>10.9767</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.83</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1905</v>
+        <v>-0.2082</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.0005</v>
+        <v>-4.3722</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2102</v>
+        <v>-0.2279</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.4142</v>
+        <v>-4.7859</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2687</v>
+        <v>-0.2856</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.6427</v>
+        <v>-5.9976</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4201</v>
+        <v>-0.4316</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.822100000000001</v>
+        <v>-9.063599999999999</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0587</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.1153</v>
+        <v>-1.4497</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0587</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.1153</v>
+        <v>-1.4497</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1629</v>
+        <v>-0.1822</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.0951</v>
+        <v>-3.4618</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4018</v>
+        <v>-0.4156</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.6342</v>
+        <v>-7.8964</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.57</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4298</v>
+        <v>-0.4422</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.1662</v>
+        <v>-8.4018</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.66</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7846</v>
+        <v>0.7758</v>
       </c>
       <c r="J217" t="n">
-        <v>14.9074</v>
+        <v>14.7402</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.65</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7741</v>
+        <v>0.7662</v>
       </c>
       <c r="J218" t="n">
-        <v>14.7079</v>
+        <v>14.5578</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2657</v>
+        <v>0.2843</v>
       </c>
       <c r="J219" t="n">
-        <v>5.0483</v>
+        <v>5.4017</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.98</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0601</v>
+        <v>-0.0614</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.1419</v>
+        <v>-1.1666</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3125</v>
+        <v>-0.32</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.9375</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.69</v>
       </c>
       <c r="I222" t="n">
-        <v>1.373</v>
+        <v>1.3518</v>
       </c>
       <c r="J222" t="n">
-        <v>23.341</v>
+        <v>22.9806</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.32</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8327</v>
+        <v>0.7886</v>
       </c>
       <c r="J223" t="n">
-        <v>14.1559</v>
+        <v>13.4062</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.13</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3793</v>
+        <v>0.3821</v>
       </c>
       <c r="J224" t="n">
-        <v>6.4481</v>
+        <v>6.4957</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>1.02</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0414</v>
+        <v>0.0635</v>
       </c>
       <c r="J225" t="n">
-        <v>0.7038</v>
+        <v>1.0795</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.223</v>
+        <v>-0.2096</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.791</v>
+        <v>-3.5632</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.26</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6227</v>
+        <v>0.5894</v>
       </c>
       <c r="J227" t="n">
-        <v>10.5859</v>
+        <v>10.0198</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0825</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.4025</v>
+        <v>-1.6677</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2388</v>
+        <v>-0.2564</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.0596</v>
+        <v>-4.3588</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3632</v>
+        <v>-0.3773</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.1744</v>
+        <v>-6.4141</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.57</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4379</v>
+        <v>-0.4486</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.4443</v>
+        <v>-7.6262</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2828</v>
+        <v>1.2481</v>
       </c>
       <c r="J232" t="n">
-        <v>29.5044</v>
+        <v>28.7063</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.52</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2039</v>
+        <v>1.1643</v>
       </c>
       <c r="J233" t="n">
-        <v>27.6897</v>
+        <v>26.7789</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5376</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J234" t="n">
-        <v>-12.3648</v>
+        <v>-11.6978</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.77</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6711</v>
       </c>
       <c r="J235" t="n">
-        <v>-16.5669</v>
+        <v>-15.4353</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.67</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.9678</v>
+        <v>-0.8872</v>
       </c>
       <c r="J236" t="n">
-        <v>-22.2594</v>
+        <v>-20.4056</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.63</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0844</v>
+        <v>1.0506</v>
       </c>
       <c r="J237" t="n">
-        <v>24.9412</v>
+        <v>24.1638</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.34</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6723</v>
+        <v>0.6496</v>
       </c>
       <c r="J238" t="n">
-        <v>15.4629</v>
+        <v>14.9408</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2025</v>
+        <v>-0.2151</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.6575</v>
+        <v>-4.9473</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.71</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3307</v>
+        <v>-0.3416</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.6061</v>
+        <v>-7.8568</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3777</v>
+        <v>-0.3871</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.687099999999999</v>
+        <v>-8.9033</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.4</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7703</v>
+        <v>0.7383</v>
       </c>
       <c r="J242" t="n">
-        <v>16.9466</v>
+        <v>16.2426</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.19</v>
       </c>
       <c r="I243" t="n">
-        <v>0.408</v>
+        <v>0.4077</v>
       </c>
       <c r="J243" t="n">
-        <v>8.976000000000001</v>
+        <v>8.9694</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3713</v>
+        <v>0.3733</v>
       </c>
       <c r="J244" t="n">
-        <v>8.1686</v>
+        <v>8.2126</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J245" t="n">
-        <v>1.903</v>
+        <v>2.1164</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.42</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.592</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.0504</v>
+        <v>-13.024</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.61</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2813</v>
+        <v>1.2534</v>
       </c>
       <c r="J247" t="n">
-        <v>28.1886</v>
+        <v>27.5748</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.56</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2183</v>
+        <v>1.1864</v>
       </c>
       <c r="J248" t="n">
-        <v>26.8026</v>
+        <v>26.1008</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0068</v>
+        <v>0.0266</v>
       </c>
       <c r="J249" t="n">
-        <v>0.1496</v>
+        <v>0.5852000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.99</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1031</v>
+        <v>-0.093</v>
       </c>
       <c r="J250" t="n">
-        <v>-2.2682</v>
+        <v>-2.046</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.82</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6226</v>
+        <v>-0.5786</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.6972</v>
+        <v>-12.7292</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.26</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6204</v>
+        <v>0.5876</v>
       </c>
       <c r="J252" t="n">
-        <v>12.408</v>
+        <v>11.752</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.14</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3855</v>
+        <v>0.3719</v>
       </c>
       <c r="J253" t="n">
-        <v>7.71</v>
+        <v>7.438</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.7</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3164</v>
+        <v>-0.3321</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.328</v>
+        <v>-6.642</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.57</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4384</v>
+        <v>-0.449</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.768000000000001</v>
+        <v>-8.98</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.54</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4661</v>
+        <v>-0.4752</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.321999999999999</v>
+        <v>-9.504</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0707</v>
+        <v>1.0294</v>
       </c>
       <c r="J257" t="n">
-        <v>21.414</v>
+        <v>20.588</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0446</v>
+        <v>0.9984</v>
       </c>
       <c r="J258" t="n">
-        <v>20.892</v>
+        <v>19.968</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.34</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8605</v>
+        <v>0.8161</v>
       </c>
       <c r="J259" t="n">
-        <v>17.21</v>
+        <v>16.322</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.12</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3357</v>
+        <v>0.3458</v>
       </c>
       <c r="J260" t="n">
-        <v>6.714</v>
+        <v>6.916</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>1.12</v>
       </c>
       <c r="I261" t="n">
-        <v>0.3357</v>
+        <v>0.3458</v>
       </c>
       <c r="J261" t="n">
-        <v>6.714</v>
+        <v>6.916</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>2.1</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1083</v>
+        <v>1.1082</v>
       </c>
       <c r="J262" t="n">
-        <v>21.0577</v>
+        <v>21.0558</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.68</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7735</v>
+        <v>0.7705</v>
       </c>
       <c r="J263" t="n">
-        <v>14.6965</v>
+        <v>14.6395</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1697</v>
+        <v>0.1936</v>
       </c>
       <c r="J264" t="n">
-        <v>3.2243</v>
+        <v>3.6784</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1697</v>
+        <v>0.1936</v>
       </c>
       <c r="J265" t="n">
-        <v>3.2243</v>
+        <v>3.6784</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.01</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.0162</v>
+        <v>-0.0033</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.3078</v>
+        <v>-0.06270000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.11</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2942</v>
+        <v>0.2809</v>
       </c>
       <c r="J267" t="n">
-        <v>5.5898</v>
+        <v>5.3371</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1204</v>
+        <v>-0.1417</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.2876</v>
+        <v>-2.6923</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.62</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.376</v>
+        <v>-0.3923</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.144</v>
+        <v>-7.4537</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.61</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3854</v>
+        <v>-0.4012</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.3226</v>
+        <v>-7.6228</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.45</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5345</v>
+        <v>-0.5417</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.1555</v>
+        <v>-10.2923</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.52</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9993</v>
+        <v>0.9456</v>
       </c>
       <c r="J272" t="n">
-        <v>15.9888</v>
+        <v>15.1296</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.02</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0756</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="J273" t="n">
-        <v>1.2096</v>
+        <v>1.2832</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>0.98</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0325</v>
+        <v>-0.0401</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.52</v>
+        <v>-0.6415999999999999</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.64</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3871</v>
+        <v>-0.3977</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.1936</v>
+        <v>-6.3632</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.6</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4241</v>
+        <v>-0.4331</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.7856</v>
+        <v>-6.9296</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.76</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4191</v>
+        <v>1.4071</v>
       </c>
       <c r="J277" t="n">
-        <v>22.7056</v>
+        <v>22.5136</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.55</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1691</v>
+        <v>1.1407</v>
       </c>
       <c r="J278" t="n">
-        <v>18.7056</v>
+        <v>18.2512</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>1.28</v>
       </c>
       <c r="I279" t="n">
-        <v>0.7164</v>
+        <v>0.6912</v>
       </c>
       <c r="J279" t="n">
-        <v>11.4624</v>
+        <v>11.0592</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>1.15</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3994</v>
+        <v>0.4074</v>
       </c>
       <c r="J280" t="n">
-        <v>6.3904</v>
+        <v>6.5184</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>1.11</v>
       </c>
       <c r="I281" t="n">
-        <v>0.2914</v>
+        <v>0.3088</v>
       </c>
       <c r="J281" t="n">
-        <v>4.6624</v>
+        <v>4.9408</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.35</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7313</v>
+        <v>0.696</v>
       </c>
       <c r="J282" t="n">
-        <v>14.626</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0584</v>
+        <v>-0.0689</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.168</v>
+        <v>-1.378</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.88</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1491</v>
+        <v>-0.1639</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.982</v>
+        <v>-3.278</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.78</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2515</v>
+        <v>-0.2663</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.03</v>
+        <v>-5.326</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.72</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3098</v>
+        <v>-0.3234</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.196</v>
+        <v>-6.468</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1813</v>
+        <v>1.1466</v>
       </c>
       <c r="J287" t="n">
-        <v>23.626</v>
+        <v>22.932</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.9308</v>
+        <v>0.8738</v>
       </c>
       <c r="J288" t="n">
-        <v>18.616</v>
+        <v>17.476</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.386</v>
+        <v>0.3867</v>
       </c>
       <c r="J289" t="n">
-        <v>7.72</v>
+        <v>7.734</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.11</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3318</v>
+        <v>0.3369</v>
       </c>
       <c r="J290" t="n">
-        <v>6.636</v>
+        <v>6.738</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.84</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5686</v>
+        <v>-0.5304</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.372</v>
+        <v>-10.608</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.99</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0444</v>
+        <v>1.0347</v>
       </c>
       <c r="J292" t="n">
-        <v>18.7992</v>
+        <v>18.6246</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.46</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5488</v>
+        <v>0.5607</v>
       </c>
       <c r="J293" t="n">
-        <v>9.878399999999999</v>
+        <v>10.0926</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.45</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5386</v>
+        <v>0.551</v>
       </c>
       <c r="J294" t="n">
-        <v>9.694800000000001</v>
+        <v>9.917999999999999</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2219</v>
+        <v>0.2454</v>
       </c>
       <c r="J295" t="n">
-        <v>3.9942</v>
+        <v>4.4172</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>1.01</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.0167</v>
+        <v>-0.0037</v>
       </c>
       <c r="J296" t="n">
-        <v>-0.3006</v>
+        <v>-0.06660000000000001</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>0.88</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1001</v>
+        <v>-0.1258</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.8018</v>
+        <v>-2.2644</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>0.77</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2226</v>
+        <v>-0.2461</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.0068</v>
+        <v>-4.4298</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3111</v>
+        <v>-0.3318</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.5998</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.62</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3645</v>
+        <v>-0.3834</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.561</v>
+        <v>-6.9012</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.36</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6081</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.9458</v>
+        <v>-11.0052</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.25</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6148</v>
+        <v>0.5804</v>
       </c>
       <c r="J302" t="n">
-        <v>9.8368</v>
+        <v>9.2864</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2077</v>
+        <v>-0.226</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.3232</v>
+        <v>-3.616</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.77</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2462</v>
+        <v>-0.2643</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.9392</v>
+        <v>-4.2288</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.7</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3134</v>
+        <v>-0.3298</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.0144</v>
+        <v>-5.2768</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.57</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4355</v>
+        <v>-0.4467</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.968</v>
+        <v>-7.1472</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.96</v>
       </c>
       <c r="I307" t="n">
-        <v>1.6394</v>
+        <v>1.6401</v>
       </c>
       <c r="J307" t="n">
-        <v>26.2304</v>
+        <v>26.2416</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.67</v>
       </c>
       <c r="I308" t="n">
-        <v>1.3049</v>
+        <v>1.2874</v>
       </c>
       <c r="J308" t="n">
-        <v>20.8784</v>
+        <v>20.5984</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.54</v>
       </c>
       <c r="I309" t="n">
-        <v>1.1506</v>
+        <v>1.1221</v>
       </c>
       <c r="J309" t="n">
-        <v>18.4096</v>
+        <v>17.9536</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2305</v>
+        <v>-0.2056</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.688</v>
+        <v>-3.2896</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.92</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.392</v>
+        <v>-0.359</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.272</v>
+        <v>-5.744</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.32</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6412</v>
+        <v>0.621</v>
       </c>
       <c r="J312" t="n">
-        <v>19.236</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5102</v>
       </c>
       <c r="J313" t="n">
-        <v>15.591</v>
+        <v>15.306</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1779</v>
+        <v>0.1875</v>
       </c>
       <c r="J314" t="n">
-        <v>5.337</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.85</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1912</v>
+        <v>-0.204</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.736</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.65</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3861</v>
+        <v>-0.3953</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.583</v>
+        <v>-11.859</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.3</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8441</v>
+        <v>0.7882</v>
       </c>
       <c r="J317" t="n">
-        <v>25.323</v>
+        <v>23.646</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.23</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6723</v>
+        <v>0.6374</v>
       </c>
       <c r="J318" t="n">
-        <v>20.169</v>
+        <v>19.122</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.07</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2448</v>
+        <v>0.2491</v>
       </c>
       <c r="J319" t="n">
-        <v>7.344</v>
+        <v>7.473</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>1.07</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2448</v>
+        <v>0.2491</v>
       </c>
       <c r="J320" t="n">
-        <v>7.344</v>
+        <v>7.473</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.63</v>
       </c>
       <c r="I321" t="n">
-        <v>-1.0597</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-31.791</v>
+        <v>-29.016</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.95</v>
       </c>
       <c r="I322" t="n">
-        <v>1.7099</v>
+        <v>1.7012</v>
       </c>
       <c r="J322" t="n">
-        <v>41.0376</v>
+        <v>40.8288</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.59</v>
       </c>
       <c r="I323" t="n">
-        <v>1.2654</v>
+        <v>1.2349</v>
       </c>
       <c r="J323" t="n">
-        <v>30.3696</v>
+        <v>29.6376</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.82</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.6147</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="J324" t="n">
-        <v>-14.7528</v>
+        <v>-13.7544</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.7436</v>
+        <v>-0.6875</v>
       </c>
       <c r="J325" t="n">
-        <v>-17.8464</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.9169</v>
+        <v>-0.8395</v>
       </c>
       <c r="J326" t="n">
-        <v>-22.0056</v>
+        <v>-20.148</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.36</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7362</v>
+        <v>0.7024</v>
       </c>
       <c r="J327" t="n">
-        <v>17.6688</v>
+        <v>16.8576</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2353</v>
+        <v>0.2395</v>
       </c>
       <c r="J328" t="n">
-        <v>5.6472</v>
+        <v>5.748</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.92</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1079</v>
+        <v>-0.1207</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.5896</v>
+        <v>-2.8968</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.84</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1941</v>
+        <v>-0.2086</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.6584</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.61</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4162</v>
+        <v>-0.4254</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.988799999999999</v>
+        <v>-10.2096</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.25</v>
       </c>
       <c r="I332" t="n">
-        <v>0.7212</v>
+        <v>0.6807</v>
       </c>
       <c r="J332" t="n">
-        <v>25.242</v>
+        <v>23.8245</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.19</v>
       </c>
       <c r="I333" t="n">
-        <v>0.5703</v>
+        <v>0.547</v>
       </c>
       <c r="J333" t="n">
-        <v>19.9605</v>
+        <v>19.145</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.18</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5446</v>
+        <v>0.524</v>
       </c>
       <c r="J334" t="n">
-        <v>19.061</v>
+        <v>18.34</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.99</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0678</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J335" t="n">
-        <v>-2.373</v>
+        <v>-2.401</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.7</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8911</v>
+        <v>-0.8213</v>
       </c>
       <c r="J336" t="n">
-        <v>-31.1885</v>
+        <v>-28.7455</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.78</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2013</v>
+        <v>1.1829</v>
       </c>
       <c r="J337" t="n">
-        <v>42.0455</v>
+        <v>41.4015</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.03</v>
       </c>
       <c r="I338" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J338" t="n">
-        <v>2.7195</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.02</v>
       </c>
       <c r="I339" t="n">
-        <v>0.0517</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J339" t="n">
-        <v>1.8095</v>
+        <v>2.212</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1105</v>
+        <v>-0.1196</v>
       </c>
       <c r="J340" t="n">
-        <v>-3.8675</v>
+        <v>-4.186</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3181</v>
+        <v>-0.3281</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.1335</v>
+        <v>-11.4835</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.39</v>
       </c>
       <c r="I342" t="n">
-        <v>0.6369</v>
+        <v>0.6123</v>
       </c>
       <c r="J342" t="n">
-        <v>13.3749</v>
+        <v>12.8583</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.04</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1131</v>
+        <v>0.1156</v>
       </c>
       <c r="J343" t="n">
-        <v>2.3751</v>
+        <v>2.4276</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1539</v>
+        <v>-0.1703</v>
       </c>
       <c r="J344" t="n">
-        <v>-3.2319</v>
+        <v>-3.5763</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3313</v>
+        <v>-0.3456</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.9573</v>
+        <v>-7.2576</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.42</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5795</v>
+        <v>-0.5812</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.1695</v>
+        <v>-12.2052</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.4</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5072</v>
+        <v>0.517</v>
       </c>
       <c r="J347" t="n">
-        <v>10.6512</v>
+        <v>10.857</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.3</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3947</v>
+        <v>0.4098</v>
       </c>
       <c r="J348" t="n">
-        <v>8.2887</v>
+        <v>8.6058</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.29</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3833</v>
+        <v>0.3988</v>
       </c>
       <c r="J349" t="n">
-        <v>8.049300000000001</v>
+        <v>8.3748</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>1.22</v>
       </c>
       <c r="I350" t="n">
-        <v>0.303</v>
+        <v>0.3206</v>
       </c>
       <c r="J350" t="n">
-        <v>6.363</v>
+        <v>6.7326</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.96</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.0868</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J351" t="n">
-        <v>-1.8228</v>
+        <v>-1.9068</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.43</v>
       </c>
       <c r="I352" t="n">
-        <v>1.0562</v>
+        <v>1.0065</v>
       </c>
       <c r="J352" t="n">
-        <v>21.124</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.26</v>
       </c>
       <c r="I353" t="n">
-        <v>0.7069</v>
+        <v>0.6753</v>
       </c>
       <c r="J353" t="n">
-        <v>14.138</v>
+        <v>13.506</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.26</v>
       </c>
       <c r="I354" t="n">
-        <v>0.7069</v>
+        <v>0.6753</v>
       </c>
       <c r="J354" t="n">
-        <v>14.138</v>
+        <v>13.506</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.1</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3081</v>
+        <v>0.3141</v>
       </c>
       <c r="J355" t="n">
-        <v>6.162</v>
+        <v>6.282</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.83</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5908</v>
+        <v>-0.5512</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.816</v>
+        <v>-11.024</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.35</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6891</v>
+        <v>0.6649</v>
       </c>
       <c r="J357" t="n">
-        <v>13.782</v>
+        <v>13.298</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.25</v>
       </c>
       <c r="I358" t="n">
-        <v>0.5172</v>
+        <v>0.5083</v>
       </c>
       <c r="J358" t="n">
-        <v>10.344</v>
+        <v>10.166</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>1.15</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3354</v>
+        <v>0.3392</v>
       </c>
       <c r="J359" t="n">
-        <v>6.708</v>
+        <v>6.784</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.85</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1921</v>
+        <v>-0.2047</v>
       </c>
       <c r="J360" t="n">
-        <v>-3.842</v>
+        <v>-4.094</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.58</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.451</v>
+        <v>-0.4574</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.02</v>
+        <v>-9.148</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.9</v>
       </c>
       <c r="I362" t="n">
-        <v>1.6612</v>
+        <v>1.6489</v>
       </c>
       <c r="J362" t="n">
-        <v>38.2076</v>
+        <v>37.9247</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.22</v>
       </c>
       <c r="I363" t="n">
-        <v>0.6214</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J363" t="n">
-        <v>14.2922</v>
+        <v>13.7379</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.19</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5476</v>
+        <v>0.5313</v>
       </c>
       <c r="J364" t="n">
-        <v>12.5948</v>
+        <v>12.2199</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.9</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3875</v>
+        <v>-0.3689</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.9125</v>
+        <v>-8.4847</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.48</v>
       </c>
       <c r="I366" t="n">
-        <v>-1.424</v>
+        <v>-1.276</v>
       </c>
       <c r="J366" t="n">
-        <v>-32.752</v>
+        <v>-29.348</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.3</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5783</v>
       </c>
       <c r="J367" t="n">
-        <v>13.5976</v>
+        <v>13.3009</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.19</v>
       </c>
       <c r="I368" t="n">
-        <v>0.3994</v>
+        <v>0.4014</v>
       </c>
       <c r="J368" t="n">
-        <v>9.186199999999999</v>
+        <v>9.232200000000001</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.03</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0814</v>
+        <v>0.0926</v>
       </c>
       <c r="J369" t="n">
-        <v>1.8722</v>
+        <v>2.1298</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.97</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.0575</v>
+        <v>-0.064</v>
       </c>
       <c r="J370" t="n">
-        <v>-1.3225</v>
+        <v>-1.472</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1537</v>
+        <v>-0.1648</v>
       </c>
       <c r="J371" t="n">
-        <v>-3.5351</v>
+        <v>-3.7904</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.84</v>
       </c>
       <c r="I372" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9506</v>
       </c>
       <c r="J372" t="n">
-        <v>22.3629</v>
+        <v>21.8638</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.14</v>
       </c>
       <c r="I373" t="n">
-        <v>0.2048</v>
+        <v>0.2234</v>
       </c>
       <c r="J373" t="n">
-        <v>4.7104</v>
+        <v>5.1382</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.12</v>
       </c>
       <c r="I374" t="n">
-        <v>0.1779</v>
+        <v>0.1966</v>
       </c>
       <c r="J374" t="n">
-        <v>4.0917</v>
+        <v>4.5218</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>1.07</v>
       </c>
       <c r="I375" t="n">
-        <v>0.1059</v>
+        <v>0.1238</v>
       </c>
       <c r="J375" t="n">
-        <v>2.4357</v>
+        <v>2.8474</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.92</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.1343</v>
+        <v>-0.1412</v>
       </c>
       <c r="J376" t="n">
-        <v>-3.0889</v>
+        <v>-3.2476</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.51</v>
       </c>
       <c r="I377" t="n">
-        <v>0.7681</v>
+        <v>0.735</v>
       </c>
       <c r="J377" t="n">
-        <v>17.6663</v>
+        <v>16.905</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.03</v>
       </c>
       <c r="I378" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J378" t="n">
-        <v>1.8561</v>
+        <v>1.978</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.96</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.0584</v>
+        <v>-0.0689</v>
       </c>
       <c r="J379" t="n">
-        <v>-1.3432</v>
+        <v>-1.5847</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.68</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3479</v>
+        <v>-0.3603</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.0017</v>
+        <v>-8.286899999999999</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.51</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5044</v>
+        <v>-0.5097</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.6012</v>
+        <v>-11.7231</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.28</v>
       </c>
       <c r="I382" t="n">
-        <v>0.6159</v>
+        <v>0.5904</v>
       </c>
       <c r="J382" t="n">
-        <v>13.5498</v>
+        <v>12.9888</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.17</v>
       </c>
       <c r="I383" t="n">
-        <v>0.4107</v>
+        <v>0.4022</v>
       </c>
       <c r="J383" t="n">
-        <v>9.035399999999999</v>
+        <v>8.8484</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.91</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.115</v>
+        <v>-0.1292</v>
       </c>
       <c r="J384" t="n">
-        <v>-2.53</v>
+        <v>-2.8424</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.62</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.4019</v>
+        <v>-0.4126</v>
       </c>
       <c r="J385" t="n">
-        <v>-8.841799999999999</v>
+        <v>-9.077199999999999</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.62</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4019</v>
+        <v>-0.4126</v>
       </c>
       <c r="J386" t="n">
-        <v>-8.841799999999999</v>
+        <v>-9.077199999999999</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.82</v>
       </c>
       <c r="I387" t="n">
-        <v>1.5565</v>
+        <v>1.5408</v>
       </c>
       <c r="J387" t="n">
-        <v>34.243</v>
+        <v>33.8976</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.24</v>
       </c>
       <c r="I388" t="n">
-        <v>0.6653</v>
+        <v>0.6373</v>
       </c>
       <c r="J388" t="n">
-        <v>14.6366</v>
+        <v>14.0206</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.17</v>
       </c>
       <c r="I389" t="n">
-        <v>0.4946</v>
+        <v>0.4842</v>
       </c>
       <c r="J389" t="n">
-        <v>10.8812</v>
+        <v>10.6524</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.9</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3917</v>
+        <v>-0.3719</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.6174</v>
+        <v>-8.181800000000001</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.64</v>
       </c>
       <c r="I391" t="n">
-        <v>-1.0581</v>
+        <v>-0.9624</v>
       </c>
       <c r="J391" t="n">
-        <v>-23.2782</v>
+        <v>-21.1728</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.54</v>
       </c>
       <c r="I392" t="n">
-        <v>1.0072</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J392" t="n">
-        <v>24.1728</v>
+        <v>22.9728</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.02</v>
       </c>
       <c r="I393" t="n">
-        <v>0.0674</v>
+        <v>0.0743</v>
       </c>
       <c r="J393" t="n">
-        <v>1.6176</v>
+        <v>1.7832</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.9</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.1334</v>
+        <v>-0.1463</v>
       </c>
       <c r="J394" t="n">
-        <v>-3.2016</v>
+        <v>-3.5112</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.78</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.258</v>
+        <v>-0.2713</v>
       </c>
       <c r="J395" t="n">
-        <v>-6.192</v>
+        <v>-6.5112</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.72</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3163</v>
+        <v>-0.3285</v>
       </c>
       <c r="J396" t="n">
-        <v>-7.5912</v>
+        <v>-7.884</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.39</v>
       </c>
       <c r="I397" t="n">
-        <v>1.0257</v>
+        <v>0.9641</v>
       </c>
       <c r="J397" t="n">
-        <v>24.6168</v>
+        <v>23.1384</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.16</v>
       </c>
       <c r="I398" t="n">
-        <v>0.4876</v>
+        <v>0.4738</v>
       </c>
       <c r="J398" t="n">
-        <v>11.7024</v>
+        <v>11.3712</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.11</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3542</v>
+        <v>0.3521</v>
       </c>
       <c r="J399" t="n">
-        <v>8.5008</v>
+        <v>8.4504</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.99</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J400" t="n">
-        <v>-1.728</v>
+        <v>-1.7136</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.74</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.7964</v>
+        <v>-0.7379</v>
       </c>
       <c r="J401" t="n">
-        <v>-19.1136</v>
+        <v>-17.7096</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.41</v>
       </c>
       <c r="I402" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="J402" t="n">
-        <v>16.22</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.06</v>
       </c>
       <c r="I403" t="n">
-        <v>0.1648</v>
+        <v>0.1724</v>
       </c>
       <c r="J403" t="n">
-        <v>3.296</v>
+        <v>3.448</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.01</v>
       </c>
       <c r="I404" t="n">
-        <v>0.0398</v>
+        <v>0.0448</v>
       </c>
       <c r="J404" t="n">
-        <v>0.796</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2573</v>
+        <v>-0.2708</v>
       </c>
       <c r="J405" t="n">
-        <v>-5.146</v>
+        <v>-5.416</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.67</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3629</v>
+        <v>-0.3738</v>
       </c>
       <c r="J406" t="n">
-        <v>-7.258</v>
+        <v>-7.476</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.56</v>
       </c>
       <c r="I407" t="n">
-        <v>1.2096</v>
+        <v>1.1787</v>
       </c>
       <c r="J407" t="n">
-        <v>24.192</v>
+        <v>23.574</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.56</v>
       </c>
       <c r="I408" t="n">
-        <v>1.2096</v>
+        <v>1.1787</v>
       </c>
       <c r="J408" t="n">
-        <v>24.192</v>
+        <v>23.574</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.44</v>
       </c>
       <c r="I409" t="n">
-        <v>1.057</v>
+        <v>1.0103</v>
       </c>
       <c r="J409" t="n">
-        <v>21.14</v>
+        <v>20.206</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.98</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1527</v>
+        <v>-0.1404</v>
       </c>
       <c r="J410" t="n">
-        <v>-3.054</v>
+        <v>-2.808</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.62</v>
       </c>
       <c r="I411" t="n">
-        <v>-1.1211</v>
+        <v>-1.0144</v>
       </c>
       <c r="J411" t="n">
-        <v>-22.422</v>
+        <v>-20.288</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.14</v>
       </c>
       <c r="I412" t="n">
-        <v>0.4124</v>
+        <v>0.3918</v>
       </c>
       <c r="J412" t="n">
-        <v>6.5984</v>
+        <v>6.2688</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>0.83</v>
       </c>
       <c r="I413" t="n">
-        <v>-0.1855</v>
+        <v>-0.2044</v>
       </c>
       <c r="J413" t="n">
-        <v>-2.968</v>
+        <v>-3.2704</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>0.7</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.3094</v>
+        <v>-0.3267</v>
       </c>
       <c r="J414" t="n">
-        <v>-4.9504</v>
+        <v>-5.2272</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.67</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.3378</v>
+        <v>-0.3541</v>
       </c>
       <c r="J415" t="n">
-        <v>-5.4048</v>
+        <v>-5.6656</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.62</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3848</v>
+        <v>-0.3992</v>
       </c>
       <c r="J416" t="n">
-        <v>-6.1568</v>
+        <v>-6.3872</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.94</v>
       </c>
       <c r="I417" t="n">
-        <v>1.5981</v>
+        <v>1.5999</v>
       </c>
       <c r="J417" t="n">
-        <v>25.5696</v>
+        <v>25.5984</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.89</v>
       </c>
       <c r="I418" t="n">
-        <v>1.542</v>
+        <v>1.5411</v>
       </c>
       <c r="J418" t="n">
-        <v>24.672</v>
+        <v>24.6576</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>1.4</v>
       </c>
       <c r="I419" t="n">
-        <v>0.9537</v>
+        <v>0.907</v>
       </c>
       <c r="J419" t="n">
-        <v>15.2592</v>
+        <v>14.512</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>1.22</v>
       </c>
       <c r="I420" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5481</v>
       </c>
       <c r="J420" t="n">
-        <v>8.798400000000001</v>
+        <v>8.769600000000001</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>1.01</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.0586</v>
+        <v>-0.0193</v>
       </c>
       <c r="J421" t="n">
-        <v>-0.9376</v>
+        <v>-0.3088</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8039/event_8039_evp_summary.xlsx
+++ b/database/event/8039/event_8039_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.2765</v>
+        <v>8.4214</v>
       </c>
       <c r="C2" t="n">
-        <v>5.3673</v>
+        <v>5.4613</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1434</v>
+        <v>3.1478</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2765</v>
+        <v>8.4214</v>
       </c>
       <c r="F2" t="n">
         <v>2.0857</v>
@@ -520,7 +520,7 @@
         <v>2.0857</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4095</v>
+        <v>6.4036</v>
       </c>
       <c r="K2" t="n">
         <v>36</v>
@@ -529,7 +529,7 @@
         <v>197</v>
       </c>
       <c r="M2" t="n">
-        <v>8.495200000000001</v>
+        <v>8.4893</v>
       </c>
       <c r="N2" t="n">
         <v>233</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4423</v>
+        <v>7.6987</v>
       </c>
       <c r="C3" t="n">
-        <v>4.8264</v>
+        <v>4.9926</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7637</v>
+        <v>2.825</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4423</v>
+        <v>7.6987</v>
       </c>
       <c r="F3" t="n">
-        <v>1.895</v>
+        <v>1.8953</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5473</v>
+        <v>5.5462</v>
       </c>
       <c r="H3" t="n">
-        <v>1.895</v>
+        <v>1.8953</v>
       </c>
       <c r="I3" t="n">
-        <v>1.895</v>
+        <v>1.8953</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5473</v>
+        <v>5.5462</v>
       </c>
       <c r="K3" t="n">
         <v>55</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>7.442299999999999</v>
+        <v>7.4415</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0217</v>
+        <v>6.1063</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9051</v>
+        <v>3.96</v>
       </c>
       <c r="D4" t="n">
-        <v>2.117</v>
+        <v>2.1137</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0217</v>
+        <v>6.1063</v>
       </c>
       <c r="F4" t="n">
         <v>2.4877</v>
       </c>
       <c r="G4" t="n">
-        <v>3.534</v>
+        <v>3.5342</v>
       </c>
       <c r="H4" t="n">
         <v>2.7198</v>
@@ -612,7 +612,7 @@
         <v>2.7198</v>
       </c>
       <c r="J4" t="n">
-        <v>3.534</v>
+        <v>3.5342</v>
       </c>
       <c r="K4" t="n">
         <v>36</v>
@@ -621,7 +621,7 @@
         <v>197</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2538</v>
+        <v>6.254</v>
       </c>
       <c r="N4" t="n">
         <v>233</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7289</v>
+        <v>5.8941</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7152</v>
+        <v>3.8223</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9837</v>
+        <v>2.0189</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7289</v>
+        <v>5.8941</v>
       </c>
       <c r="F5" t="n">
         <v>1.9894</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7396</v>
+        <v>3.7297</v>
       </c>
       <c r="H5" t="n">
         <v>1.9894</v>
@@ -658,7 +658,7 @@
         <v>1.9894</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7396</v>
+        <v>3.7297</v>
       </c>
       <c r="K5" t="n">
         <v>113</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>5.729</v>
+        <v>5.7191</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1972</v>
+        <v>4.2787</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7219</v>
+        <v>2.7747</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2864</v>
+        <v>1.2974</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1972</v>
+        <v>4.2787</v>
       </c>
       <c r="F6" t="n">
         <v>-0.1597</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3569</v>
+        <v>4.357</v>
       </c>
       <c r="H6" t="n">
         <v>-0.1597</v>
@@ -704,7 +704,7 @@
         <v>-0.1597</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3569</v>
+        <v>4.357</v>
       </c>
       <c r="K6" t="n">
         <v>36</v>
@@ -713,7 +713,7 @@
         <v>197</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1972</v>
+        <v>4.1973</v>
       </c>
       <c r="N6" t="n">
         <v>233</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9656</v>
+        <v>4.2116</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5717</v>
+        <v>2.7312</v>
       </c>
       <c r="D7" t="n">
-        <v>1.181</v>
+        <v>1.2674</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9656</v>
+        <v>4.2116</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9528</v>
+        <v>2.9612</v>
       </c>
       <c r="G7" t="n">
         <v>1.0128</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7379</v>
+        <v>3.7562</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7379</v>
+        <v>3.7562</v>
       </c>
       <c r="J7" t="n">
         <v>1.0128</v>
@@ -759,7 +759,7 @@
         <v>109</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7507</v>
+        <v>4.769</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6378</v>
+        <v>3.812</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3591</v>
+        <v>2.4721</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0318</v>
+        <v>1.0889</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6378</v>
+        <v>3.812</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6521</v>
+        <v>2.8289</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9857</v>
+        <v>0.7802</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6521</v>
+        <v>3.4667</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6521</v>
+        <v>3.4667</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9857</v>
+        <v>0.7802</v>
       </c>
       <c r="K8" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="L8" t="n">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6378</v>
+        <v>4.2469</v>
       </c>
       <c r="N8" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6095</v>
+        <v>3.7765</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3408</v>
+        <v>2.4491</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0189</v>
+        <v>1.0731</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6095</v>
+        <v>3.7765</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8293</v>
+        <v>1.652</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7802</v>
+        <v>1.985</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4674</v>
+        <v>1.652</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4674</v>
+        <v>1.652</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7802</v>
+        <v>1.985</v>
       </c>
       <c r="K9" t="n">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="L9" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2476</v>
+        <v>3.637</v>
       </c>
       <c r="N9" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4607</v>
+        <v>3.6278</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2443</v>
+        <v>2.3526</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9512</v>
+        <v>1.0066</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4607</v>
+        <v>3.6278</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5621</v>
+        <v>1.578</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8986</v>
+        <v>1.8978</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5621</v>
+        <v>1.578</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5621</v>
+        <v>1.578</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8986</v>
+        <v>1.8978</v>
       </c>
       <c r="K10" t="n">
         <v>55</v>
@@ -897,7 +897,7 @@
         <v>156</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4607</v>
+        <v>3.4758</v>
       </c>
       <c r="N10" t="n">
         <v>211</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2416</v>
+        <v>3.3283</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1022</v>
+        <v>2.1584</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8514</v>
+        <v>0.8729</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2416</v>
+        <v>3.3283</v>
       </c>
       <c r="F11" t="n">
         <v>1.5685</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6731</v>
+        <v>1.6682</v>
       </c>
       <c r="H11" t="n">
         <v>1.5685</v>
@@ -934,7 +934,7 @@
         <v>1.5685</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6731</v>
+        <v>1.6682</v>
       </c>
       <c r="K11" t="n">
         <v>113</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2416</v>
+        <v>3.2367</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8657</v>
+        <v>3.0267</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8584</v>
+        <v>1.9628</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6803</v>
+        <v>0.7381</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8657</v>
+        <v>3.0267</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7845</v>
+        <v>1.7842</v>
       </c>
       <c r="G12" t="n">
         <v>1.0812</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7845</v>
+        <v>1.7842</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7845</v>
+        <v>1.7842</v>
       </c>
       <c r="J12" t="n">
         <v>1.0812</v>
@@ -989,7 +989,7 @@
         <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8657</v>
+        <v>2.8654</v>
       </c>
       <c r="N12" t="n">
         <v>108</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7212</v>
+        <v>2.6966</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7647</v>
+        <v>1.7488</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6145</v>
+        <v>0.5907</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7212</v>
+        <v>2.6966</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6098</v>
+        <v>1.5902</v>
       </c>
       <c r="G13" t="n">
         <v>1.1114</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6098</v>
+        <v>1.5902</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6098</v>
+        <v>1.5902</v>
       </c>
       <c r="J13" t="n">
         <v>1.1114</v>
@@ -1035,7 +1035,7 @@
         <v>109</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7212</v>
+        <v>2.7016</v>
       </c>
       <c r="N13" t="n">
         <v>205</v>
@@ -1044,415 +1044,415 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5104</v>
+        <v>2.5841</v>
       </c>
       <c r="C14" t="n">
-        <v>1.628</v>
+        <v>1.6758</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5404</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5104</v>
+        <v>2.5841</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5584</v>
+        <v>2.1256</v>
       </c>
       <c r="G14" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5584</v>
+        <v>2.1256</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5584</v>
+        <v>2.1256</v>
       </c>
       <c r="J14" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L14" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5104</v>
+        <v>2.1256</v>
       </c>
       <c r="N14" t="n">
-        <v>233</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3096</v>
+        <v>2.5357</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4978</v>
+        <v>1.6444</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4272</v>
+        <v>0.5188</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3096</v>
+        <v>2.5357</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6211</v>
+        <v>1.5584</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6885</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6211</v>
+        <v>1.5584</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6211</v>
+        <v>1.5584</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6885</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L15" t="n">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3096</v>
+        <v>2.5105</v>
       </c>
       <c r="N15" t="n">
-        <v>125</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1253</v>
+        <v>2.4026</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3783</v>
+        <v>1.5581</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3433</v>
+        <v>0.4594</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1253</v>
+        <v>2.4026</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1253</v>
+        <v>1.6204</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.6979</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1253</v>
+        <v>1.6204</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1253</v>
+        <v>1.6204</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.6979</v>
       </c>
       <c r="K16" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1253</v>
+        <v>2.3183</v>
       </c>
       <c r="N16" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0696</v>
+        <v>2.3733</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3421</v>
+        <v>1.5391</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3179</v>
+        <v>0.4463</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0696</v>
+        <v>2.3733</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0739</v>
+        <v>1.8844</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0043</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0739</v>
+        <v>1.8844</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0739</v>
+        <v>1.8844</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0043</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L17" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0696</v>
+        <v>1.8844</v>
       </c>
       <c r="N17" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8844</v>
+        <v>2.3642</v>
       </c>
       <c r="C18" t="n">
-        <v>1.222</v>
+        <v>1.5332</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2336</v>
+        <v>0.4422</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8844</v>
+        <v>2.3642</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8844</v>
+        <v>2.0695</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8844</v>
+        <v>2.0695</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8844</v>
+        <v>2.0695</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="K18" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8844</v>
+        <v>2.0743</v>
       </c>
       <c r="N18" t="n">
-        <v>55</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5708</v>
+        <v>1.9345</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0187</v>
+        <v>1.2545</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.2503</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5708</v>
+        <v>1.9345</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0314</v>
+        <v>1.4224</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4606</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0314</v>
+        <v>1.4224</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0314</v>
+        <v>1.4224</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4606</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L19" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5708</v>
+        <v>1.4224</v>
       </c>
       <c r="N19" t="n">
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5251</v>
+        <v>1.646</v>
       </c>
       <c r="C20" t="n">
-        <v>0.989</v>
+        <v>1.0674</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0701</v>
+        <v>0.1214</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5251</v>
+        <v>1.646</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9786</v>
+        <v>1.4959</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4535</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9786</v>
+        <v>1.4959</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9786</v>
+        <v>1.4959</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4535</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5251</v>
+        <v>1.4959</v>
       </c>
       <c r="N20" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4952</v>
+        <v>1.6222</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9696</v>
+        <v>1.052</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0564</v>
+        <v>0.1108</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4952</v>
+        <v>1.6222</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4952</v>
+        <v>2.031</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.4606</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4952</v>
+        <v>2.031</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4952</v>
+        <v>2.031</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.4606</v>
       </c>
       <c r="K21" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4952</v>
+        <v>1.5704</v>
       </c>
       <c r="N21" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4224</v>
+        <v>1.5699</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9224</v>
+        <v>1.0181</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0233</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4224</v>
+        <v>1.5699</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4224</v>
+        <v>1.9786</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.4535</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4224</v>
+        <v>1.9786</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4224</v>
+        <v>1.9786</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.4535</v>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4224</v>
+        <v>1.5251</v>
       </c>
       <c r="N22" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3966</v>
+        <v>1.5408</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9992</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0116</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3966</v>
+        <v>1.5408</v>
       </c>
       <c r="F23" t="n">
         <v>1.0363</v>
@@ -1504,262 +1504,262 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3038</v>
+        <v>1.4378</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8455</v>
+        <v>0.9324</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0307</v>
+        <v>0.0284</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3038</v>
+        <v>1.4378</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5988</v>
+        <v>1.1087</v>
       </c>
       <c r="G24" t="n">
-        <v>0.705</v>
+        <v>0.1715</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5988</v>
+        <v>1.1087</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5988</v>
+        <v>1.1087</v>
       </c>
       <c r="J24" t="n">
-        <v>0.705</v>
+        <v>0.1715</v>
       </c>
       <c r="K24" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="L24" t="n">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3038</v>
+        <v>1.2802</v>
       </c>
       <c r="N24" t="n">
-        <v>205</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2713</v>
+        <v>1.3123</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8244</v>
+        <v>0.851</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0455</v>
+        <v>-0.0276</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2713</v>
+        <v>1.3123</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1091</v>
+        <v>1.2467</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1622</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1091</v>
+        <v>1.2467</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1091</v>
+        <v>1.2467</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1622</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L25" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2713</v>
+        <v>1.2467</v>
       </c>
       <c r="N25" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2303</v>
+        <v>1.2955</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.8401</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0641</v>
+        <v>-0.0351</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2303</v>
+        <v>1.2955</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2303</v>
+        <v>1.1403</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2303</v>
+        <v>1.1403</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2303</v>
+        <v>1.1403</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2303</v>
+        <v>1.1403</v>
       </c>
       <c r="N26" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1603</v>
+        <v>1.275</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.8268</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.096</v>
+        <v>-0.0443</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1603</v>
+        <v>1.275</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5855</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5748</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5855</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5855</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5748</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L27" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1603</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>233</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1405</v>
+        <v>1.1673</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7396</v>
+        <v>0.757</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.105</v>
+        <v>-0.0924</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1405</v>
+        <v>1.1673</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1405</v>
+        <v>0.6026</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1405</v>
+        <v>0.6026</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1405</v>
+        <v>0.6026</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="K28" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1405</v>
+        <v>1.3076</v>
       </c>
       <c r="N28" t="n">
-        <v>59</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9557</v>
+        <v>1.0403</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6198</v>
+        <v>0.6746</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1891</v>
+        <v>-0.1491</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9557</v>
+        <v>1.0403</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9557</v>
+        <v>0.9486</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9557</v>
+        <v>0.9486</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9557</v>
+        <v>0.9486</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9557</v>
+        <v>0.9486</v>
       </c>
       <c r="N29" t="n">
         <v>64</v>
@@ -1780,415 +1780,415 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9488</v>
+        <v>1.0308</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6153</v>
+        <v>0.6685</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1923</v>
+        <v>-0.1534</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9488</v>
+        <v>1.0308</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9488</v>
+        <v>0.5855</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.5752</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9488</v>
+        <v>0.5855</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9488</v>
+        <v>0.5855</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.5752</v>
       </c>
       <c r="K30" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9488</v>
+        <v>1.1607</v>
       </c>
       <c r="N30" t="n">
-        <v>64</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9099</v>
+        <v>0.9459</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5901</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.21</v>
+        <v>-0.1913</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9099</v>
+        <v>0.9459</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9099</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9099</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9099</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9099</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8911</v>
+        <v>0.8698</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5779</v>
+        <v>0.5641</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2186</v>
+        <v>-0.2253</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8911</v>
+        <v>0.8698</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8911</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8911</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8911</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8911</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8158</v>
+        <v>0.8636</v>
       </c>
       <c r="C33" t="n">
-        <v>0.529</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2528</v>
+        <v>-0.2281</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8158</v>
+        <v>0.8636</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8158</v>
+        <v>0.8905</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8158</v>
+        <v>0.8905</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8158</v>
+        <v>0.8905</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8158</v>
+        <v>0.8905</v>
       </c>
       <c r="N33" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.8305</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4965</v>
+        <v>0.5386</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2757</v>
+        <v>-0.2429</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.8305</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.2127</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.2127</v>
       </c>
       <c r="K34" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>59</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7499</v>
+        <v>0.7572</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4863</v>
+        <v>0.491</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2828</v>
+        <v>-0.2756</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7499</v>
+        <v>0.7572</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0629</v>
+        <v>0.6838</v>
       </c>
       <c r="G35" t="n">
-        <v>1.8128</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0629</v>
+        <v>0.6838</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0629</v>
+        <v>0.6838</v>
       </c>
       <c r="J35" t="n">
-        <v>1.8128</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L35" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7499</v>
+        <v>0.6838</v>
       </c>
       <c r="N35" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7094</v>
+        <v>0.755</v>
       </c>
       <c r="C36" t="n">
-        <v>0.46</v>
+        <v>0.4896</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3013</v>
+        <v>-0.2766</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7094</v>
+        <v>0.755</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5233</v>
+        <v>-1.0632</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1861</v>
+        <v>1.8117</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5233</v>
+        <v>-1.0632</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5233</v>
+        <v>-1.0632</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1861</v>
+        <v>1.8117</v>
       </c>
       <c r="K36" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L36" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7094</v>
+        <v>0.7485000000000002</v>
       </c>
       <c r="N36" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6838</v>
+        <v>0.7514</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4434</v>
+        <v>0.4873</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3129</v>
+        <v>-0.2782</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6838</v>
+        <v>0.7514</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6838</v>
+        <v>0.4169</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6838</v>
+        <v>0.4169</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6838</v>
+        <v>0.4169</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6838</v>
+        <v>0.4169</v>
       </c>
       <c r="N37" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6407</v>
+        <v>0.7047</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4155</v>
+        <v>0.457</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3325</v>
+        <v>-0.299</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6407</v>
+        <v>0.7047</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6407</v>
+        <v>0.8158</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6407</v>
+        <v>0.8158</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6407</v>
+        <v>0.8158</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6407</v>
+        <v>0.8158</v>
       </c>
       <c r="N38" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39">
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5642</v>
+        <v>0.6878</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3659</v>
+        <v>0.446</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3674</v>
+        <v>-0.3066</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5642</v>
+        <v>0.6878</v>
       </c>
       <c r="F39" t="n">
         <v>0.5642</v>
@@ -2240,231 +2240,231 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.6765</v>
       </c>
       <c r="C40" t="n">
-        <v>0.337</v>
+        <v>0.4387</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3876</v>
+        <v>-0.3116</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.6765</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="N40" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4831</v>
+        <v>0.5513</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3133</v>
+        <v>0.3575</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4043</v>
+        <v>-0.3676</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4831</v>
+        <v>0.5513</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.5828</v>
+        <v>0.4743</v>
       </c>
       <c r="G41" t="n">
-        <v>1.0659</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.5828</v>
+        <v>0.4743</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5828</v>
+        <v>0.4743</v>
       </c>
       <c r="J41" t="n">
-        <v>1.0659</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="L41" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4831000000000001</v>
+        <v>0.4743</v>
       </c>
       <c r="N41" t="n">
-        <v>214</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4742</v>
+        <v>0.4542</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3075</v>
+        <v>0.2945</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4083</v>
+        <v>-0.4109</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4742</v>
+        <v>0.4542</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4742</v>
+        <v>-0.5828</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1.0664</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4742</v>
+        <v>-0.5828</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4742</v>
+        <v>-0.5828</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1.0664</v>
       </c>
       <c r="K42" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4742</v>
+        <v>0.4836</v>
       </c>
       <c r="N42" t="n">
-        <v>64</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4169</v>
+        <v>0.4319</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2704</v>
+        <v>0.2801</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4344</v>
+        <v>-0.4209</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4169</v>
+        <v>0.4319</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4169</v>
+        <v>0.2893</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4169</v>
+        <v>0.2893</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4169</v>
+        <v>0.2893</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4169</v>
+        <v>0.2893</v>
       </c>
       <c r="N43" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2893</v>
+        <v>0.3518</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1876</v>
+        <v>0.2281</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4925</v>
+        <v>-0.4567</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2893</v>
+        <v>0.3518</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2893</v>
+        <v>0.5193</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2893</v>
+        <v>0.5193</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2893</v>
+        <v>0.5193</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2893</v>
+        <v>0.5193</v>
       </c>
       <c r="N44" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1735</v>
+        <v>0.2815</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1125</v>
+        <v>0.1826</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5452</v>
+        <v>-0.4881</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1735</v>
+        <v>0.2815</v>
       </c>
       <c r="F45" t="n">
         <v>0.1735</v>
@@ -2520,22 +2520,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1724</v>
+        <v>0.1136</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1118</v>
+        <v>0.0737</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5457</v>
+        <v>-0.5631</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1724</v>
+        <v>0.1136</v>
       </c>
       <c r="F46" t="n">
         <v>-0.5417999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7148</v>
       </c>
       <c r="H46" t="n">
         <v>-0.5417999999999999</v>
@@ -2544,7 +2544,7 @@
         <v>-0.5417999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7148</v>
       </c>
       <c r="K46" t="n">
         <v>113</v>
@@ -2553,7 +2553,7 @@
         <v>101</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1724</v>
+        <v>0.173</v>
       </c>
       <c r="N46" t="n">
         <v>214</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1323</v>
+        <v>0.101</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0858</v>
+        <v>0.0655</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5687</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1323</v>
+        <v>0.101</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1323</v>
+        <v>0.1322</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1323</v>
+        <v>0.1322</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1323</v>
+        <v>0.1322</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1323</v>
+        <v>0.1322</v>
       </c>
       <c r="N47" t="n">
         <v>59</v>
@@ -2608,93 +2608,93 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0115</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0549</v>
+        <v>-0.0075</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5857</v>
+        <v>-0.619</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0115</v>
       </c>
       <c r="F48" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0675</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0675</v>
       </c>
       <c r="I48" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0675</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0675</v>
       </c>
       <c r="N48" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0412</v>
+        <v>-0.0377</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0267</v>
+        <v>-0.0244</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6054</v>
+        <v>-0.6307</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0412</v>
+        <v>-0.0377</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0412</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0412</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0412</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0412</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0103</v>
+        <v>-0.0394</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0067</v>
+        <v>-0.0256</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6289</v>
+        <v>-0.6314</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0103</v>
+        <v>-0.0394</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0103</v>
+        <v>-0.0102</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0103</v>
+        <v>-0.0102</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0103</v>
+        <v>-0.0102</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0103</v>
+        <v>-0.0102</v>
       </c>
       <c r="N50" t="n">
         <v>69</v>
@@ -2746,553 +2746,553 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0569</v>
+        <v>-0.0522</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0369</v>
+        <v>-0.0339</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6501</v>
+        <v>-0.6371</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0569</v>
+        <v>-0.0522</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3428</v>
+        <v>0.0412</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.3997</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3428</v>
+        <v>0.0412</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3428</v>
+        <v>0.0412</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.3997</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.05690000000000001</v>
+        <v>0.0412</v>
       </c>
       <c r="N51" t="n">
-        <v>102</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0675</v>
+        <v>-0.0622</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0438</v>
+        <v>-0.0403</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6549</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0675</v>
+        <v>-0.0622</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0675</v>
+        <v>-0.442</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0675</v>
+        <v>-0.442</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0675</v>
+        <v>-0.442</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="K52" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0675</v>
+        <v>-0.1599</v>
       </c>
       <c r="N52" t="n">
-        <v>42</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1149</v>
+        <v>-0.0828</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0745</v>
+        <v>-0.0537</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6765</v>
+        <v>-0.6508</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1149</v>
+        <v>-0.0828</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1149</v>
+        <v>0.3428</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.3997</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1149</v>
+        <v>0.3428</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1149</v>
+        <v>0.3428</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.3997</v>
       </c>
       <c r="K53" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1149</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1186</v>
+        <v>-0.1221</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0769</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6782</v>
+        <v>-0.6684</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1186</v>
+        <v>-0.1221</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1186</v>
+        <v>-0.4995</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.3814</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1186</v>
+        <v>-0.4995</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1186</v>
+        <v>-0.4995</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>0.3814</v>
       </c>
       <c r="K54" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1186</v>
+        <v>-0.1181</v>
       </c>
       <c r="N54" t="n">
-        <v>59</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.119</v>
+        <v>-0.167</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0772</v>
+        <v>-0.1083</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6784</v>
+        <v>-0.6884</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.119</v>
+        <v>-0.167</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.119</v>
+        <v>-0.1596</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.119</v>
+        <v>-0.1596</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.119</v>
+        <v>-0.1596</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.119</v>
+        <v>-0.1596</v>
       </c>
       <c r="N55" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.142</v>
+        <v>-0.177</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0921</v>
+        <v>-0.1148</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6888</v>
+        <v>-0.6929</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.142</v>
+        <v>-0.177</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.5243</v>
+        <v>-0.1043</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3823</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.5243</v>
+        <v>-0.1043</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5243</v>
+        <v>-0.1043</v>
       </c>
       <c r="J56" t="n">
-        <v>0.3823</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L56" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.142</v>
+        <v>-0.1043</v>
       </c>
       <c r="N56" t="n">
-        <v>134</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1596</v>
+        <v>-0.263</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1035</v>
+        <v>-0.1706</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6969</v>
+        <v>-0.7313</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1596</v>
+        <v>-0.263</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1596</v>
+        <v>-0.2403</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1596</v>
+        <v>-0.2403</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1596</v>
+        <v>-0.2403</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1596</v>
+        <v>-0.2403</v>
       </c>
       <c r="N57" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1596</v>
+        <v>-0.2978</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1035</v>
+        <v>-0.1931</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6969</v>
+        <v>-0.7468</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1596</v>
+        <v>-0.2978</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4417</v>
+        <v>-0.1186</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4417</v>
+        <v>-0.1186</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4417</v>
+        <v>-0.1186</v>
       </c>
       <c r="J58" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L58" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1596</v>
+        <v>-0.1186</v>
       </c>
       <c r="N58" t="n">
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2201</v>
+        <v>-0.3347</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1427</v>
+        <v>-0.2171</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7244</v>
+        <v>-0.7633</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2201</v>
+        <v>-0.3347</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2201</v>
+        <v>-0.3596</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2201</v>
+        <v>-0.3596</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2201</v>
+        <v>-0.3596</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2201</v>
+        <v>-0.3596</v>
       </c>
       <c r="N59" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2365</v>
+        <v>-0.378</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1534</v>
+        <v>-0.2451</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7319</v>
+        <v>-0.7827</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2365</v>
+        <v>-0.378</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4483</v>
+        <v>-0.3337</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.6848</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.4483</v>
+        <v>-0.3337</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4483</v>
+        <v>-0.3337</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.6848</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>69</v>
       </c>
       <c r="L60" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2365</v>
+        <v>-0.3337</v>
       </c>
       <c r="N60" t="n">
-        <v>134</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2403</v>
+        <v>-0.3862</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1558</v>
+        <v>-0.2505</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7336</v>
+        <v>-0.7863</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2403</v>
+        <v>-0.3862</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2403</v>
+        <v>-0.2201</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2403</v>
+        <v>-0.2201</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2403</v>
+        <v>-0.2201</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2403</v>
+        <v>-0.2201</v>
       </c>
       <c r="N61" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2884</v>
+        <v>-0.4123</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.187</v>
+        <v>-0.2674</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.798</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2884</v>
+        <v>-0.4123</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2884</v>
+        <v>0.4479</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.6853</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2884</v>
+        <v>0.4479</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2884</v>
+        <v>0.4479</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.6853</v>
       </c>
       <c r="K62" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2884</v>
+        <v>-0.2374</v>
       </c>
       <c r="N62" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63">
@@ -3302,31 +3302,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2988</v>
+        <v>-0.4251</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1938</v>
+        <v>-0.2757</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7602</v>
+        <v>-0.8037</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2988</v>
+        <v>-0.4251</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6269</v>
+        <v>0.6271</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.9257</v>
+        <v>-0.8902</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6269</v>
+        <v>0.6271</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6269</v>
+        <v>0.6271</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.9257</v>
+        <v>-0.8902</v>
       </c>
       <c r="K63" t="n">
         <v>55</v>
@@ -3335,7 +3335,7 @@
         <v>156</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2988</v>
+        <v>-0.2631</v>
       </c>
       <c r="N63" t="n">
         <v>211</v>
@@ -3344,185 +3344,185 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3339</v>
+        <v>-0.4587</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2165</v>
+        <v>-0.2975</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7762</v>
+        <v>-0.8187</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3339</v>
+        <v>-0.4587</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3339</v>
+        <v>0.634</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3339</v>
+        <v>0.634</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3339</v>
+        <v>0.634</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K64" t="n">
         <v>69</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3339</v>
+        <v>-0.366</v>
       </c>
       <c r="N64" t="n">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3595</v>
+        <v>-0.4737</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2331</v>
+        <v>-0.3072</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7879</v>
+        <v>-0.8254</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3595</v>
+        <v>-0.4737</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3595</v>
+        <v>-0.1146</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3595</v>
+        <v>-0.1146</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3595</v>
+        <v>-0.1146</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.3595</v>
+        <v>-0.1146</v>
       </c>
       <c r="N65" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3656</v>
+        <v>-0.6194</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2371</v>
+        <v>-0.4017</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7906</v>
+        <v>-0.8905</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3656</v>
+        <v>-0.6194</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6344</v>
+        <v>-0.4347</v>
       </c>
       <c r="G66" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6344</v>
+        <v>-0.4347</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6344</v>
+        <v>-0.4347</v>
       </c>
       <c r="J66" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L66" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3656</v>
+        <v>-0.4347</v>
       </c>
       <c r="N66" t="n">
-        <v>134</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4346</v>
+        <v>-0.6449</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2818</v>
+        <v>-0.4182</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.822</v>
+        <v>-0.9019</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4346</v>
+        <v>-0.6449</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4346</v>
+        <v>-0.2882</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4346</v>
+        <v>-0.2882</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4346</v>
+        <v>-0.2882</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.4346</v>
+        <v>-0.2882</v>
       </c>
       <c r="N67" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4998</v>
+        <v>-0.7562</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3241</v>
+        <v>-0.4904</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8517</v>
+        <v>-0.9516</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4998</v>
+        <v>-0.7562</v>
       </c>
       <c r="F68" t="n">
         <v>0.3302</v>
@@ -3574,185 +3574,185 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Alkaren</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5975</v>
+        <v>-0.7709</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3875</v>
+        <v>-0.4999</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8962</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5975</v>
+        <v>-0.7709</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5975</v>
+        <v>-0.5681</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5975</v>
+        <v>-0.5681</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5975</v>
+        <v>-0.5681</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
       <c r="K69" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5975</v>
+        <v>-0.6221000000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alkaren</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6219</v>
+        <v>-0.8186</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4033</v>
+        <v>-0.5309</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9073</v>
+        <v>-0.9795</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6219</v>
+        <v>-0.8186</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5679</v>
+        <v>-0.2033</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.054</v>
+        <v>-0.4625</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5679</v>
+        <v>-0.2033</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5679</v>
+        <v>-0.2033</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.054</v>
+        <v>-0.4625</v>
       </c>
       <c r="K70" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L70" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6219</v>
+        <v>-0.6658000000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6646</v>
+        <v>-0.8894</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.431</v>
+        <v>-0.5768</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9267</v>
+        <v>-1.0111</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6646</v>
+        <v>-0.8894</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.2028</v>
+        <v>-0.6673</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.4618</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.2028</v>
+        <v>-0.6673</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2028</v>
+        <v>-0.6673</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.4618</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L71" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6646</v>
+        <v>-0.6673</v>
       </c>
       <c r="N71" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6673</v>
+        <v>-0.9092</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4327</v>
+        <v>-0.5896</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.928</v>
+        <v>-1.0199</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6673</v>
+        <v>-0.9092</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6673</v>
+        <v>-0.8045</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>-0.1034</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6673</v>
+        <v>-0.8045</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6673</v>
+        <v>-0.8045</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>-0.1034</v>
       </c>
       <c r="K72" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6673</v>
+        <v>-0.9079</v>
       </c>
       <c r="N72" t="n">
-        <v>55</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73">
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.735</v>
+        <v>-0.9166</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4766</v>
+        <v>-0.5944</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9588</v>
+        <v>-1.0232</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.735</v>
+        <v>-0.9166</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6562</v>
+        <v>0.6558</v>
       </c>
       <c r="G73" t="n">
         <v>-1.3912</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6562</v>
+        <v>0.6558</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6562</v>
+        <v>0.6558</v>
       </c>
       <c r="J73" t="n">
         <v>-1.3912</v>
@@ -3795,7 +3795,7 @@
         <v>109</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.735</v>
+        <v>-0.7353999999999999</v>
       </c>
       <c r="N73" t="n">
         <v>205</v>
@@ -3804,78 +3804,78 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.9172</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4886</v>
+        <v>-0.5948</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.0235</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.9172</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.051</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>-0.735</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.051</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.051</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>-0.735</v>
       </c>
       <c r="K74" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.786</v>
       </c>
       <c r="N74" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.773</v>
+        <v>-0.9935</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5013</v>
+        <v>-0.6443</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9761</v>
+        <v>-1.0576</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.773</v>
+        <v>-0.9935</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.773</v>
+        <v>-0.5975</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.773</v>
+        <v>-0.5975</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.773</v>
+        <v>-0.5975</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.773</v>
+        <v>-0.5975</v>
       </c>
       <c r="N75" t="n">
         <v>36</v>
@@ -3896,185 +3896,185 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.7982</v>
+        <v>-1.05</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9876</v>
+        <v>-1.0828</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.7982</v>
+        <v>-1.05</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.735</v>
+        <v>-0.0298</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.735</v>
+        <v>-0.0298</v>
       </c>
       <c r="K76" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L76" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.7982</v>
+        <v>-0.9093</v>
       </c>
       <c r="N76" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.8457</v>
+        <v>-1.1529</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5484</v>
+        <v>-0.7477</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0092</v>
+        <v>-1.1288</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.8457</v>
+        <v>-1.1529</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8457</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8457</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.8457</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.8457</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="N77" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.9079</v>
+        <v>-1.1723</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5888</v>
+        <v>-0.7602</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0375</v>
+        <v>-1.1375</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9079</v>
+        <v>-1.1723</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.8045</v>
+        <v>-0.773</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1034</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.8045</v>
+        <v>-0.773</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.8045</v>
+        <v>-0.773</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.1034</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L78" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.9079</v>
+        <v>-0.773</v>
       </c>
       <c r="N78" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.9295</v>
+        <v>-1.2117</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6028</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0473</v>
+        <v>-1.1551</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9295</v>
+        <v>-1.2117</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.9</v>
+        <v>-0.8456</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.0295</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.9</v>
+        <v>-0.8456</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.9</v>
+        <v>-0.8456</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.0295</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L79" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.9295</v>
+        <v>-0.8456</v>
       </c>
       <c r="N79" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80">
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.1707</v>
+        <v>-1.4171</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7592</v>
+        <v>-0.919</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1571</v>
+        <v>-1.2468</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.1707</v>
+        <v>-1.4171</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.7633</v>
+        <v>-0.7871</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4074</v>
+        <v>-0.3855</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.7633</v>
+        <v>-0.7871</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7633</v>
+        <v>-0.7871</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.4074</v>
+        <v>-0.3855</v>
       </c>
       <c r="K80" t="n">
         <v>55</v>
@@ -4117,7 +4117,7 @@
         <v>156</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.1707</v>
+        <v>-1.1726</v>
       </c>
       <c r="N80" t="n">
         <v>211</v>
@@ -4130,22 +4130,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.9252</v>
+        <v>-2.1898</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.2485</v>
+        <v>-1.4201</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5006</v>
+        <v>-1.592</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.9252</v>
+        <v>-2.1898</v>
       </c>
       <c r="F81" t="n">
         <v>-1.6894</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.2357</v>
+        <v>-0.2354</v>
       </c>
       <c r="H81" t="n">
         <v>-1.6894</v>
@@ -4154,7 +4154,7 @@
         <v>-1.6894</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.2357</v>
+        <v>-0.2354</v>
       </c>
       <c r="K81" t="n">
         <v>113</v>
@@ -4163,7 +4163,7 @@
         <v>101</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.9251</v>
+        <v>-1.9248</v>
       </c>
       <c r="N81" t="n">
         <v>214</v>
@@ -5706,13 +5706,13 @@
         <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0416</v>
+        <v>-0.0567</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9152</v>
+        <v>-1.2474</v>
       </c>
     </row>
     <row r="39">
@@ -5826,13 +5826,13 @@
         <v>22</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.47</v>
+        <v>-0.4613</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.34</v>
+        <v>-10.1486</v>
       </c>
     </row>
     <row r="42">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0432</v>
+        <v>1.042</v>
       </c>
       <c r="J72" t="n">
-        <v>25.0368</v>
+        <v>25.008</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6453</v>
+        <v>0.6445</v>
       </c>
       <c r="J73" t="n">
-        <v>15.4872</v>
+        <v>15.468</v>
       </c>
     </row>
     <row r="74">
@@ -7146,13 +7146,13 @@
         <v>24</v>
       </c>
       <c r="H74" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0883</v>
+        <v>0.1238</v>
       </c>
       <c r="J74" t="n">
-        <v>2.1192</v>
+        <v>2.9712</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6041</v>
+        <v>-0.6048</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.4984</v>
+        <v>-14.5152</v>
       </c>
     </row>
     <row r="76">
@@ -7226,13 +7226,13 @@
         <v>24</v>
       </c>
       <c r="H76" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.6278</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.5928</v>
+        <v>-15.0672</v>
       </c>
     </row>
     <row r="77">
@@ -7866,13 +7866,13 @@
         <v>22</v>
       </c>
       <c r="H92" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5889</v>
+        <v>0.5808</v>
       </c>
       <c r="J92" t="n">
-        <v>12.9558</v>
+        <v>12.7776</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4663</v>
+        <v>0.4667</v>
       </c>
       <c r="J93" t="n">
-        <v>10.2586</v>
+        <v>10.2674</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0439</v>
+        <v>-0.0438</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.9658</v>
+        <v>-0.9636</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1598</v>
+        <v>-0.1596</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.5156</v>
+        <v>-3.5112</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.46</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5576</v>
+        <v>-0.5575</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.2672</v>
+        <v>-12.265</v>
       </c>
     </row>
     <row r="97">
@@ -8466,13 +8466,13 @@
         <v>20</v>
       </c>
       <c r="H107" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8082</v>
+        <v>0.8183</v>
       </c>
       <c r="J107" t="n">
-        <v>16.164</v>
+        <v>16.366</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4376</v>
+        <v>0.4371</v>
       </c>
       <c r="J108" t="n">
-        <v>8.752000000000001</v>
+        <v>8.742000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.85</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1989</v>
+        <v>-0.1991</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.978</v>
+        <v>-3.982</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3543</v>
+        <v>-0.3545</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.086</v>
+        <v>-7.09</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4349</v>
+        <v>-0.435</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.698</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -9669,10 +9669,10 @@
         <v>1.61</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8861</v>
+        <v>0.885</v>
       </c>
       <c r="J137" t="n">
-        <v>20.3803</v>
+        <v>20.355</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.267</v>
+        <v>0.2663</v>
       </c>
       <c r="J138" t="n">
-        <v>6.141</v>
+        <v>6.1249</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.126</v>
+        <v>-0.1263</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.898</v>
+        <v>-2.9049</v>
       </c>
     </row>
     <row r="140">
@@ -9786,13 +9786,13 @@
         <v>23</v>
       </c>
       <c r="H140" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2843</v>
+        <v>-0.2749</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.5389</v>
+        <v>-6.3227</v>
       </c>
     </row>
     <row r="141">
@@ -9826,13 +9826,13 @@
         <v>23</v>
       </c>
       <c r="H141" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3223</v>
+        <v>-0.3132</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.4129</v>
+        <v>-7.2036</v>
       </c>
     </row>
     <row r="142">
@@ -10869,10 +10869,10 @@
         <v>2.73</v>
       </c>
       <c r="I167" t="n">
-        <v>2.353</v>
+        <v>2.3538</v>
       </c>
       <c r="J167" t="n">
-        <v>40.001</v>
+        <v>40.0146</v>
       </c>
     </row>
     <row r="168">
@@ -10906,13 +10906,13 @@
         <v>17</v>
       </c>
       <c r="H168" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5728</v>
+        <v>0.5574</v>
       </c>
       <c r="J168" t="n">
-        <v>9.7376</v>
+        <v>9.4758</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4765</v>
+        <v>0.4767</v>
       </c>
       <c r="J169" t="n">
-        <v>8.1005</v>
+        <v>8.103899999999999</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.191</v>
+        <v>0.1913</v>
       </c>
       <c r="J170" t="n">
-        <v>3.247</v>
+        <v>3.2521</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3049</v>
+        <v>-0.3046</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.1833</v>
+        <v>-5.1782</v>
       </c>
     </row>
     <row r="172">
@@ -11269,10 +11269,10 @@
         <v>1.73</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2498</v>
+        <v>1.2503</v>
       </c>
       <c r="J177" t="n">
-        <v>26.2458</v>
+        <v>26.2563</v>
       </c>
     </row>
     <row r="178">
@@ -11306,13 +11306,13 @@
         <v>21</v>
       </c>
       <c r="H178" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8787</v>
+        <v>0.8652</v>
       </c>
       <c r="J178" t="n">
-        <v>18.4527</v>
+        <v>18.1692</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2759</v>
+        <v>0.2762</v>
       </c>
       <c r="J179" t="n">
-        <v>5.7939</v>
+        <v>5.8002</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0419</v>
+        <v>-0.0415</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.8799</v>
+        <v>-0.8715000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.97</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1798</v>
+        <v>-0.1795</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.7758</v>
+        <v>-3.7695</v>
       </c>
     </row>
     <row r="182">
@@ -12069,10 +12069,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7583</v>
+        <v>0.7579</v>
       </c>
       <c r="J197" t="n">
-        <v>16.6826</v>
+        <v>16.6738</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5639</v>
+        <v>0.5636</v>
       </c>
       <c r="J198" t="n">
-        <v>12.4058</v>
+        <v>12.3992</v>
       </c>
     </row>
     <row r="199">
@@ -12146,13 +12146,13 @@
         <v>22</v>
       </c>
       <c r="H199" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1326</v>
+        <v>0.1477</v>
       </c>
       <c r="J199" t="n">
-        <v>2.9172</v>
+        <v>3.2494</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3665</v>
+        <v>-0.3667</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.063000000000001</v>
+        <v>-8.067399999999999</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.64</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4112</v>
+        <v>-0.4114</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.0464</v>
+        <v>-9.050800000000001</v>
       </c>
     </row>
     <row r="202">
@@ -12466,13 +12466,13 @@
         <v>21</v>
       </c>
       <c r="H207" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5342</v>
       </c>
       <c r="J207" t="n">
-        <v>10.9767</v>
+        <v>11.2182</v>
       </c>
     </row>
     <row r="208">
@@ -12506,13 +12506,13 @@
         <v>21</v>
       </c>
       <c r="H208" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2082</v>
+        <v>-0.1986</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.3722</v>
+        <v>-4.1706</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2279</v>
+        <v>-0.2282</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.7859</v>
+        <v>-4.7922</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2856</v>
+        <v>-0.2861</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.9976</v>
+        <v>-6.0081</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4316</v>
+        <v>-0.432</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.063599999999999</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.4497</v>
+        <v>-1.4573</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.4497</v>
+        <v>-1.4573</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1822</v>
+        <v>-0.1825</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.4618</v>
+        <v>-3.4675</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4156</v>
+        <v>-0.4159</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.8964</v>
+        <v>-7.9021</v>
       </c>
     </row>
     <row r="216">
@@ -12826,13 +12826,13 @@
         <v>19</v>
       </c>
       <c r="H216" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4422</v>
+        <v>-0.4336</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.4018</v>
+        <v>-8.2384</v>
       </c>
     </row>
     <row r="217">
@@ -13066,13 +13066,13 @@
         <v>17</v>
       </c>
       <c r="H222" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3518</v>
+        <v>1.3394</v>
       </c>
       <c r="J222" t="n">
-        <v>22.9806</v>
+        <v>22.7698</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.32</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7886</v>
+        <v>0.7889</v>
       </c>
       <c r="J223" t="n">
-        <v>13.4062</v>
+        <v>13.4113</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.13</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3821</v>
+        <v>0.3824</v>
       </c>
       <c r="J224" t="n">
-        <v>6.4957</v>
+        <v>6.5008</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>1.02</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0635</v>
+        <v>0.0638</v>
       </c>
       <c r="J225" t="n">
-        <v>1.0795</v>
+        <v>1.0846</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2096</v>
+        <v>-0.2092</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.5632</v>
+        <v>-3.5564</v>
       </c>
     </row>
     <row r="227">
@@ -13469,10 +13469,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2481</v>
+        <v>1.2474</v>
       </c>
       <c r="J232" t="n">
-        <v>28.7063</v>
+        <v>28.6902</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.52</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1643</v>
+        <v>1.1637</v>
       </c>
       <c r="J233" t="n">
-        <v>26.7789</v>
+        <v>26.7651</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.509</v>
       </c>
       <c r="J234" t="n">
-        <v>-11.6978</v>
+        <v>-11.707</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.77</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6711</v>
+        <v>-0.6715</v>
       </c>
       <c r="J235" t="n">
-        <v>-15.4353</v>
+        <v>-15.4445</v>
       </c>
     </row>
     <row r="236">
@@ -13626,13 +13626,13 @@
         <v>23</v>
       </c>
       <c r="H236" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8872</v>
+        <v>-0.8666</v>
       </c>
       <c r="J236" t="n">
-        <v>-20.4056</v>
+        <v>-19.9318</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.63</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0506</v>
+        <v>1.05</v>
       </c>
       <c r="J237" t="n">
-        <v>24.1638</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="238">
@@ -13706,13 +13706,13 @@
         <v>23</v>
       </c>
       <c r="H238" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6496</v>
+        <v>0.6643</v>
       </c>
       <c r="J238" t="n">
-        <v>14.9408</v>
+        <v>15.2789</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2151</v>
+        <v>-0.2153</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.9473</v>
+        <v>-4.9519</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.71</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3416</v>
+        <v>-0.3417</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.8568</v>
+        <v>-7.8591</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3871</v>
+        <v>-0.3872</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.9033</v>
+        <v>-8.9056</v>
       </c>
     </row>
     <row r="242">
@@ -14066,13 +14066,13 @@
         <v>22</v>
       </c>
       <c r="H247" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2534</v>
+        <v>1.2789</v>
       </c>
       <c r="J247" t="n">
-        <v>27.5748</v>
+        <v>28.1358</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.56</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1864</v>
+        <v>1.1854</v>
       </c>
       <c r="J248" t="n">
-        <v>26.1008</v>
+        <v>26.0788</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0266</v>
+        <v>0.0259</v>
       </c>
       <c r="J249" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5698</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.99</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.093</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J250" t="n">
-        <v>-2.046</v>
+        <v>-2.0636</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.82</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5786</v>
+        <v>-0.5793</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.7292</v>
+        <v>-12.7446</v>
       </c>
     </row>
     <row r="252">
@@ -14469,10 +14469,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0294</v>
+        <v>1.0298</v>
       </c>
       <c r="J257" t="n">
-        <v>20.588</v>
+        <v>20.596</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9984</v>
+        <v>0.9987</v>
       </c>
       <c r="J258" t="n">
-        <v>19.968</v>
+        <v>19.974</v>
       </c>
     </row>
     <row r="259">
@@ -14546,13 +14546,13 @@
         <v>20</v>
       </c>
       <c r="H259" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8161</v>
+        <v>0.7972</v>
       </c>
       <c r="J259" t="n">
-        <v>16.322</v>
+        <v>15.944</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.12</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3458</v>
+        <v>0.3461</v>
       </c>
       <c r="J260" t="n">
-        <v>6.916</v>
+        <v>6.922</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>1.12</v>
       </c>
       <c r="I261" t="n">
-        <v>0.3458</v>
+        <v>0.3461</v>
       </c>
       <c r="J261" t="n">
-        <v>6.916</v>
+        <v>6.922</v>
       </c>
     </row>
     <row r="262">
@@ -14866,13 +14866,13 @@
         <v>19</v>
       </c>
       <c r="H267" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2809</v>
+        <v>0.2963</v>
       </c>
       <c r="J267" t="n">
-        <v>5.3371</v>
+        <v>5.6297</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1417</v>
+        <v>-0.1421</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.6923</v>
+        <v>-2.6999</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.62</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3923</v>
+        <v>-0.3925</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.4537</v>
+        <v>-7.4575</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.61</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4012</v>
+        <v>-0.4014</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.6228</v>
+        <v>-7.6266</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.45</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5417</v>
+        <v>-0.5419</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.2923</v>
+        <v>-10.2961</v>
       </c>
     </row>
     <row r="272">
@@ -15669,10 +15669,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1466</v>
+        <v>1.1471</v>
       </c>
       <c r="J287" t="n">
-        <v>22.932</v>
+        <v>22.942</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8738</v>
+        <v>0.8743</v>
       </c>
       <c r="J288" t="n">
-        <v>17.476</v>
+        <v>17.486</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3867</v>
+        <v>0.387</v>
       </c>
       <c r="J289" t="n">
-        <v>7.734</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.11</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3369</v>
+        <v>0.3373</v>
       </c>
       <c r="J290" t="n">
-        <v>6.738</v>
+        <v>6.746</v>
       </c>
     </row>
     <row r="291">
@@ -15826,13 +15826,13 @@
         <v>20</v>
       </c>
       <c r="H291" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5304</v>
+        <v>-0.554</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.608</v>
+        <v>-11.08</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.99</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0347</v>
+        <v>1.035</v>
       </c>
       <c r="J292" t="n">
-        <v>18.6246</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="293">
@@ -15906,13 +15906,13 @@
         <v>18</v>
       </c>
       <c r="H293" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5607</v>
+        <v>0.5511</v>
       </c>
       <c r="J293" t="n">
-        <v>10.0926</v>
+        <v>9.9198</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.45</v>
       </c>
       <c r="I294" t="n">
-        <v>0.551</v>
+        <v>0.5511</v>
       </c>
       <c r="J294" t="n">
-        <v>9.917999999999999</v>
+        <v>9.9198</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2454</v>
+        <v>0.2456</v>
       </c>
       <c r="J295" t="n">
-        <v>4.4172</v>
+        <v>4.4208</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>1.01</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.0037</v>
+        <v>-0.0036</v>
       </c>
       <c r="J296" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0648</v>
       </c>
     </row>
     <row r="297">
@@ -16469,10 +16469,10 @@
         <v>1.96</v>
       </c>
       <c r="I307" t="n">
-        <v>1.6401</v>
+        <v>1.6397</v>
       </c>
       <c r="J307" t="n">
-        <v>26.2416</v>
+        <v>26.2352</v>
       </c>
     </row>
     <row r="308">
@@ -16506,13 +16506,13 @@
         <v>16</v>
       </c>
       <c r="H308" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I308" t="n">
-        <v>1.2874</v>
+        <v>1.2996</v>
       </c>
       <c r="J308" t="n">
-        <v>20.5984</v>
+        <v>20.7936</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.54</v>
       </c>
       <c r="I309" t="n">
-        <v>1.1221</v>
+        <v>1.1218</v>
       </c>
       <c r="J309" t="n">
-        <v>17.9536</v>
+        <v>17.9488</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2056</v>
+        <v>-0.2058</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.2896</v>
+        <v>-3.2928</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.92</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.359</v>
+        <v>-0.3593</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.744</v>
+        <v>-5.7488</v>
       </c>
     </row>
     <row r="312">
@@ -18869,10 +18869,10 @@
         <v>1.3</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5783</v>
+        <v>0.5779</v>
       </c>
       <c r="J367" t="n">
-        <v>13.3009</v>
+        <v>13.2917</v>
       </c>
     </row>
     <row r="368">
@@ -18906,13 +18906,13 @@
         <v>23</v>
       </c>
       <c r="H368" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I368" t="n">
-        <v>0.4014</v>
+        <v>0.4178</v>
       </c>
       <c r="J368" t="n">
-        <v>9.232200000000001</v>
+        <v>9.609400000000001</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.03</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0926</v>
+        <v>0.0924</v>
       </c>
       <c r="J369" t="n">
-        <v>2.1298</v>
+        <v>2.1252</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.97</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.064</v>
+        <v>-0.0641</v>
       </c>
       <c r="J370" t="n">
-        <v>-1.472</v>
+        <v>-1.4743</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1648</v>
+        <v>-0.1649</v>
       </c>
       <c r="J371" t="n">
-        <v>-3.7904</v>
+        <v>-3.7927</v>
       </c>
     </row>
     <row r="372">
@@ -19558,7 +19558,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -19598,7 +19598,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -19869,10 +19869,10 @@
         <v>1.54</v>
       </c>
       <c r="I392" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9579</v>
       </c>
       <c r="J392" t="n">
-        <v>22.9728</v>
+        <v>22.9896</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.02</v>
       </c>
       <c r="I393" t="n">
-        <v>0.0743</v>
+        <v>0.0746</v>
       </c>
       <c r="J393" t="n">
-        <v>1.7832</v>
+        <v>1.7904</v>
       </c>
     </row>
     <row r="394">
@@ -19946,13 +19946,13 @@
         <v>24</v>
       </c>
       <c r="H394" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.1463</v>
+        <v>-0.1574</v>
       </c>
       <c r="J394" t="n">
-        <v>-3.5112</v>
+        <v>-3.7776</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.78</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2713</v>
+        <v>-0.2712</v>
       </c>
       <c r="J395" t="n">
-        <v>-6.5112</v>
+        <v>-6.5088</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.72</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3285</v>
+        <v>-0.3283</v>
       </c>
       <c r="J396" t="n">
-        <v>-7.884</v>
+        <v>-7.8792</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.39</v>
       </c>
       <c r="I397" t="n">
-        <v>0.9641</v>
+        <v>0.9635</v>
       </c>
       <c r="J397" t="n">
-        <v>23.1384</v>
+        <v>23.124</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.16</v>
       </c>
       <c r="I398" t="n">
-        <v>0.4738</v>
+        <v>0.4734</v>
       </c>
       <c r="J398" t="n">
-        <v>11.3712</v>
+        <v>11.3616</v>
       </c>
     </row>
     <row r="399">
@@ -20146,13 +20146,13 @@
         <v>24</v>
       </c>
       <c r="H399" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3521</v>
+        <v>0.3769</v>
       </c>
       <c r="J399" t="n">
-        <v>8.4504</v>
+        <v>9.0456</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.99</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0718</v>
       </c>
       <c r="J400" t="n">
-        <v>-1.7136</v>
+        <v>-1.7232</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.74</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.7379</v>
+        <v>-0.7383</v>
       </c>
       <c r="J401" t="n">
-        <v>-17.7096</v>
+        <v>-17.7192</v>
       </c>
     </row>
     <row r="402">

--- a/database/event/8039/event_8039_evp_summary.xlsx
+++ b/database/event/8039/event_8039_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.4214</v>
+        <v>8.447699999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>5.4613</v>
+        <v>5.4784</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1478</v>
+        <v>3.2425</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4214</v>
+        <v>8.447699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0857</v>
+        <v>2.0961</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1908</v>
+        <v>6.2067</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0857</v>
+        <v>2.0961</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0857</v>
+        <v>2.0961</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4036</v>
+        <v>6.5196</v>
       </c>
       <c r="K2" t="n">
         <v>36</v>
@@ -529,7 +529,7 @@
         <v>197</v>
       </c>
       <c r="M2" t="n">
-        <v>8.4893</v>
+        <v>8.6157</v>
       </c>
       <c r="N2" t="n">
         <v>233</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6987</v>
+        <v>7.6091</v>
       </c>
       <c r="C3" t="n">
-        <v>4.9926</v>
+        <v>4.9345</v>
       </c>
       <c r="D3" t="n">
-        <v>2.825</v>
+        <v>2.8605</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6987</v>
+        <v>7.6091</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8953</v>
+        <v>1.9346</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5462</v>
+        <v>5.4173</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8953</v>
+        <v>1.9346</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8953</v>
+        <v>1.9346</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5462</v>
+        <v>5.4173</v>
       </c>
       <c r="K3" t="n">
         <v>55</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>7.4415</v>
+        <v>7.351900000000001</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1063</v>
+        <v>6.1924</v>
       </c>
       <c r="C4" t="n">
-        <v>3.96</v>
+        <v>4.0158</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1137</v>
+        <v>2.2151</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1063</v>
+        <v>6.1924</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4877</v>
+        <v>2.4953</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5342</v>
+        <v>3.6127</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7198</v>
+        <v>2.7683</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7198</v>
+        <v>2.7683</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5342</v>
+        <v>3.6127</v>
       </c>
       <c r="K4" t="n">
         <v>36</v>
@@ -621,7 +621,7 @@
         <v>197</v>
       </c>
       <c r="M4" t="n">
-        <v>6.254</v>
+        <v>6.381</v>
       </c>
       <c r="N4" t="n">
         <v>233</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8941</v>
+        <v>5.9283</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8223</v>
+        <v>3.8445</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0189</v>
+        <v>2.0948</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8941</v>
+        <v>5.9283</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9894</v>
+        <v>2.0368</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7297</v>
+        <v>3.7164</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9894</v>
+        <v>2.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9894</v>
+        <v>2.0368</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7297</v>
+        <v>3.7164</v>
       </c>
       <c r="K5" t="n">
         <v>113</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7191</v>
+        <v>5.7532</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2787</v>
+        <v>4.3669</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7747</v>
+        <v>2.8319</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2974</v>
+        <v>1.3835</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2787</v>
+        <v>4.3669</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1597</v>
+        <v>-0.1479</v>
       </c>
       <c r="G6" t="n">
-        <v>4.357</v>
+        <v>4.4334</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1597</v>
+        <v>-0.1479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1597</v>
+        <v>-0.1479</v>
       </c>
       <c r="J6" t="n">
-        <v>4.357</v>
+        <v>4.4334</v>
       </c>
       <c r="K6" t="n">
         <v>36</v>
@@ -713,7 +713,7 @@
         <v>197</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1973</v>
+        <v>4.2855</v>
       </c>
       <c r="N6" t="n">
         <v>233</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2116</v>
+        <v>4.1275</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7312</v>
+        <v>2.6767</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2674</v>
+        <v>1.2745</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2116</v>
+        <v>4.1275</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9612</v>
+        <v>2.95</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0128</v>
+        <v>0.9399</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7562</v>
+        <v>3.8104</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7562</v>
+        <v>3.8104</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0128</v>
+        <v>0.9399</v>
       </c>
       <c r="K7" t="n">
         <v>96</v>
@@ -759,7 +759,7 @@
         <v>109</v>
       </c>
       <c r="M7" t="n">
-        <v>4.769</v>
+        <v>4.7503</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.812</v>
+        <v>3.7704</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4721</v>
+        <v>2.4451</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0889</v>
+        <v>1.1118</v>
       </c>
       <c r="E8" t="n">
-        <v>3.812</v>
+        <v>3.7704</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8289</v>
+        <v>2.799</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7802</v>
+        <v>0.7685</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4667</v>
+        <v>3.4643</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4667</v>
+        <v>3.4643</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7802</v>
+        <v>0.7685</v>
       </c>
       <c r="K8" t="n">
         <v>96</v>
@@ -805,7 +805,7 @@
         <v>109</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2469</v>
+        <v>4.2328</v>
       </c>
       <c r="N8" t="n">
         <v>205</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7765</v>
+        <v>3.7451</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4491</v>
+        <v>2.4287</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0731</v>
+        <v>1.1003</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7765</v>
+        <v>3.7451</v>
       </c>
       <c r="F9" t="n">
-        <v>1.652</v>
+        <v>1.6582</v>
       </c>
       <c r="G9" t="n">
-        <v>1.985</v>
+        <v>1.9474</v>
       </c>
       <c r="H9" t="n">
-        <v>1.652</v>
+        <v>1.6582</v>
       </c>
       <c r="I9" t="n">
-        <v>1.652</v>
+        <v>1.6582</v>
       </c>
       <c r="J9" t="n">
-        <v>1.985</v>
+        <v>1.9474</v>
       </c>
       <c r="K9" t="n">
         <v>55</v>
@@ -851,7 +851,7 @@
         <v>156</v>
       </c>
       <c r="M9" t="n">
-        <v>3.637</v>
+        <v>3.6056</v>
       </c>
       <c r="N9" t="n">
         <v>211</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6278</v>
+        <v>3.4761</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3526</v>
+        <v>2.2543</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0066</v>
+        <v>0.9777</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6278</v>
+        <v>3.4761</v>
       </c>
       <c r="F10" t="n">
-        <v>1.578</v>
+        <v>1.5286</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8978</v>
+        <v>1.7955</v>
       </c>
       <c r="H10" t="n">
-        <v>1.578</v>
+        <v>1.5286</v>
       </c>
       <c r="I10" t="n">
-        <v>1.578</v>
+        <v>1.5286</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8978</v>
+        <v>1.7955</v>
       </c>
       <c r="K10" t="n">
         <v>55</v>
@@ -897,7 +897,7 @@
         <v>156</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4758</v>
+        <v>3.3241</v>
       </c>
       <c r="N10" t="n">
         <v>211</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3283</v>
+        <v>3.223</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1584</v>
+        <v>2.0901</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8729</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3283</v>
+        <v>3.223</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5685</v>
+        <v>1.5181</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6682</v>
+        <v>1.6133</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5685</v>
+        <v>1.5181</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5685</v>
+        <v>1.5181</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6682</v>
+        <v>1.6133</v>
       </c>
       <c r="K11" t="n">
         <v>113</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2367</v>
+        <v>3.1314</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0267</v>
+        <v>2.9814</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9628</v>
+        <v>1.9334</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7381</v>
+        <v>0.7524</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0267</v>
+        <v>2.9814</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7842</v>
+        <v>1.7895</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0812</v>
+        <v>1.0306</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7842</v>
+        <v>1.7895</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7842</v>
+        <v>1.7895</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0812</v>
+        <v>1.0306</v>
       </c>
       <c r="K12" t="n">
         <v>64</v>
@@ -989,7 +989,7 @@
         <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8654</v>
+        <v>2.8201</v>
       </c>
       <c r="N12" t="n">
         <v>108</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6966</v>
+        <v>2.7096</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7488</v>
+        <v>1.7572</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5907</v>
+        <v>0.6286</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6966</v>
+        <v>2.7096</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5902</v>
+        <v>1.5672</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1114</v>
+        <v>1.1474</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5902</v>
+        <v>1.5672</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5902</v>
+        <v>1.5672</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1114</v>
+        <v>1.1474</v>
       </c>
       <c r="K13" t="n">
         <v>96</v>
@@ -1035,7 +1035,7 @@
         <v>109</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7016</v>
+        <v>2.7146</v>
       </c>
       <c r="N13" t="n">
         <v>205</v>
@@ -1044,127 +1044,127 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5841</v>
+        <v>2.5269</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6758</v>
+        <v>1.6387</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5404</v>
+        <v>0.5453</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5841</v>
+        <v>2.5269</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1256</v>
+        <v>1.5308</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.9709</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1256</v>
+        <v>1.5308</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1256</v>
+        <v>1.5308</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.9709</v>
       </c>
       <c r="K14" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1256</v>
+        <v>2.5017</v>
       </c>
       <c r="N14" t="n">
-        <v>64</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5357</v>
+        <v>2.412</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6444</v>
+        <v>1.5642</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5188</v>
+        <v>0.493</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5357</v>
+        <v>2.412</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5584</v>
+        <v>1.9535</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9520999999999999</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5584</v>
+        <v>1.9535</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5584</v>
+        <v>1.9535</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9520999999999999</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L15" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5105</v>
+        <v>1.9535</v>
       </c>
       <c r="N15" t="n">
-        <v>233</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4026</v>
+        <v>2.4008</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5581</v>
+        <v>1.5569</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4594</v>
+        <v>0.4879</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4026</v>
+        <v>2.4008</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6204</v>
+        <v>2.1168</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6979</v>
+        <v>-0.0059</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6204</v>
+        <v>2.1168</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6204</v>
+        <v>2.1168</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6979</v>
+        <v>-0.0059</v>
       </c>
       <c r="K16" t="n">
         <v>59</v>
@@ -1173,7 +1173,7 @@
         <v>66</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3183</v>
+        <v>2.1109</v>
       </c>
       <c r="N16" t="n">
         <v>125</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3733</v>
+        <v>2.3393</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5391</v>
+        <v>1.517</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4463</v>
+        <v>0.4599</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3733</v>
+        <v>2.3393</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8844</v>
+        <v>1.6277</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.6273</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8844</v>
+        <v>1.6277</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8844</v>
+        <v>1.6277</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.6273</v>
       </c>
       <c r="K17" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8844</v>
+        <v>2.255</v>
       </c>
       <c r="N17" t="n">
-        <v>55</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3642</v>
+        <v>2.2486</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5332</v>
+        <v>1.4582</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4422</v>
+        <v>0.4186</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3642</v>
+        <v>2.2486</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0695</v>
+        <v>1.7597</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0695</v>
+        <v>1.7597</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0695</v>
+        <v>1.7597</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0743</v>
+        <v>1.7597</v>
       </c>
       <c r="N18" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9345</v>
+        <v>1.869</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2545</v>
+        <v>1.2121</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2503</v>
+        <v>0.2456</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9345</v>
+        <v>1.869</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4224</v>
+        <v>1.3569</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4224</v>
+        <v>1.3569</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4224</v>
+        <v>1.3569</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4224</v>
+        <v>1.3569</v>
       </c>
       <c r="N19" t="n">
         <v>59</v>
@@ -1320,323 +1320,323 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.646</v>
+        <v>1.6799</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0674</v>
+        <v>1.0894</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1214</v>
+        <v>0.1595</v>
       </c>
       <c r="E20" t="n">
-        <v>1.646</v>
+        <v>1.6799</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4959</v>
+        <v>2.0511</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.423</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4959</v>
+        <v>2.0511</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4959</v>
+        <v>2.0511</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.423</v>
       </c>
       <c r="K20" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4959</v>
+        <v>1.6281</v>
       </c>
       <c r="N20" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6222</v>
+        <v>1.6273</v>
       </c>
       <c r="C21" t="n">
-        <v>1.052</v>
+        <v>1.0553</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1108</v>
+        <v>0.1355</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6222</v>
+        <v>1.6273</v>
       </c>
       <c r="F21" t="n">
-        <v>2.031</v>
+        <v>2.0188</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4606</v>
+        <v>-0.4363</v>
       </c>
       <c r="H21" t="n">
-        <v>2.031</v>
+        <v>2.0188</v>
       </c>
       <c r="I21" t="n">
-        <v>2.031</v>
+        <v>2.0188</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4606</v>
+        <v>-0.4363</v>
       </c>
       <c r="K21" t="n">
         <v>64</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5704</v>
+        <v>1.5825</v>
       </c>
       <c r="N21" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5699</v>
+        <v>1.5468</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0181</v>
+        <v>1.0031</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0989</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5699</v>
+        <v>1.5468</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9786</v>
+        <v>1.3967</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4535</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9786</v>
+        <v>1.3967</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9786</v>
+        <v>1.3967</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4535</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5251</v>
+        <v>1.3967</v>
       </c>
       <c r="N22" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5408</v>
+        <v>1.5129</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9992</v>
+        <v>0.9811</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0834</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5408</v>
+        <v>1.5129</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0363</v>
+        <v>1.1854</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3603</v>
+        <v>0.1699</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0363</v>
+        <v>1.1854</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0363</v>
+        <v>1.1854</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3603</v>
+        <v>0.1699</v>
       </c>
       <c r="K23" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3966</v>
+        <v>1.3553</v>
       </c>
       <c r="N23" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4378</v>
+        <v>1.4487</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9324</v>
+        <v>0.9395</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0284</v>
+        <v>0.0542</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4378</v>
+        <v>1.4487</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1087</v>
+        <v>0.9853</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1715</v>
+        <v>0.3192</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1087</v>
+        <v>0.9853</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1087</v>
+        <v>0.9853</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1715</v>
+        <v>0.3192</v>
       </c>
       <c r="K24" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L24" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2802</v>
+        <v>1.3045</v>
       </c>
       <c r="N24" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3123</v>
+        <v>1.1876</v>
       </c>
       <c r="C25" t="n">
-        <v>0.851</v>
+        <v>0.7702</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0276</v>
+        <v>-0.0648</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3123</v>
+        <v>1.1876</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2467</v>
+        <v>1.0324</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2467</v>
+        <v>1.0324</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2467</v>
+        <v>1.0324</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2467</v>
+        <v>1.0324</v>
       </c>
       <c r="N25" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2955</v>
+        <v>1.1725</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8401</v>
+        <v>0.7604</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0351</v>
+        <v>-0.0717</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2955</v>
+        <v>1.1725</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1403</v>
+        <v>0.58</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.7328</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1403</v>
+        <v>0.58</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1403</v>
+        <v>0.58</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.7328</v>
       </c>
       <c r="K26" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1403</v>
+        <v>1.3128</v>
       </c>
       <c r="N26" t="n">
-        <v>59</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.275</v>
+        <v>1.1618</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8268</v>
+        <v>0.7534</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0443</v>
+        <v>-0.0765</v>
       </c>
       <c r="E27" t="n">
-        <v>1.275</v>
+        <v>1.1618</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.8329</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.8329</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.8329</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.8329</v>
       </c>
       <c r="N27" t="n">
         <v>64</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1673</v>
+        <v>1.1355</v>
       </c>
       <c r="C28" t="n">
-        <v>0.757</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0924</v>
+        <v>-0.0885</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1673</v>
+        <v>1.1355</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6026</v>
+        <v>1.0699</v>
       </c>
       <c r="G28" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6026</v>
+        <v>1.0699</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6026</v>
+        <v>1.0699</v>
       </c>
       <c r="J28" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L28" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3076</v>
+        <v>1.0699</v>
       </c>
       <c r="N28" t="n">
-        <v>205</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0403</v>
+        <v>1.0228</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6746</v>
+        <v>0.6633</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1491</v>
+        <v>-0.1399</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0403</v>
+        <v>1.0228</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9486</v>
+        <v>0.6197</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9486</v>
+        <v>0.6197</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9486</v>
+        <v>0.6197</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="K29" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9486</v>
+        <v>1.1527</v>
       </c>
       <c r="N29" t="n">
-        <v>64</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0308</v>
+        <v>0.8911</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6685</v>
+        <v>0.5779</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1534</v>
+        <v>-0.1998</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0308</v>
+        <v>0.8911</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5855</v>
+        <v>0.7994</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5752</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5855</v>
+        <v>0.7994</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5855</v>
+        <v>0.7994</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5752</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L30" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1607</v>
+        <v>0.7994</v>
       </c>
       <c r="N30" t="n">
-        <v>233</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9459</v>
+        <v>0.8698</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.5641</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1913</v>
+        <v>-0.2096</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9459</v>
+        <v>0.8698</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6895</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6895</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6895</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6895</v>
       </c>
       <c r="N31" t="n">
         <v>59</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8698</v>
+        <v>0.863</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5641</v>
+        <v>0.5597</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2253</v>
+        <v>-0.2127</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8698</v>
+        <v>0.863</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8899</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8899</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8899</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8899</v>
       </c>
       <c r="N32" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8636</v>
+        <v>0.8238</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5342</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2281</v>
+        <v>-0.2305</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8636</v>
+        <v>0.8238</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8905</v>
+        <v>0.5681</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.1606</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8905</v>
+        <v>0.5681</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8905</v>
+        <v>0.5681</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.1606</v>
       </c>
       <c r="K33" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8905</v>
+        <v>0.7287</v>
       </c>
       <c r="N33" t="n">
-        <v>59</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8305</v>
+        <v>0.7642</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5386</v>
+        <v>0.4956</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2429</v>
+        <v>-0.2577</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8305</v>
+        <v>0.7642</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.8042</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2127</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.8042</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.8042</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2127</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L34" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.8042</v>
       </c>
       <c r="N34" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7572</v>
+        <v>0.7111</v>
       </c>
       <c r="C35" t="n">
-        <v>0.491</v>
+        <v>0.4612</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2756</v>
+        <v>-0.2818</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7572</v>
+        <v>0.7111</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6838</v>
+        <v>0.3766</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6838</v>
+        <v>0.3766</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6838</v>
+        <v>0.3766</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6838</v>
+        <v>0.3766</v>
       </c>
       <c r="N35" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.755</v>
+        <v>0.7027</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4896</v>
+        <v>0.4557</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2766</v>
+        <v>-0.2857</v>
       </c>
       <c r="E36" t="n">
-        <v>0.755</v>
+        <v>0.7027</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0632</v>
+        <v>-0.9791</v>
       </c>
       <c r="G36" t="n">
-        <v>1.8117</v>
+        <v>1.6753</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0632</v>
+        <v>-0.9791</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0632</v>
+        <v>-0.9791</v>
       </c>
       <c r="J36" t="n">
-        <v>1.8117</v>
+        <v>1.6753</v>
       </c>
       <c r="K36" t="n">
         <v>59</v>
@@ -2093,7 +2093,7 @@
         <v>66</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7485000000000002</v>
+        <v>0.6962</v>
       </c>
       <c r="N36" t="n">
         <v>125</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7514</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4873</v>
+        <v>0.4403</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2782</v>
+        <v>-0.2965</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7514</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4169</v>
+        <v>0.6055</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4169</v>
+        <v>0.6055</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4169</v>
+        <v>0.6055</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4169</v>
+        <v>0.6055</v>
       </c>
       <c r="N37" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7047</v>
+        <v>0.6423</v>
       </c>
       <c r="C38" t="n">
-        <v>0.457</v>
+        <v>0.4165</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.299</v>
+        <v>-0.3132</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7047</v>
+        <v>0.6423</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8158</v>
+        <v>0.7534</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8158</v>
+        <v>0.7534</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8158</v>
+        <v>0.7534</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8158</v>
+        <v>0.7534</v>
       </c>
       <c r="N38" t="n">
         <v>55</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6878</v>
+        <v>0.5997</v>
       </c>
       <c r="C39" t="n">
-        <v>0.446</v>
+        <v>0.3889</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3066</v>
+        <v>-0.3326</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6878</v>
+        <v>0.5997</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5642</v>
+        <v>0.4761</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5642</v>
+        <v>0.4761</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5642</v>
+        <v>0.4761</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5642</v>
+        <v>0.4761</v>
       </c>
       <c r="N39" t="n">
         <v>36</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6765</v>
+        <v>0.597</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4387</v>
+        <v>0.3872</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3116</v>
+        <v>-0.3338</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6765</v>
+        <v>0.597</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6296</v>
+        <v>0.5501</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6296</v>
+        <v>0.5501</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6296</v>
+        <v>0.5501</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6296</v>
+        <v>0.5501</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5513</v>
+        <v>0.4618</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3575</v>
+        <v>0.2995</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3676</v>
+        <v>-0.3954</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5513</v>
+        <v>0.4618</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4743</v>
+        <v>0.3848</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4743</v>
+        <v>0.3848</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4743</v>
+        <v>0.3848</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4743</v>
+        <v>0.3848</v>
       </c>
       <c r="N41" t="n">
         <v>64</v>
@@ -2332,185 +2332,185 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4542</v>
+        <v>0.3806</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2945</v>
+        <v>0.2468</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4109</v>
+        <v>-0.4324</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4542</v>
+        <v>0.3806</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.5828</v>
+        <v>0.238</v>
       </c>
       <c r="G42" t="n">
-        <v>1.0664</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.5828</v>
+        <v>0.238</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5828</v>
+        <v>0.238</v>
       </c>
       <c r="J42" t="n">
-        <v>1.0664</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="L42" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4836</v>
+        <v>0.238</v>
       </c>
       <c r="N42" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4319</v>
+        <v>0.326</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2801</v>
+        <v>0.2114</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4209</v>
+        <v>-0.4573</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4319</v>
+        <v>0.326</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2893</v>
+        <v>-0.5608</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.9162</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2893</v>
+        <v>-0.5608</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2893</v>
+        <v>-0.5608</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.9162</v>
       </c>
       <c r="K43" t="n">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2893</v>
+        <v>0.3554</v>
       </c>
       <c r="N43" t="n">
-        <v>42</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3518</v>
+        <v>0.2359</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2281</v>
+        <v>0.153</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4567</v>
+        <v>-0.4983</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3518</v>
+        <v>0.2359</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5193</v>
+        <v>0.1279</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5193</v>
+        <v>0.1279</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5193</v>
+        <v>0.1279</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5193</v>
+        <v>0.1279</v>
       </c>
       <c r="N44" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2815</v>
+        <v>0.2315</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1826</v>
+        <v>0.1501</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4881</v>
+        <v>-0.5003</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2815</v>
+        <v>0.2315</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1735</v>
+        <v>0.399</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1735</v>
+        <v>0.399</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1735</v>
+        <v>0.399</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1735</v>
+        <v>0.399</v>
       </c>
       <c r="N45" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46">
@@ -2520,31 +2520,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1136</v>
+        <v>0.1418</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0737</v>
+        <v>0.092</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5631</v>
+        <v>-0.5412</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1136</v>
+        <v>0.1418</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5632</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7148</v>
+        <v>0.7644</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5632</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5632</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7148</v>
+        <v>0.7644</v>
       </c>
       <c r="K46" t="n">
         <v>113</v>
@@ -2553,7 +2553,7 @@
         <v>101</v>
       </c>
       <c r="M46" t="n">
-        <v>0.173</v>
+        <v>0.2011999999999999</v>
       </c>
       <c r="N46" t="n">
         <v>214</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.101</v>
+        <v>0.0584</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0655</v>
+        <v>0.0379</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5687</v>
+        <v>-0.5792</v>
       </c>
       <c r="E47" t="n">
-        <v>0.101</v>
+        <v>0.0584</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1322</v>
+        <v>0.0896</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1322</v>
+        <v>0.0896</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1322</v>
+        <v>0.0896</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1322</v>
+        <v>0.0896</v>
       </c>
       <c r="N47" t="n">
         <v>59</v>
@@ -2608,231 +2608,231 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0115</v>
+        <v>-0.0554</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0075</v>
+        <v>-0.0359</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.619</v>
+        <v>-0.631</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0115</v>
+        <v>-0.0554</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0675</v>
+        <v>0.0669</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0675</v>
+        <v>0.0669</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0675</v>
+        <v>0.0669</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0675</v>
+        <v>0.0669</v>
       </c>
       <c r="N48" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0377</v>
+        <v>-0.0567</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0244</v>
+        <v>-0.0368</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6307</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0377</v>
+        <v>-0.0567</v>
       </c>
       <c r="F49" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0275</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0275</v>
       </c>
       <c r="I49" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0275</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0275</v>
       </c>
       <c r="N49" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0394</v>
+        <v>-0.0644</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0256</v>
+        <v>-0.0418</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6314</v>
+        <v>-0.6351</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0394</v>
+        <v>-0.0644</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0102</v>
+        <v>-0.1204</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0102</v>
+        <v>-0.1204</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0102</v>
+        <v>-0.1204</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0102</v>
+        <v>-0.1204</v>
       </c>
       <c r="N50" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0522</v>
+        <v>-0.0896</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0339</v>
+        <v>-0.0581</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6371</v>
+        <v>-0.6466</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0522</v>
+        <v>-0.0896</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0412</v>
+        <v>-0.4309</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0412</v>
+        <v>-0.4309</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0412</v>
+        <v>-0.4309</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="K51" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0412</v>
+        <v>-0.1873</v>
       </c>
       <c r="N51" t="n">
-        <v>42</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0622</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0403</v>
+        <v>-0.0589</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.6472</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0622</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.442</v>
+        <v>0.0026</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.442</v>
+        <v>0.0026</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.442</v>
+        <v>0.0026</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="L52" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1599</v>
+        <v>0.0026</v>
       </c>
       <c r="N52" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
@@ -2842,31 +2842,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0828</v>
+        <v>-0.1423</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0537</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6508</v>
+        <v>-0.6706</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0828</v>
+        <v>-0.1423</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3428</v>
+        <v>0.3361</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.3997</v>
+        <v>-0.4525</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3428</v>
+        <v>0.3361</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3428</v>
+        <v>0.3361</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.3997</v>
+        <v>-0.4525</v>
       </c>
       <c r="K53" t="n">
         <v>64</v>
@@ -2875,7 +2875,7 @@
         <v>38</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.1164</v>
       </c>
       <c r="N53" t="n">
         <v>102</v>
@@ -2884,93 +2884,93 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1221</v>
+        <v>-0.165</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.107</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6684</v>
+        <v>-0.681</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1221</v>
+        <v>-0.165</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4995</v>
+        <v>-0.1576</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3814</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.4995</v>
+        <v>-0.1576</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4995</v>
+        <v>-0.1576</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3814</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="L54" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1181</v>
+        <v>-0.1576</v>
       </c>
       <c r="N54" t="n">
-        <v>134</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.167</v>
+        <v>-0.1895</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1083</v>
+        <v>-0.1229</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6884</v>
+        <v>-0.6921</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.167</v>
+        <v>-0.1895</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1596</v>
+        <v>-0.55</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.3645</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1596</v>
+        <v>-0.55</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1596</v>
+        <v>-0.55</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>0.3645</v>
       </c>
       <c r="K55" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1596</v>
+        <v>-0.1855000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.177</v>
+        <v>-0.2146</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1148</v>
+        <v>-0.1392</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6929</v>
+        <v>-0.7035</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.177</v>
+        <v>-0.2146</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1043</v>
+        <v>-0.1419</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1043</v>
+        <v>-0.1419</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1043</v>
+        <v>-0.1419</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.1043</v>
+        <v>-0.1419</v>
       </c>
       <c r="N56" t="n">
         <v>59</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.263</v>
+        <v>-0.2266</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1706</v>
+        <v>-0.147</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7313</v>
+        <v>-0.709</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.263</v>
+        <v>-0.2266</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2403</v>
+        <v>-0.2039</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2403</v>
+        <v>-0.2039</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2403</v>
+        <v>-0.2039</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2403</v>
+        <v>-0.2039</v>
       </c>
       <c r="N57" t="n">
         <v>59</v>
@@ -3068,93 +3068,93 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2978</v>
+        <v>-0.2846</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1931</v>
+        <v>-0.1846</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7468</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2978</v>
+        <v>-0.2846</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1186</v>
+        <v>-0.3095</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1186</v>
+        <v>-0.3095</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1186</v>
+        <v>-0.3095</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1186</v>
+        <v>-0.3095</v>
       </c>
       <c r="N58" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3347</v>
+        <v>-0.2991</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2171</v>
+        <v>-0.194</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7633</v>
+        <v>-0.742</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3347</v>
+        <v>-0.2991</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3596</v>
+        <v>-0.1199</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3596</v>
+        <v>-0.1199</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3596</v>
+        <v>-0.1199</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.3596</v>
+        <v>-0.1199</v>
       </c>
       <c r="N59" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.378</v>
+        <v>-0.3734</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2451</v>
+        <v>-0.2422</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7827</v>
+        <v>-0.7759</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.378</v>
+        <v>-0.3734</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3337</v>
+        <v>-0.3291</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3337</v>
+        <v>-0.3291</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3337</v>
+        <v>-0.3291</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3337</v>
+        <v>-0.3291</v>
       </c>
       <c r="N60" t="n">
         <v>69</v>
@@ -3206,47 +3206,47 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3862</v>
+        <v>-0.4056</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2505</v>
+        <v>-0.263</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7863</v>
+        <v>-0.7906</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3862</v>
+        <v>-0.4056</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2201</v>
+        <v>0.6871</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2201</v>
+        <v>0.6871</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2201</v>
+        <v>0.6871</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K61" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2201</v>
+        <v>-0.3129</v>
       </c>
       <c r="N61" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62">
@@ -3256,31 +3256,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4123</v>
+        <v>-0.448</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2674</v>
+        <v>-0.2905</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.798</v>
+        <v>-0.8099</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4123</v>
+        <v>-0.448</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4479</v>
+        <v>0.3679</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.6853</v>
+        <v>-0.641</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4479</v>
+        <v>0.3679</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4479</v>
+        <v>0.3679</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.6853</v>
+        <v>-0.641</v>
       </c>
       <c r="K62" t="n">
         <v>69</v>
@@ -3289,7 +3289,7 @@
         <v>65</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2374</v>
+        <v>-0.2731</v>
       </c>
       <c r="N62" t="n">
         <v>134</v>
@@ -3298,93 +3298,93 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4251</v>
+        <v>-0.4534</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2757</v>
+        <v>-0.294</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8037</v>
+        <v>-0.8123</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4251</v>
+        <v>-0.4534</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6271</v>
+        <v>-0.2873</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.8902</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6271</v>
+        <v>-0.2873</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6271</v>
+        <v>-0.2873</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.8902</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="L63" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2631</v>
+        <v>-0.2873</v>
       </c>
       <c r="N63" t="n">
-        <v>211</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4587</v>
+        <v>-0.5134</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2975</v>
+        <v>-0.3329</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8187</v>
+        <v>-0.8397</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4587</v>
+        <v>-0.5134</v>
       </c>
       <c r="F64" t="n">
-        <v>0.634</v>
+        <v>0.5826</v>
       </c>
       <c r="G64" t="n">
-        <v>-1</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>0.634</v>
+        <v>0.5826</v>
       </c>
       <c r="I64" t="n">
-        <v>0.634</v>
+        <v>0.5826</v>
       </c>
       <c r="J64" t="n">
-        <v>-1</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="L64" t="n">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.366</v>
+        <v>-0.3514</v>
       </c>
       <c r="N64" t="n">
-        <v>134</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.4737</v>
+        <v>-0.5286</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3072</v>
+        <v>-0.3428</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8254</v>
+        <v>-0.8466</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.4737</v>
+        <v>-0.5286</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1146</v>
+        <v>-0.1695</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1146</v>
+        <v>-0.1695</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1146</v>
+        <v>-0.1695</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.1146</v>
+        <v>-0.1695</v>
       </c>
       <c r="N65" t="n">
         <v>69</v>
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6194</v>
+        <v>-0.641</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4017</v>
+        <v>-0.4157</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8905</v>
+        <v>-0.8978</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6194</v>
+        <v>-0.641</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4347</v>
+        <v>-0.4563</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4347</v>
+        <v>-0.4563</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4347</v>
+        <v>-0.4563</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4347</v>
+        <v>-0.4563</v>
       </c>
       <c r="N66" t="n">
         <v>59</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.6449</v>
+        <v>-0.6524</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4182</v>
+        <v>-0.4231</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9019</v>
+        <v>-0.903</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.6449</v>
+        <v>-0.6524</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2882</v>
+        <v>-0.2957</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.2882</v>
+        <v>-0.2957</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2882</v>
+        <v>-0.2957</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.2882</v>
+        <v>-0.2957</v>
       </c>
       <c r="N67" t="n">
         <v>64</v>
@@ -3528,323 +3528,323 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Alkaren</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7562</v>
+        <v>-0.8094</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4904</v>
+        <v>-0.5249</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9516</v>
+        <v>-0.9745</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7562</v>
+        <v>-0.8094</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3302</v>
+        <v>-0.5907</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.83</v>
+        <v>-0.0699</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3302</v>
+        <v>-0.5907</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3302</v>
+        <v>-0.5907</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.83</v>
+        <v>-0.0699</v>
       </c>
       <c r="K68" t="n">
         <v>64</v>
       </c>
       <c r="L68" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4998</v>
+        <v>-0.6606</v>
       </c>
       <c r="N68" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alkaren</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7709</v>
+        <v>-0.8208</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4999</v>
+        <v>-0.5323</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-0.9797</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7709</v>
+        <v>-0.8208</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5681</v>
+        <v>-0.1824</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.054</v>
+        <v>-0.4856</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5681</v>
+        <v>-0.1824</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5681</v>
+        <v>-0.1824</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.054</v>
+        <v>-0.4856</v>
       </c>
       <c r="K69" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L69" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6221000000000001</v>
+        <v>-0.6679999999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8186</v>
+        <v>-0.8348</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5309</v>
+        <v>-0.5414</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9795</v>
+        <v>-0.9861</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8186</v>
+        <v>-0.8348</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.2033</v>
+        <v>0.2482</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.4625</v>
+        <v>-0.8266</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.2033</v>
+        <v>0.2482</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2033</v>
+        <v>0.2482</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.4625</v>
+        <v>-0.8266</v>
       </c>
       <c r="K70" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L70" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6658000000000001</v>
+        <v>-0.5784</v>
       </c>
       <c r="N70" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8894</v>
+        <v>-0.8528</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5768</v>
+        <v>-0.553</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0111</v>
+        <v>-0.9943</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8894</v>
+        <v>-0.8528</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6673</v>
+        <v>-0.7401</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-0.1114</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6673</v>
+        <v>-0.7401</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6673</v>
+        <v>-0.7401</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>-0.1114</v>
       </c>
       <c r="K71" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6673</v>
+        <v>-0.8514999999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>55</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9092</v>
+        <v>-0.854</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5896</v>
+        <v>-0.5538</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0199</v>
+        <v>-0.9948</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9092</v>
+        <v>-0.854</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.8045</v>
+        <v>-0.0139</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.1034</v>
+        <v>-0.7089</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.8045</v>
+        <v>-0.0139</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.8045</v>
+        <v>-0.0139</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.1034</v>
+        <v>-0.7089</v>
       </c>
       <c r="K72" t="n">
         <v>64</v>
       </c>
       <c r="L72" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9079</v>
+        <v>-0.7228</v>
       </c>
       <c r="N72" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9166</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5944</v>
+        <v>-0.5606</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0232</v>
+        <v>-0.9996</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9166</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6558</v>
+        <v>-0.6423</v>
       </c>
       <c r="G73" t="n">
-        <v>-1.3912</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6558</v>
+        <v>-0.6423</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6558</v>
+        <v>-0.6423</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.3912</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="L73" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7353999999999999</v>
+        <v>-0.6423</v>
       </c>
       <c r="N73" t="n">
-        <v>205</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9172</v>
+        <v>-0.8646</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5948</v>
+        <v>-0.5607</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0235</v>
+        <v>-0.9997</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.9172</v>
+        <v>-0.8646</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.051</v>
+        <v>0.6684</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.735</v>
+        <v>-1.3517</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.051</v>
+        <v>0.6684</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.051</v>
+        <v>0.6684</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.735</v>
+        <v>-1.3517</v>
       </c>
       <c r="K74" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="L74" t="n">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.786</v>
+        <v>-0.6832999999999999</v>
       </c>
       <c r="N74" t="n">
-        <v>108</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9935</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6443</v>
+        <v>-0.6214</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0576</v>
+        <v>-1.0423</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9935</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.5975</v>
+        <v>-0.5622</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.5975</v>
+        <v>-0.5622</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5975</v>
+        <v>-0.5622</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.5975</v>
+        <v>-0.5622</v>
       </c>
       <c r="N75" t="n">
         <v>36</v>
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.05</v>
+        <v>-1.0395</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0828</v>
+        <v>-1.0793</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.05</v>
+        <v>-1.0395</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.8656</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.0298</v>
+        <v>-0.0332</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.8656</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.8656</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.0298</v>
+        <v>-0.0332</v>
       </c>
       <c r="K76" t="n">
         <v>59</v>
@@ -3933,7 +3933,7 @@
         <v>66</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.9093</v>
+        <v>-0.8988</v>
       </c>
       <c r="N76" t="n">
         <v>125</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.1529</v>
+        <v>-1.1295</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7477</v>
+        <v>-0.7325</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1288</v>
+        <v>-1.1203</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.1529</v>
+        <v>-1.1295</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7301</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7301</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7301</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7301</v>
       </c>
       <c r="N77" t="n">
         <v>59</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.1723</v>
+        <v>-1.1479</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7602</v>
+        <v>-0.7444</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1375</v>
+        <v>-1.1287</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.1723</v>
+        <v>-1.1479</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.773</v>
+        <v>-0.7486</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.773</v>
+        <v>-0.7486</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.773</v>
+        <v>-0.7486</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.773</v>
+        <v>-0.7486</v>
       </c>
       <c r="N78" t="n">
         <v>36</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.2117</v>
+        <v>-1.1997</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.778</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1551</v>
+        <v>-1.1523</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.2117</v>
+        <v>-1.1997</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.8456</v>
+        <v>-0.8336</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.8456</v>
+        <v>-0.8336</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.8456</v>
+        <v>-0.8336</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.8456</v>
+        <v>-0.8336</v>
       </c>
       <c r="N79" t="n">
         <v>64</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.4171</v>
+        <v>-1.451</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.919</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2468</v>
+        <v>-1.2668</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.4171</v>
+        <v>-1.451</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.7871</v>
+        <v>-0.7855</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.3855</v>
+        <v>-0.421</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.7871</v>
+        <v>-0.7855</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7871</v>
+        <v>-0.7855</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.3855</v>
+        <v>-0.421</v>
       </c>
       <c r="K80" t="n">
         <v>55</v>
@@ -4117,7 +4117,7 @@
         <v>156</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.1726</v>
+        <v>-1.2065</v>
       </c>
       <c r="N80" t="n">
         <v>211</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1898</v>
+        <v>-2.2054</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.4201</v>
+        <v>-1.4302</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.592</v>
+        <v>-1.6105</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1898</v>
+        <v>-2.2054</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.6894</v>
+        <v>-1.6602</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.2354</v>
+        <v>-0.2802</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.6894</v>
+        <v>-1.6602</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.6894</v>
+        <v>-1.6602</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.2354</v>
+        <v>-0.2802</v>
       </c>
       <c r="K81" t="n">
         <v>113</v>
@@ -4163,7 +4163,7 @@
         <v>101</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.9248</v>
+        <v>-1.9404</v>
       </c>
       <c r="N81" t="n">
         <v>214</v>
@@ -4269,10 +4269,10 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6627</v>
+        <v>1.7013</v>
       </c>
       <c r="J2" t="n">
-        <v>49.881</v>
+        <v>51.039</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1495</v>
+        <v>0.1247</v>
       </c>
       <c r="J3" t="n">
-        <v>4.485</v>
+        <v>3.741</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0796</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.388</v>
+        <v>1.881</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1226</v>
+        <v>-0.0955</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.678</v>
+        <v>-2.865</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5669</v>
+        <v>-0.5284</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.007</v>
+        <v>-15.852</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8054</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>24.162</v>
+        <v>22.605</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.701</v>
+        <v>0.6442</v>
       </c>
       <c r="J8" t="n">
-        <v>21.03</v>
+        <v>19.326</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2099</v>
+        <v>0.1681</v>
       </c>
       <c r="J9" t="n">
-        <v>6.297</v>
+        <v>5.043</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.65</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3944</v>
+        <v>-0.3838</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.832</v>
+        <v>-11.514</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4902</v>
+        <v>-0.4908</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.706</v>
+        <v>-14.724</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2543</v>
+        <v>1.2784</v>
       </c>
       <c r="J12" t="n">
-        <v>27.5946</v>
+        <v>28.1248</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5981</v>
+        <v>0.5617</v>
       </c>
       <c r="J13" t="n">
-        <v>13.1582</v>
+        <v>12.3574</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3204</v>
+        <v>0.2852</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0488</v>
+        <v>6.2744</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3682</v>
+        <v>-0.326</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.1004</v>
+        <v>-7.172</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3682</v>
+        <v>-0.326</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.1004</v>
+        <v>-7.172</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.39</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7528</v>
+        <v>0.7015</v>
       </c>
       <c r="J17" t="n">
-        <v>16.5616</v>
+        <v>15.433</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0224</v>
+        <v>-0.0166</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4928</v>
+        <v>-0.3652</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1198</v>
+        <v>-0.1023</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6356</v>
+        <v>-2.2506</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1651</v>
+        <v>-0.1454</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.6322</v>
+        <v>-3.1988</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.58</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4506</v>
+        <v>-0.4454</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.9132</v>
+        <v>-9.7988</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>2.71</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J22" t="n">
-        <v>31.3701</v>
+        <v>33.6974</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5105</v>
+        <v>0.4819</v>
       </c>
       <c r="J23" t="n">
-        <v>8.6785</v>
+        <v>8.192299999999999</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.18</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4655</v>
+        <v>0.4354</v>
       </c>
       <c r="J24" t="n">
-        <v>7.9135</v>
+        <v>7.4018</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2446</v>
+        <v>0.2121</v>
       </c>
       <c r="J25" t="n">
-        <v>4.1582</v>
+        <v>3.6057</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1602</v>
+        <v>0.1301</v>
       </c>
       <c r="J26" t="n">
-        <v>2.7234</v>
+        <v>2.2117</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.45</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9011</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>15.3187</v>
+        <v>14.8835</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2366</v>
+        <v>-0.2181</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.0222</v>
+        <v>-3.7077</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.79</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2462</v>
+        <v>-0.2278</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.1854</v>
+        <v>-3.8726</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4214</v>
+        <v>-0.4119</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.1638</v>
+        <v>-7.0023</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4915</v>
+        <v>-0.4899</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.355499999999999</v>
+        <v>-8.3283</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.83</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9413</v>
+        <v>0.8774</v>
       </c>
       <c r="J32" t="n">
-        <v>20.7086</v>
+        <v>19.3028</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3778</v>
+        <v>0.3182</v>
       </c>
       <c r="J33" t="n">
-        <v>8.3116</v>
+        <v>7.0004</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.25</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3553</v>
+        <v>0.2977</v>
       </c>
       <c r="J34" t="n">
-        <v>7.8166</v>
+        <v>6.5494</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0552</v>
+        <v>0.0387</v>
       </c>
       <c r="J35" t="n">
-        <v>1.2144</v>
+        <v>0.8514</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.72</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3461</v>
+        <v>-0.3336</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.6142</v>
+        <v>-7.3392</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.75</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9825</v>
+        <v>1.0871</v>
       </c>
       <c r="J37" t="n">
-        <v>21.615</v>
+        <v>23.9162</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>0.97</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0567</v>
+        <v>-0.0449</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.2474</v>
+        <v>-0.9878</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.92</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1217</v>
+        <v>-0.1036</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.6774</v>
+        <v>-2.2792</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3729</v>
+        <v>-0.36</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.203799999999999</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4613</v>
+        <v>-0.4576</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.1486</v>
+        <v>-10.0672</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>0.87</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0577</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.4464</v>
+        <v>-0.9232</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>0.71</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2736</v>
+        <v>-0.2595</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.3776</v>
+        <v>-4.152</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.43</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5302</v>
+        <v>-0.5321</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.4832</v>
+        <v>-8.5136</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.34</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6108</v>
+        <v>-0.623</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.7728</v>
+        <v>-9.968</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.29</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6559</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.4944</v>
+        <v>-10.8144</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>2.59</v>
       </c>
       <c r="I47" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J47" t="n">
-        <v>30.9952</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.75</v>
       </c>
       <c r="I48" t="n">
-        <v>1.352</v>
+        <v>1.3803</v>
       </c>
       <c r="J48" t="n">
-        <v>21.632</v>
+        <v>22.0848</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.56</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1254</v>
+        <v>1.1489</v>
       </c>
       <c r="J49" t="n">
-        <v>18.0064</v>
+        <v>18.3824</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.43</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9378</v>
+        <v>0.9423</v>
       </c>
       <c r="J50" t="n">
-        <v>15.0048</v>
+        <v>15.0768</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>1.07</v>
       </c>
       <c r="I51" t="n">
-        <v>0.159</v>
+        <v>0.1219</v>
       </c>
       <c r="J51" t="n">
-        <v>2.544</v>
+        <v>1.9504</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>0.97</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0352</v>
+        <v>-0.0257</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.5632</v>
+        <v>-0.4112</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0645</v>
+        <v>-0.0525</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.032</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1939</v>
+        <v>-0.1774</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.1024</v>
+        <v>-2.8384</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2895</v>
+        <v>-0.2724</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.632</v>
+        <v>-4.3584</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.45</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5476</v>
+        <v>-0.5533</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.7616</v>
+        <v>-8.8528</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>2.08</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7836</v>
+        <v>1.8417</v>
       </c>
       <c r="J57" t="n">
-        <v>28.5376</v>
+        <v>29.4672</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.46</v>
       </c>
       <c r="I58" t="n">
-        <v>1.0146</v>
+        <v>1.0202</v>
       </c>
       <c r="J58" t="n">
-        <v>16.2336</v>
+        <v>16.3232</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.28</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6868</v>
+        <v>0.6657</v>
       </c>
       <c r="J59" t="n">
-        <v>10.9888</v>
+        <v>10.6512</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3039</v>
+        <v>0.2716</v>
       </c>
       <c r="J60" t="n">
-        <v>4.8624</v>
+        <v>4.3456</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2241</v>
+        <v>0.193</v>
       </c>
       <c r="J61" t="n">
-        <v>3.5856</v>
+        <v>3.088</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.58</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0399</v>
+        <v>1.0291</v>
       </c>
       <c r="J62" t="n">
-        <v>19.7581</v>
+        <v>19.5529</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.57</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0268</v>
+        <v>1.0156</v>
       </c>
       <c r="J63" t="n">
-        <v>19.5092</v>
+        <v>19.2964</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.21</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5216</v>
+        <v>0.5169</v>
       </c>
       <c r="J64" t="n">
-        <v>9.910399999999999</v>
+        <v>9.821099999999999</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1.14</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3906</v>
+        <v>0.3587</v>
       </c>
       <c r="J65" t="n">
-        <v>7.4214</v>
+        <v>6.8153</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3414</v>
+        <v>0.3094</v>
       </c>
       <c r="J66" t="n">
-        <v>6.4866</v>
+        <v>5.8786</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0241</v>
+        <v>0.0185</v>
       </c>
       <c r="J67" t="n">
-        <v>0.4579</v>
+        <v>0.3515</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1476</v>
+        <v>-0.1308</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.8044</v>
+        <v>-2.4852</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1585</v>
+        <v>-0.1412</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.0115</v>
+        <v>-2.6828</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2194</v>
+        <v>-0.2004</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.1686</v>
+        <v>-3.8076</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.71</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3248</v>
+        <v>-0.3081</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.1712</v>
+        <v>-5.8539</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>1.042</v>
+        <v>1.0338</v>
       </c>
       <c r="J72" t="n">
-        <v>25.008</v>
+        <v>24.8112</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6445</v>
+        <v>0.6302</v>
       </c>
       <c r="J73" t="n">
-        <v>15.468</v>
+        <v>15.1248</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1238</v>
+        <v>0.1008</v>
       </c>
       <c r="J74" t="n">
-        <v>2.9712</v>
+        <v>2.4192</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6048</v>
+        <v>-0.5673</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.5152</v>
+        <v>-13.6152</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.79</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6278</v>
+        <v>-0.5915</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.0672</v>
+        <v>-14.196</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7607</v>
+        <v>0.7259</v>
       </c>
       <c r="J77" t="n">
-        <v>18.2568</v>
+        <v>17.4216</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I78" t="n">
-        <v>0.267</v>
+        <v>0.2196</v>
       </c>
       <c r="J78" t="n">
-        <v>6.408</v>
+        <v>5.2704</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1493</v>
+        <v>-0.1295</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.5832</v>
+        <v>-3.108</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1718</v>
+        <v>-0.1513</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.1232</v>
+        <v>-3.6312</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2939</v>
+        <v>-0.2758</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.0536</v>
+        <v>-6.6192</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.56</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0247</v>
+        <v>1.013</v>
       </c>
       <c r="J82" t="n">
-        <v>21.5187</v>
+        <v>21.273</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.44</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8622</v>
+        <v>0.8476</v>
       </c>
       <c r="J83" t="n">
-        <v>18.1062</v>
+        <v>17.7996</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.59</v>
+        <v>0.583</v>
       </c>
       <c r="J84" t="n">
-        <v>12.39</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1269</v>
+        <v>0.1033</v>
       </c>
       <c r="J85" t="n">
-        <v>2.6649</v>
+        <v>2.1693</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>1.03</v>
       </c>
       <c r="I86" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="J86" t="n">
-        <v>1.9572</v>
+        <v>1.5267</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.36</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6292</v>
+        <v>0.6004</v>
       </c>
       <c r="J87" t="n">
-        <v>13.2132</v>
+        <v>12.6084</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5948</v>
+        <v>0.5679</v>
       </c>
       <c r="J88" t="n">
-        <v>12.4908</v>
+        <v>11.9259</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1101</v>
+        <v>-0.0927</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.3121</v>
+        <v>-1.9467</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1999</v>
+        <v>-0.1793</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.1979</v>
+        <v>-3.7653</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.44</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5718</v>
+        <v>-0.5841</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.0078</v>
+        <v>-12.2661</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.44</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5808</v>
+        <v>0.6152</v>
       </c>
       <c r="J92" t="n">
-        <v>12.7776</v>
+        <v>13.5344</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4667</v>
+        <v>0.4825</v>
       </c>
       <c r="J93" t="n">
-        <v>10.2674</v>
+        <v>10.615</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0438</v>
+        <v>-0.0331</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.9636</v>
+        <v>-0.7282</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1596</v>
+        <v>-0.1395</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.5112</v>
+        <v>-3.069</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.46</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5575</v>
+        <v>-0.5679</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.265</v>
+        <v>-12.4938</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.44</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5339</v>
+        <v>0.4953</v>
       </c>
       <c r="J97" t="n">
-        <v>11.7458</v>
+        <v>10.8966</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.29</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4047</v>
+        <v>0.3422</v>
       </c>
       <c r="J98" t="n">
-        <v>8.9034</v>
+        <v>7.5284</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>1.28</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3937</v>
+        <v>0.3318</v>
       </c>
       <c r="J99" t="n">
-        <v>8.6614</v>
+        <v>7.2996</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0573</v>
       </c>
       <c r="J100" t="n">
-        <v>1.7226</v>
+        <v>1.2606</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2567</v>
+        <v>-0.2382</v>
       </c>
       <c r="J101" t="n">
-        <v>-5.6474</v>
+        <v>-5.2404</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>2.29</v>
       </c>
       <c r="I102" t="n">
-        <v>1.9448</v>
+        <v>2.0343</v>
       </c>
       <c r="J102" t="n">
-        <v>38.896</v>
+        <v>40.686</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.2</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5161</v>
+        <v>0.507</v>
       </c>
       <c r="J103" t="n">
-        <v>10.322</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2713</v>
+        <v>-0.2334</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.426</v>
+        <v>-4.668</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4358</v>
+        <v>-0.3955</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.715999999999999</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.79</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6515</v>
+        <v>-0.6198</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.03</v>
+        <v>-12.396</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.53</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8183</v>
+        <v>0.7855</v>
       </c>
       <c r="J107" t="n">
-        <v>16.366</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.2</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4371</v>
+        <v>0.3826</v>
       </c>
       <c r="J108" t="n">
-        <v>8.742000000000001</v>
+        <v>7.652</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.85</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1991</v>
+        <v>-0.1786</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.982</v>
+        <v>-3.572</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3545</v>
+        <v>-0.34</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.09</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.435</v>
+        <v>-0.4282</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.564</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9404</v>
       </c>
       <c r="J112" t="n">
-        <v>20.9902</v>
+        <v>20.6888</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.24</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5858</v>
+        <v>0.5752</v>
       </c>
       <c r="J113" t="n">
-        <v>12.8876</v>
+        <v>12.6544</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.22</v>
       </c>
       <c r="I114" t="n">
-        <v>0.554</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>12.188</v>
+        <v>11.9878</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1777</v>
+        <v>0.1507</v>
       </c>
       <c r="J115" t="n">
-        <v>3.9094</v>
+        <v>3.3154</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.76</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7073</v>
+        <v>-0.6778</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.5606</v>
+        <v>-14.9116</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6187</v>
+        <v>0.5906</v>
       </c>
       <c r="J117" t="n">
-        <v>13.6114</v>
+        <v>12.9932</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2163</v>
+        <v>0.1732</v>
       </c>
       <c r="J118" t="n">
-        <v>4.7586</v>
+        <v>3.8104</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.95</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0693</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.859</v>
+        <v>-1.5246</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1782</v>
+        <v>-0.1579</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.9204</v>
+        <v>-3.4738</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.64</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4</v>
+        <v>-0.3896</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.571199999999999</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3164</v>
+        <v>0.3089</v>
       </c>
       <c r="J122" t="n">
-        <v>6.6444</v>
+        <v>6.4869</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1006</v>
+        <v>-0.0864</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.1126</v>
+        <v>-1.8144</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1793</v>
+        <v>-0.1612</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.7653</v>
+        <v>-3.3852</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.79</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2487</v>
+        <v>-0.2297</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.2227</v>
+        <v>-4.8237</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4681</v>
+        <v>-0.4638</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.8301</v>
+        <v>-9.739800000000001</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.69</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7104</v>
+        <v>0.6645</v>
       </c>
       <c r="J127" t="n">
-        <v>14.9184</v>
+        <v>13.9545</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4962</v>
+        <v>0.4483</v>
       </c>
       <c r="J128" t="n">
-        <v>10.4202</v>
+        <v>9.414300000000001</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.25</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3541</v>
+        <v>0.2971</v>
       </c>
       <c r="J129" t="n">
-        <v>7.4361</v>
+        <v>6.2391</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.11</v>
       </c>
       <c r="I130" t="n">
-        <v>0.181</v>
+        <v>0.1435</v>
       </c>
       <c r="J130" t="n">
-        <v>3.801</v>
+        <v>3.0135</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3288</v>
+        <v>-0.3152</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.9048</v>
+        <v>-6.6192</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0336</v>
+        <v>1.024</v>
       </c>
       <c r="J132" t="n">
-        <v>23.7728</v>
+        <v>23.552</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.39</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8203</v>
+        <v>0.8043</v>
       </c>
       <c r="J133" t="n">
-        <v>18.8669</v>
+        <v>18.4989</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0828</v>
+        <v>0.0654</v>
       </c>
       <c r="J134" t="n">
-        <v>1.9044</v>
+        <v>1.5042</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.9</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3644</v>
+        <v>-0.322</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.3812</v>
+        <v>-7.406</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.788</v>
+        <v>-0.7641</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.124</v>
+        <v>-17.5743</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.61</v>
       </c>
       <c r="I137" t="n">
-        <v>0.885</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>20.355</v>
+        <v>19.5339</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2663</v>
+        <v>0.2192</v>
       </c>
       <c r="J138" t="n">
-        <v>6.1249</v>
+        <v>5.0416</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1263</v>
+        <v>-0.1074</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.9049</v>
+        <v>-2.4702</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2749</v>
+        <v>-0.256</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.3227</v>
+        <v>-5.888</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3132</v>
+        <v>-0.2963</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.2036</v>
+        <v>-6.8149</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5278</v>
       </c>
       <c r="J142" t="n">
-        <v>10.856</v>
+        <v>10.556</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2138</v>
+        <v>-0.1971</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.276</v>
+        <v>-3.942</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>0.77</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2612</v>
+        <v>-0.2441</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.224</v>
+        <v>-4.882</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4163</v>
+        <v>-0.4062</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.326000000000001</v>
+        <v>-8.124000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5041</v>
+        <v>-0.5036</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.082</v>
+        <v>-10.072</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.89</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4211</v>
+        <v>1.433</v>
       </c>
       <c r="J147" t="n">
-        <v>28.422</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.38</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7678</v>
+        <v>0.7572</v>
       </c>
       <c r="J148" t="n">
-        <v>15.356</v>
+        <v>15.144</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>1.3</v>
       </c>
       <c r="I149" t="n">
-        <v>0.656</v>
+        <v>0.649</v>
       </c>
       <c r="J149" t="n">
-        <v>13.12</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>1.2</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5014</v>
+        <v>0.4932</v>
       </c>
       <c r="J150" t="n">
-        <v>10.028</v>
+        <v>9.864000000000001</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>1.03</v>
       </c>
       <c r="I151" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0559</v>
       </c>
       <c r="J151" t="n">
-        <v>1.554</v>
+        <v>1.118</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.53</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7862</v>
+        <v>0.7489</v>
       </c>
       <c r="J152" t="n">
-        <v>18.8688</v>
+        <v>17.9736</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.3</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5384</v>
+        <v>0.51</v>
       </c>
       <c r="J153" t="n">
-        <v>12.9216</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1598</v>
+        <v>0.1272</v>
       </c>
       <c r="J154" t="n">
-        <v>3.8352</v>
+        <v>3.0528</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1994</v>
+        <v>-0.1789</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.7856</v>
+        <v>-4.2936</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3187</v>
+        <v>-0.3027</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.6488</v>
+        <v>-7.2648</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7055</v>
+        <v>0.6903</v>
       </c>
       <c r="J157" t="n">
-        <v>16.932</v>
+        <v>16.5672</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3621</v>
+        <v>0.3204</v>
       </c>
       <c r="J158" t="n">
-        <v>8.6904</v>
+        <v>7.6896</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.05</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1957</v>
+        <v>0.1628</v>
       </c>
       <c r="J159" t="n">
-        <v>4.6968</v>
+        <v>3.9072</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.99</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0625</v>
+        <v>-0.0449</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.5</v>
+        <v>-1.0776</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.68</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8568</v>
+        <v>-0.8374</v>
       </c>
       <c r="J161" t="n">
-        <v>-20.5632</v>
+        <v>-20.0976</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I162" t="n">
-        <v>0.167</v>
+        <v>0.14</v>
       </c>
       <c r="J162" t="n">
-        <v>2.839</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0698</v>
+        <v>-0.0563</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.1866</v>
+        <v>-0.9571</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.78</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2488</v>
+        <v>-0.2331</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.2296</v>
+        <v>-3.9627</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4205</v>
+        <v>-0.4107</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.1485</v>
+        <v>-6.9819</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.39</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5945</v>
+        <v>-0.6071</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.1065</v>
+        <v>-10.3207</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>2.73</v>
       </c>
       <c r="I167" t="n">
-        <v>2.3538</v>
+        <v>2.4959</v>
       </c>
       <c r="J167" t="n">
-        <v>40.0146</v>
+        <v>42.4303</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.24</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5574</v>
+        <v>0.5556</v>
       </c>
       <c r="J168" t="n">
-        <v>9.4758</v>
+        <v>9.4452</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4767</v>
+        <v>0.4608</v>
       </c>
       <c r="J169" t="n">
-        <v>8.103899999999999</v>
+        <v>7.8336</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1913</v>
+        <v>0.1604</v>
       </c>
       <c r="J170" t="n">
-        <v>3.2521</v>
+        <v>2.7268</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3046</v>
+        <v>-0.2724</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.1782</v>
+        <v>-4.6308</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.18</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4301</v>
+        <v>0.3777</v>
       </c>
       <c r="J172" t="n">
-        <v>9.0321</v>
+        <v>7.9317</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1948</v>
+        <v>0.1546</v>
       </c>
       <c r="J173" t="n">
-        <v>4.0908</v>
+        <v>3.2466</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.98</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.033</v>
+        <v>-0.0256</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.5376</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.77</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2704</v>
+        <v>-0.2514</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.6784</v>
+        <v>-5.2794</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.42</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5812</v>
+        <v>-0.5935</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.2052</v>
+        <v>-12.4635</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.73</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2503</v>
+        <v>1.2508</v>
       </c>
       <c r="J177" t="n">
-        <v>26.2563</v>
+        <v>26.2668</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8652</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>18.1692</v>
+        <v>17.8563</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2762</v>
+        <v>0.245</v>
       </c>
       <c r="J179" t="n">
-        <v>5.8002</v>
+        <v>5.145</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0415</v>
+        <v>-0.0362</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.97</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1795</v>
+        <v>-0.1487</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.7695</v>
+        <v>-3.1227</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.78</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2958</v>
+        <v>1.2983</v>
       </c>
       <c r="J182" t="n">
-        <v>28.5076</v>
+        <v>28.5626</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.66</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1443</v>
+        <v>1.1376</v>
       </c>
       <c r="J183" t="n">
-        <v>25.1746</v>
+        <v>25.0272</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4362</v>
+        <v>0.4076</v>
       </c>
       <c r="J184" t="n">
-        <v>9.596399999999999</v>
+        <v>8.9672</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3423</v>
+        <v>0.3103</v>
       </c>
       <c r="J185" t="n">
-        <v>7.5306</v>
+        <v>6.8266</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4769</v>
+        <v>-0.4401</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.4918</v>
+        <v>-9.6822</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>0.93</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.9888</v>
+        <v>-1.6918</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>0.93</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.9888</v>
+        <v>-1.6918</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.84</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1935</v>
+        <v>-0.1771</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.257</v>
+        <v>-3.8962</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3352</v>
+        <v>-0.3196</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.3744</v>
+        <v>-7.0312</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4692</v>
+        <v>-0.4645</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.3224</v>
+        <v>-10.219</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.77</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8376</v>
+        <v>0.903</v>
       </c>
       <c r="J192" t="n">
-        <v>18.4272</v>
+        <v>19.866</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.19</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3169</v>
+        <v>0.3064</v>
       </c>
       <c r="J193" t="n">
-        <v>6.9718</v>
+        <v>6.7408</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0036</v>
+        <v>-0.0022</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0484</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1519</v>
+        <v>-0.1319</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.3418</v>
+        <v>-2.9018</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.43</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5848</v>
+        <v>-0.6002</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.8656</v>
+        <v>-13.2044</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.73</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7579</v>
+        <v>0.7118</v>
       </c>
       <c r="J197" t="n">
-        <v>16.6738</v>
+        <v>15.6596</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5636</v>
+        <v>0.5285</v>
       </c>
       <c r="J198" t="n">
-        <v>12.3992</v>
+        <v>11.627</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1477</v>
+        <v>0.1137</v>
       </c>
       <c r="J199" t="n">
-        <v>3.2494</v>
+        <v>2.5014</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3667</v>
+        <v>-0.3547</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.067399999999999</v>
+        <v>-7.8034</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.64</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4114</v>
+        <v>-0.4038</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.050800000000001</v>
+        <v>-8.883599999999999</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.41</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8208</v>
+        <v>0.8063</v>
       </c>
       <c r="J202" t="n">
-        <v>17.2368</v>
+        <v>16.9323</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.37</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7644</v>
+        <v>0.7507</v>
       </c>
       <c r="J203" t="n">
-        <v>16.0524</v>
+        <v>15.7647</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.26</v>
       </c>
       <c r="I204" t="n">
-        <v>0.605</v>
+        <v>0.5971</v>
       </c>
       <c r="J204" t="n">
-        <v>12.705</v>
+        <v>12.5391</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5831</v>
       </c>
       <c r="J205" t="n">
-        <v>12.3942</v>
+        <v>12.2451</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>1.02</v>
       </c>
       <c r="I206" t="n">
-        <v>0.057</v>
+        <v>0.0407</v>
       </c>
       <c r="J206" t="n">
-        <v>1.197</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.25</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5342</v>
+        <v>0.5125</v>
       </c>
       <c r="J207" t="n">
-        <v>11.2182</v>
+        <v>10.7625</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1986</v>
+        <v>-0.1803</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.1706</v>
+        <v>-3.7863</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2282</v>
+        <v>-0.2094</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.7922</v>
+        <v>-4.3974</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2861</v>
+        <v>-0.2679</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.0081</v>
+        <v>-5.6259</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.432</v>
+        <v>-0.4236</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.071999999999999</v>
+        <v>-8.8956</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0767</v>
+        <v>-0.0638</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.4573</v>
+        <v>-1.2122</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0767</v>
+        <v>-0.0638</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.4573</v>
+        <v>-1.2122</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1825</v>
+        <v>-0.1663</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.4675</v>
+        <v>-3.1597</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4159</v>
+        <v>-0.4057</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.9021</v>
+        <v>-7.7083</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.58</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4336</v>
+        <v>-0.425</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.2384</v>
+        <v>-8.074999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.66</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7758</v>
+        <v>0.7043</v>
       </c>
       <c r="J217" t="n">
-        <v>14.7402</v>
+        <v>13.3817</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.65</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7662</v>
+        <v>0.6945</v>
       </c>
       <c r="J218" t="n">
-        <v>14.5578</v>
+        <v>13.1955</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2843</v>
+        <v>0.2345</v>
       </c>
       <c r="J219" t="n">
-        <v>5.4017</v>
+        <v>4.4555</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.98</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0614</v>
+        <v>-0.0493</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.1666</v>
+        <v>-0.9367</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.32</v>
+        <v>-0.3058</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.08</v>
+        <v>-5.8102</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3394</v>
+        <v>1.3618</v>
       </c>
       <c r="J222" t="n">
-        <v>22.7698</v>
+        <v>23.1506</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.32</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7889</v>
+        <v>0.7647</v>
       </c>
       <c r="J223" t="n">
-        <v>13.4113</v>
+        <v>12.9999</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.13</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3824</v>
+        <v>0.3489</v>
       </c>
       <c r="J224" t="n">
-        <v>6.5008</v>
+        <v>5.9313</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>1.02</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0638</v>
+        <v>0.0477</v>
       </c>
       <c r="J225" t="n">
-        <v>1.0846</v>
+        <v>0.8109</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.96</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2092</v>
+        <v>-0.1751</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.5564</v>
+        <v>-2.9767</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.26</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5894</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>10.0198</v>
+        <v>9.176600000000001</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0843</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.6677</v>
+        <v>-1.4331</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2564</v>
+        <v>-0.2379</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.3588</v>
+        <v>-4.0443</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3773</v>
+        <v>-0.364</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.4141</v>
+        <v>-6.188</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.57</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4486</v>
+        <v>-0.4419</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.6262</v>
+        <v>-7.5123</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2474</v>
+        <v>1.2687</v>
       </c>
       <c r="J232" t="n">
-        <v>28.6902</v>
+        <v>29.1801</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.52</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1637</v>
+        <v>1.18</v>
       </c>
       <c r="J233" t="n">
-        <v>26.7651</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.509</v>
+        <v>-0.4675</v>
       </c>
       <c r="J234" t="n">
-        <v>-11.707</v>
+        <v>-10.7525</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.77</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6715</v>
+        <v>-0.6377</v>
       </c>
       <c r="J235" t="n">
-        <v>-15.4445</v>
+        <v>-14.6671</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.68</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8666</v>
+        <v>-0.8495</v>
       </c>
       <c r="J236" t="n">
-        <v>-19.9318</v>
+        <v>-19.5385</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.63</v>
       </c>
       <c r="I237" t="n">
-        <v>1.05</v>
+        <v>1.0297</v>
       </c>
       <c r="J237" t="n">
-        <v>24.15</v>
+        <v>23.6831</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6643</v>
+        <v>0.6058</v>
       </c>
       <c r="J238" t="n">
-        <v>15.2789</v>
+        <v>13.9334</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2153</v>
+        <v>-0.1947</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.9519</v>
+        <v>-4.4781</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.71</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3417</v>
+        <v>-0.3268</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.8591</v>
+        <v>-7.5164</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.66</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3872</v>
+        <v>-0.3762</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.9056</v>
+        <v>-8.6526</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.4</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7383</v>
+        <v>0.6821</v>
       </c>
       <c r="J242" t="n">
-        <v>16.2426</v>
+        <v>15.0062</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.19</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4077</v>
+        <v>0.3512</v>
       </c>
       <c r="J243" t="n">
-        <v>8.9694</v>
+        <v>7.7264</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3733</v>
+        <v>0.3185</v>
       </c>
       <c r="J244" t="n">
-        <v>8.2126</v>
+        <v>7.007</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0721</v>
       </c>
       <c r="J245" t="n">
-        <v>2.1164</v>
+        <v>1.5862</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.42</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.592</v>
+        <v>-0.6085</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.024</v>
+        <v>-13.387</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2789</v>
+        <v>1.2981</v>
       </c>
       <c r="J247" t="n">
-        <v>28.1358</v>
+        <v>28.5582</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.56</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1854</v>
+        <v>1.1999</v>
       </c>
       <c r="J248" t="n">
-        <v>26.0788</v>
+        <v>26.3978</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0259</v>
+        <v>0.0161</v>
       </c>
       <c r="J249" t="n">
-        <v>0.5698</v>
+        <v>0.3542</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.99</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0728</v>
       </c>
       <c r="J250" t="n">
-        <v>-2.0636</v>
+        <v>-1.6016</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.82</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5793</v>
+        <v>-0.543</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.7446</v>
+        <v>-11.946</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.26</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5876</v>
+        <v>0.5376</v>
       </c>
       <c r="J252" t="n">
-        <v>11.752</v>
+        <v>10.752</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.14</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3719</v>
+        <v>0.3212</v>
       </c>
       <c r="J253" t="n">
-        <v>7.438</v>
+        <v>6.424</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.7</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3321</v>
+        <v>-0.3159</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.642</v>
+        <v>-6.318</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.57</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.449</v>
+        <v>-0.4424</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.98</v>
+        <v>-8.848000000000001</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.54</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4752</v>
+        <v>-0.4716</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.504</v>
+        <v>-9.432</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0298</v>
+        <v>1.0337</v>
       </c>
       <c r="J257" t="n">
-        <v>20.596</v>
+        <v>20.674</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.44</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9987</v>
+        <v>0.9976</v>
       </c>
       <c r="J258" t="n">
-        <v>19.974</v>
+        <v>19.952</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.33</v>
       </c>
       <c r="I259" t="n">
-        <v>0.7972</v>
+        <v>0.7769</v>
       </c>
       <c r="J259" t="n">
-        <v>15.944</v>
+        <v>15.538</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.12</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3461</v>
+        <v>0.314</v>
       </c>
       <c r="J260" t="n">
-        <v>6.922</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>1.12</v>
       </c>
       <c r="I261" t="n">
-        <v>0.3461</v>
+        <v>0.314</v>
       </c>
       <c r="J261" t="n">
-        <v>6.922</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>2.1</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1082</v>
+        <v>1.0722</v>
       </c>
       <c r="J262" t="n">
-        <v>21.0558</v>
+        <v>20.3718</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.68</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7705</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="J263" t="n">
-        <v>14.6395</v>
+        <v>13.2829</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.13</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1936</v>
+        <v>0.1548</v>
       </c>
       <c r="J264" t="n">
-        <v>3.6784</v>
+        <v>2.9412</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1936</v>
+        <v>0.1548</v>
       </c>
       <c r="J265" t="n">
-        <v>3.6784</v>
+        <v>2.9412</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.01</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.0033</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.1653</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.12</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2963</v>
+        <v>0.2977</v>
       </c>
       <c r="J267" t="n">
-        <v>5.6297</v>
+        <v>5.6563</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.88</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1421</v>
+        <v>-0.1266</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.6999</v>
+        <v>-2.4054</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.62</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3925</v>
+        <v>-0.3807</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.4575</v>
+        <v>-7.2333</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.61</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4014</v>
+        <v>-0.3903</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.6266</v>
+        <v>-7.4157</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.45</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5419</v>
+        <v>-0.546</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.2961</v>
+        <v>-10.374</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.52</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9456</v>
+        <v>0.9104</v>
       </c>
       <c r="J272" t="n">
-        <v>15.1296</v>
+        <v>14.5664</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.02</v>
       </c>
       <c r="I273" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="J273" t="n">
-        <v>1.2832</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>0.98</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0401</v>
+        <v>-0.0311</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.4976</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.64</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3977</v>
+        <v>-0.3868</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.3632</v>
+        <v>-6.1888</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.6</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4331</v>
+        <v>-0.4259</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.9296</v>
+        <v>-6.8144</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.76</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4071</v>
+        <v>1.4323</v>
       </c>
       <c r="J277" t="n">
-        <v>22.5136</v>
+        <v>22.9168</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.55</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1407</v>
+        <v>1.1551</v>
       </c>
       <c r="J278" t="n">
-        <v>18.2512</v>
+        <v>18.4816</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>1.28</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6912</v>
+        <v>0.6693</v>
       </c>
       <c r="J279" t="n">
-        <v>11.0592</v>
+        <v>10.7088</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>1.15</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4074</v>
+        <v>0.3759</v>
       </c>
       <c r="J280" t="n">
-        <v>6.5184</v>
+        <v>6.0144</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>1.11</v>
       </c>
       <c r="I281" t="n">
-        <v>0.3088</v>
+        <v>0.2768</v>
       </c>
       <c r="J281" t="n">
-        <v>4.9408</v>
+        <v>4.4288</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.35</v>
       </c>
       <c r="I282" t="n">
-        <v>0.696</v>
+        <v>0.6427</v>
       </c>
       <c r="J282" t="n">
-        <v>13.92</v>
+        <v>12.854</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>0.96</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0689</v>
+        <v>-0.0563</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.378</v>
+        <v>-1.126</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.88</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1639</v>
+        <v>-0.1444</v>
       </c>
       <c r="J284" t="n">
-        <v>-3.278</v>
+        <v>-2.888</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.78</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2663</v>
+        <v>-0.2468</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.326</v>
+        <v>-4.936</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.72</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3234</v>
+        <v>-0.3066</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.468</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1471</v>
+        <v>1.1602</v>
       </c>
       <c r="J287" t="n">
-        <v>22.942</v>
+        <v>23.204</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8743</v>
+        <v>0.855</v>
       </c>
       <c r="J288" t="n">
-        <v>17.486</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.387</v>
+        <v>0.3525</v>
       </c>
       <c r="J289" t="n">
-        <v>7.74</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.11</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3373</v>
+        <v>0.3036</v>
       </c>
       <c r="J290" t="n">
-        <v>6.746</v>
+        <v>6.072</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.83</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.554</v>
+        <v>-0.5163</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.08</v>
+        <v>-10.326</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.99</v>
       </c>
       <c r="I292" t="n">
-        <v>1.035</v>
+        <v>0.9839</v>
       </c>
       <c r="J292" t="n">
-        <v>18.63</v>
+        <v>17.7102</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5511</v>
+        <v>0.4849</v>
       </c>
       <c r="J293" t="n">
-        <v>9.9198</v>
+        <v>8.728199999999999</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.45</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5511</v>
+        <v>0.4849</v>
       </c>
       <c r="J294" t="n">
-        <v>9.9198</v>
+        <v>8.728199999999999</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2456</v>
+        <v>0.2012</v>
       </c>
       <c r="J295" t="n">
-        <v>4.4208</v>
+        <v>3.6216</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>1.01</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.0036</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J296" t="n">
-        <v>-0.0648</v>
+        <v>-0.162</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>0.88</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1258</v>
+        <v>-0.1083</v>
       </c>
       <c r="J297" t="n">
-        <v>-2.2644</v>
+        <v>-1.9494</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>0.77</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2461</v>
+        <v>-0.2321</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.4298</v>
+        <v>-4.1778</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.68</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3318</v>
+        <v>-0.3198</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.9724</v>
+        <v>-5.7564</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.62</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3834</v>
+        <v>-0.3725</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.9012</v>
+        <v>-6.705</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.36</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.0052</v>
+        <v>-11.259</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.25</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5804</v>
+        <v>0.5324</v>
       </c>
       <c r="J302" t="n">
-        <v>9.2864</v>
+        <v>8.5184</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.226</v>
+        <v>-0.208</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.616</v>
+        <v>-3.328</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.77</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2643</v>
+        <v>-0.2462</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.2288</v>
+        <v>-3.9392</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.7</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3298</v>
+        <v>-0.3136</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.2768</v>
+        <v>-5.0176</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.57</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4467</v>
+        <v>-0.4396</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.1472</v>
+        <v>-7.0336</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.96</v>
       </c>
       <c r="I307" t="n">
-        <v>1.6397</v>
+        <v>1.6827</v>
       </c>
       <c r="J307" t="n">
-        <v>26.2352</v>
+        <v>26.9232</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.68</v>
       </c>
       <c r="I308" t="n">
-        <v>1.2996</v>
+        <v>1.3195</v>
       </c>
       <c r="J308" t="n">
-        <v>20.7936</v>
+        <v>21.112</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.54</v>
       </c>
       <c r="I309" t="n">
-        <v>1.1218</v>
+        <v>1.1371</v>
       </c>
       <c r="J309" t="n">
-        <v>17.9488</v>
+        <v>18.1936</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2058</v>
+        <v>-0.179</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.2928</v>
+        <v>-2.864</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.92</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3593</v>
+        <v>-0.3249</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.7488</v>
+        <v>-5.1984</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.32</v>
       </c>
       <c r="I312" t="n">
-        <v>0.621</v>
+        <v>0.5618</v>
       </c>
       <c r="J312" t="n">
-        <v>18.63</v>
+        <v>16.854</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5102</v>
+        <v>0.4508</v>
       </c>
       <c r="J313" t="n">
-        <v>15.306</v>
+        <v>13.524</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.07</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1875</v>
+        <v>0.1488</v>
       </c>
       <c r="J314" t="n">
-        <v>5.625</v>
+        <v>4.464</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.85</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.204</v>
+        <v>-0.1833</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.12</v>
+        <v>-5.499</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.65</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3953</v>
+        <v>-0.385</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.859</v>
+        <v>-11.55</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.3</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7882</v>
+        <v>0.7607</v>
       </c>
       <c r="J317" t="n">
-        <v>23.646</v>
+        <v>22.821</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.23</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6374</v>
+        <v>0.6005</v>
       </c>
       <c r="J318" t="n">
-        <v>19.122</v>
+        <v>18.015</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.07</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2491</v>
+        <v>0.2138</v>
       </c>
       <c r="J319" t="n">
-        <v>7.473</v>
+        <v>6.414</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>1.07</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2491</v>
+        <v>0.2138</v>
       </c>
       <c r="J320" t="n">
-        <v>7.473</v>
+        <v>6.414</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.63</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.9609</v>
       </c>
       <c r="J321" t="n">
-        <v>-29.016</v>
+        <v>-28.827</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.95</v>
       </c>
       <c r="I322" t="n">
-        <v>1.7012</v>
+        <v>1.762</v>
       </c>
       <c r="J322" t="n">
-        <v>40.8288</v>
+        <v>42.288</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.59</v>
       </c>
       <c r="I323" t="n">
-        <v>1.2349</v>
+        <v>1.2523</v>
       </c>
       <c r="J323" t="n">
-        <v>29.6376</v>
+        <v>30.0552</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.82</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5356</v>
       </c>
       <c r="J324" t="n">
-        <v>-13.7544</v>
+        <v>-12.8544</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.6875</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J325" t="n">
-        <v>-16.5</v>
+        <v>-15.7632</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.8395</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="J326" t="n">
-        <v>-20.148</v>
+        <v>-19.7304</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.36</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7024</v>
+        <v>0.6478</v>
       </c>
       <c r="J327" t="n">
-        <v>16.8576</v>
+        <v>15.5472</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2395</v>
+        <v>0.1939</v>
       </c>
       <c r="J328" t="n">
-        <v>5.748</v>
+        <v>4.6536</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.92</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1207</v>
+        <v>-0.1029</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.8968</v>
+        <v>-2.4696</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.84</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2086</v>
+        <v>-0.1881</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.0064</v>
+        <v>-4.5144</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.61</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4254</v>
+        <v>-0.4174</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.2096</v>
+        <v>-10.0176</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.25</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6807</v>
+        <v>0.646</v>
       </c>
       <c r="J332" t="n">
-        <v>23.8245</v>
+        <v>22.61</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.19</v>
       </c>
       <c r="I333" t="n">
-        <v>0.547</v>
+        <v>0.5069</v>
       </c>
       <c r="J333" t="n">
-        <v>19.145</v>
+        <v>17.7415</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.18</v>
       </c>
       <c r="I334" t="n">
-        <v>0.524</v>
+        <v>0.4833</v>
       </c>
       <c r="J334" t="n">
-        <v>18.34</v>
+        <v>16.9155</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.99</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0494</v>
       </c>
       <c r="J335" t="n">
-        <v>-2.401</v>
+        <v>-1.729</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.7</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8213</v>
+        <v>-0.7993</v>
       </c>
       <c r="J336" t="n">
-        <v>-28.7455</v>
+        <v>-27.9755</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.78</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1829</v>
+        <v>1.1724</v>
       </c>
       <c r="J337" t="n">
-        <v>41.4015</v>
+        <v>41.034</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.03</v>
       </c>
       <c r="I338" t="n">
-        <v>0.09</v>
+        <v>0.0682</v>
       </c>
       <c r="J338" t="n">
-        <v>3.15</v>
+        <v>2.387</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.02</v>
       </c>
       <c r="I339" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0465</v>
       </c>
       <c r="J339" t="n">
-        <v>2.212</v>
+        <v>1.6275</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1196</v>
+        <v>-0.101</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.186</v>
+        <v>-3.535</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3281</v>
+        <v>-0.3127</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.4835</v>
+        <v>-10.9445</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.39</v>
       </c>
       <c r="I342" t="n">
-        <v>0.6123</v>
+        <v>0.649</v>
       </c>
       <c r="J342" t="n">
-        <v>12.8583</v>
+        <v>13.629</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.04</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1156</v>
+        <v>0.0997</v>
       </c>
       <c r="J343" t="n">
-        <v>2.4276</v>
+        <v>2.0937</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1703</v>
+        <v>-0.1518</v>
       </c>
       <c r="J344" t="n">
-        <v>-3.5763</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3456</v>
+        <v>-0.33</v>
       </c>
       <c r="J345" t="n">
-        <v>-7.2576</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.42</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5812</v>
+        <v>-0.5935</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.2052</v>
+        <v>-12.4635</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.4</v>
       </c>
       <c r="I347" t="n">
-        <v>0.517</v>
+        <v>0.4487</v>
       </c>
       <c r="J347" t="n">
-        <v>10.857</v>
+        <v>9.422700000000001</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.3</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4098</v>
+        <v>0.348</v>
       </c>
       <c r="J348" t="n">
-        <v>8.6058</v>
+        <v>7.308</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.29</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3988</v>
+        <v>0.3378</v>
       </c>
       <c r="J349" t="n">
-        <v>8.3748</v>
+        <v>7.0938</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>1.22</v>
       </c>
       <c r="I350" t="n">
-        <v>0.3206</v>
+        <v>0.2668</v>
       </c>
       <c r="J350" t="n">
-        <v>6.7326</v>
+        <v>5.6028</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.96</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J351" t="n">
-        <v>-1.9068</v>
+        <v>-1.5813</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.43</v>
       </c>
       <c r="I352" t="n">
-        <v>1.0065</v>
+        <v>1.0045</v>
       </c>
       <c r="J352" t="n">
-        <v>20.13</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.26</v>
       </c>
       <c r="I353" t="n">
-        <v>0.6753</v>
+        <v>0.6434</v>
       </c>
       <c r="J353" t="n">
-        <v>13.506</v>
+        <v>12.868</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.26</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6753</v>
+        <v>0.6434</v>
       </c>
       <c r="J354" t="n">
-        <v>13.506</v>
+        <v>12.868</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.1</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3141</v>
+        <v>0.2806</v>
       </c>
       <c r="J355" t="n">
-        <v>6.282</v>
+        <v>5.612</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.83</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5512</v>
+        <v>-0.513</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.024</v>
+        <v>-10.26</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.35</v>
       </c>
       <c r="I357" t="n">
-        <v>0.6649</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J357" t="n">
-        <v>13.298</v>
+        <v>12.128</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.25</v>
       </c>
       <c r="I358" t="n">
-        <v>0.5083</v>
+        <v>0.449</v>
       </c>
       <c r="J358" t="n">
-        <v>10.166</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>1.15</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3392</v>
+        <v>0.2864</v>
       </c>
       <c r="J359" t="n">
-        <v>6.784</v>
+        <v>5.728</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.85</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2047</v>
+        <v>-0.184</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.094</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.58</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4574</v>
+        <v>-0.454</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.148</v>
+        <v>-9.08</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.9</v>
       </c>
       <c r="I362" t="n">
-        <v>1.6489</v>
+        <v>1.7054</v>
       </c>
       <c r="J362" t="n">
-        <v>37.9247</v>
+        <v>39.2242</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.22</v>
       </c>
       <c r="I363" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5611</v>
       </c>
       <c r="J363" t="n">
-        <v>13.7379</v>
+        <v>12.9053</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.19</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5313</v>
+        <v>0.4937</v>
       </c>
       <c r="J364" t="n">
-        <v>12.2199</v>
+        <v>11.3551</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.9</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3689</v>
+        <v>-0.3268</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.4847</v>
+        <v>-7.5164</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.48</v>
       </c>
       <c r="I366" t="n">
-        <v>-1.276</v>
+        <v>-1.3174</v>
       </c>
       <c r="J366" t="n">
-        <v>-29.348</v>
+        <v>-30.3002</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.3</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5779</v>
+        <v>0.518</v>
       </c>
       <c r="J367" t="n">
-        <v>13.2917</v>
+        <v>11.914</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.2</v>
       </c>
       <c r="I368" t="n">
-        <v>0.4178</v>
+        <v>0.3615</v>
       </c>
       <c r="J368" t="n">
-        <v>9.609400000000001</v>
+        <v>8.314500000000001</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.03</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0924</v>
+        <v>0.0699</v>
       </c>
       <c r="J369" t="n">
-        <v>2.1252</v>
+        <v>1.6077</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.97</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.0641</v>
+        <v>-0.0502</v>
       </c>
       <c r="J370" t="n">
-        <v>-1.4743</v>
+        <v>-1.1546</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1649</v>
+        <v>-0.1446</v>
       </c>
       <c r="J371" t="n">
-        <v>-3.7927</v>
+        <v>-3.3258</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.84</v>
       </c>
       <c r="I372" t="n">
-        <v>0.9506</v>
+        <v>0.8878</v>
       </c>
       <c r="J372" t="n">
-        <v>21.8638</v>
+        <v>20.4194</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.14</v>
       </c>
       <c r="I373" t="n">
-        <v>0.2234</v>
+        <v>0.1802</v>
       </c>
       <c r="J373" t="n">
-        <v>5.1382</v>
+        <v>4.1446</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.12</v>
       </c>
       <c r="I374" t="n">
-        <v>0.1966</v>
+        <v>0.1568</v>
       </c>
       <c r="J374" t="n">
-        <v>4.5218</v>
+        <v>3.6064</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>1.07</v>
       </c>
       <c r="I375" t="n">
-        <v>0.1238</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J375" t="n">
-        <v>2.8474</v>
+        <v>2.1781</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.92</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.1412</v>
+        <v>-0.1225</v>
       </c>
       <c r="J376" t="n">
-        <v>-3.2476</v>
+        <v>-2.8175</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.51</v>
       </c>
       <c r="I377" t="n">
-        <v>0.735</v>
+        <v>0.7935</v>
       </c>
       <c r="J377" t="n">
-        <v>16.905</v>
+        <v>18.2505</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.03</v>
       </c>
       <c r="I378" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0712</v>
       </c>
       <c r="J378" t="n">
-        <v>1.978</v>
+        <v>1.6376</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.96</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.0689</v>
+        <v>-0.0563</v>
       </c>
       <c r="J379" t="n">
-        <v>-1.5847</v>
+        <v>-1.2949</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.68</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3603</v>
+        <v>-0.346</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.286899999999999</v>
+        <v>-7.958</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.51</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5097</v>
+        <v>-0.5119</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.7231</v>
+        <v>-11.7737</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.28</v>
       </c>
       <c r="I382" t="n">
-        <v>0.5904</v>
+        <v>0.5345</v>
       </c>
       <c r="J382" t="n">
-        <v>12.9888</v>
+        <v>11.759</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.17</v>
       </c>
       <c r="I383" t="n">
-        <v>0.4022</v>
+        <v>0.3469</v>
       </c>
       <c r="J383" t="n">
-        <v>8.8484</v>
+        <v>7.6318</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.91</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1292</v>
+        <v>-0.1118</v>
       </c>
       <c r="J384" t="n">
-        <v>-2.8424</v>
+        <v>-2.4596</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.62</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.4126</v>
+        <v>-0.4028</v>
       </c>
       <c r="J385" t="n">
-        <v>-9.077199999999999</v>
+        <v>-8.861599999999999</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.62</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4126</v>
+        <v>-0.4028</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.077199999999999</v>
+        <v>-8.861599999999999</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.82</v>
       </c>
       <c r="I387" t="n">
-        <v>1.5408</v>
+        <v>1.5835</v>
       </c>
       <c r="J387" t="n">
-        <v>33.8976</v>
+        <v>34.837</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.24</v>
       </c>
       <c r="I388" t="n">
-        <v>0.6373</v>
+        <v>0.603</v>
       </c>
       <c r="J388" t="n">
-        <v>14.0206</v>
+        <v>13.266</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.17</v>
       </c>
       <c r="I389" t="n">
-        <v>0.4842</v>
+        <v>0.4471</v>
       </c>
       <c r="J389" t="n">
-        <v>10.6524</v>
+        <v>9.8362</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.9</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3719</v>
+        <v>-0.33</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.181800000000001</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.64</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.9624</v>
+        <v>-0.9583</v>
       </c>
       <c r="J391" t="n">
-        <v>-21.1728</v>
+        <v>-21.0826</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.54</v>
       </c>
       <c r="I392" t="n">
-        <v>0.9579</v>
+        <v>0.9214</v>
       </c>
       <c r="J392" t="n">
-        <v>22.9896</v>
+        <v>22.1136</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.02</v>
       </c>
       <c r="I393" t="n">
-        <v>0.0746</v>
+        <v>0.0531</v>
       </c>
       <c r="J393" t="n">
-        <v>1.7904</v>
+        <v>1.2744</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.89</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.1574</v>
+        <v>-0.1374</v>
       </c>
       <c r="J394" t="n">
-        <v>-3.7776</v>
+        <v>-3.2976</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.78</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2712</v>
+        <v>-0.2519</v>
       </c>
       <c r="J395" t="n">
-        <v>-6.5088</v>
+        <v>-6.0456</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.72</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3283</v>
+        <v>-0.312</v>
       </c>
       <c r="J396" t="n">
-        <v>-7.8792</v>
+        <v>-7.488</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.39</v>
       </c>
       <c r="I397" t="n">
-        <v>0.9635</v>
+        <v>0.9544</v>
       </c>
       <c r="J397" t="n">
-        <v>23.124</v>
+        <v>22.9056</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.16</v>
       </c>
       <c r="I398" t="n">
-        <v>0.4734</v>
+        <v>0.4327</v>
       </c>
       <c r="J398" t="n">
-        <v>11.3616</v>
+        <v>10.3848</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.12</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3769</v>
+        <v>0.3371</v>
       </c>
       <c r="J399" t="n">
-        <v>9.0456</v>
+        <v>8.090400000000001</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.99</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.0718</v>
+        <v>-0.0521</v>
       </c>
       <c r="J400" t="n">
-        <v>-1.7232</v>
+        <v>-1.2504</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.74</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.7383</v>
+        <v>-0.7094</v>
       </c>
       <c r="J401" t="n">
-        <v>-17.7192</v>
+        <v>-17.0256</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.41</v>
       </c>
       <c r="I402" t="n">
-        <v>0.771</v>
+        <v>0.7186</v>
       </c>
       <c r="J402" t="n">
-        <v>15.42</v>
+        <v>14.372</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.06</v>
       </c>
       <c r="I403" t="n">
-        <v>0.1724</v>
+        <v>0.1346</v>
       </c>
       <c r="J403" t="n">
-        <v>3.448</v>
+        <v>2.692</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.01</v>
       </c>
       <c r="I404" t="n">
-        <v>0.0448</v>
+        <v>0.0301</v>
       </c>
       <c r="J404" t="n">
-        <v>0.896</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2708</v>
+        <v>-0.2515</v>
       </c>
       <c r="J405" t="n">
-        <v>-5.416</v>
+        <v>-5.03</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.67</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3738</v>
+        <v>-0.361</v>
       </c>
       <c r="J406" t="n">
-        <v>-7.476</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.56</v>
       </c>
       <c r="I407" t="n">
-        <v>1.1787</v>
+        <v>1.1927</v>
       </c>
       <c r="J407" t="n">
-        <v>23.574</v>
+        <v>23.854</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.56</v>
       </c>
       <c r="I408" t="n">
-        <v>1.1787</v>
+        <v>1.1927</v>
       </c>
       <c r="J408" t="n">
-        <v>23.574</v>
+        <v>23.854</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.44</v>
       </c>
       <c r="I409" t="n">
-        <v>1.0103</v>
+        <v>1.0096</v>
       </c>
       <c r="J409" t="n">
-        <v>20.206</v>
+        <v>20.192</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.98</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1404</v>
+        <v>-0.1136</v>
       </c>
       <c r="J410" t="n">
-        <v>-2.808</v>
+        <v>-2.272</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.62</v>
       </c>
       <c r="I411" t="n">
-        <v>-1.0144</v>
+        <v>-1.0192</v>
       </c>
       <c r="J411" t="n">
-        <v>-20.288</v>
+        <v>-20.384</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.14</v>
       </c>
       <c r="I412" t="n">
-        <v>0.3918</v>
+        <v>0.3448</v>
       </c>
       <c r="J412" t="n">
-        <v>6.2688</v>
+        <v>5.5168</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>0.83</v>
       </c>
       <c r="I413" t="n">
-        <v>-0.2044</v>
+        <v>-0.1877</v>
       </c>
       <c r="J413" t="n">
-        <v>-3.2704</v>
+        <v>-3.0032</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>0.7</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.3267</v>
+        <v>-0.3107</v>
       </c>
       <c r="J414" t="n">
-        <v>-5.2272</v>
+        <v>-4.9712</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.67</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.3541</v>
+        <v>-0.3394</v>
       </c>
       <c r="J415" t="n">
-        <v>-5.6656</v>
+        <v>-5.4304</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.62</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3992</v>
+        <v>-0.3876</v>
       </c>
       <c r="J416" t="n">
-        <v>-6.3872</v>
+        <v>-6.2016</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.94</v>
       </c>
       <c r="I417" t="n">
-        <v>1.5999</v>
+        <v>1.6389</v>
       </c>
       <c r="J417" t="n">
-        <v>25.5984</v>
+        <v>26.2224</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.89</v>
       </c>
       <c r="I418" t="n">
-        <v>1.5411</v>
+        <v>1.5756</v>
       </c>
       <c r="J418" t="n">
-        <v>24.6576</v>
+        <v>25.2096</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>1.4</v>
       </c>
       <c r="I419" t="n">
-        <v>0.907</v>
+        <v>0.9034</v>
       </c>
       <c r="J419" t="n">
-        <v>14.512</v>
+        <v>14.4544</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>1.22</v>
       </c>
       <c r="I420" t="n">
-        <v>0.5481</v>
+        <v>0.5212</v>
       </c>
       <c r="J420" t="n">
-        <v>8.769600000000001</v>
+        <v>8.3392</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>1.01</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.0193</v>
+        <v>-0.0343</v>
       </c>
       <c r="J421" t="n">
-        <v>-0.3088</v>
+        <v>-0.5488</v>
       </c>
     </row>
   </sheetData>
